--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -6360,8 +6360,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="A10:N10"/>
-    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -6360,8 +6360,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="A10:N10"/>
     <mergeCell ref="BV21:BY21"/>
-    <mergeCell ref="A10:N10"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -26,10 +26,738 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+  <si>
+    <t>  1. CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. ACTIVE TABLE / MATRIX</t>
+  </si>
+  <si>
+    <t>  3. REVIEW / DECISION</t>
+  </si>
+  <si>
+    <t>  REFERENCE / SOURCE CONTEXT</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$14)+1</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>ACCESS</t>
+  </si>
+  <si>
+    <t>ACCESS_ACTION_TYPE</t>
+  </si>
+  <si>
+    <t>ADJUST</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>ALL HANDS</t>
+  </si>
+  <si>
+    <t>ANNEX</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>APPROVER</t>
+  </si>
+  <si>
+    <t>ATTENDANCE_STATUS</t>
+  </si>
+  <si>
+    <t>AUDIENCE_CLASS</t>
+  </si>
+  <si>
+    <t>AUDIT_FINDING_SEVERITY</t>
+  </si>
+  <si>
+    <t>AUTHORITY_ROLE</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZED</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Action ID</t>
+  </si>
+  <si>
+    <t>Action Plan</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>BACKUP_FLAG</t>
+  </si>
+  <si>
+    <t>Boundary / SoR</t>
+  </si>
+  <si>
+    <t>CHANGE</t>
+  </si>
+  <si>
+    <t>CHANGE_PRIORITY</t>
+  </si>
+  <si>
+    <t>CHANGE_TYPE</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>COMMERCIAL_REFERENCE</t>
+  </si>
+  <si>
+    <t>COMM_CHANNEL</t>
+  </si>
+  <si>
+    <t>COMPETENCY_LEVEL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CONFIGURATION</t>
+  </si>
+  <si>
+    <t>CONTAINED</t>
+  </si>
+  <si>
+    <t>CONTEXT_CLASS</t>
+  </si>
+  <si>
+    <t>CONTRACT</t>
+  </si>
+  <si>
+    <t>CONTRACT REVIEW</t>
+  </si>
+  <si>
+    <t>CONTRIBUTOR</t>
+  </si>
+  <si>
+    <t>CONTROL_METHOD</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>CREATE</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Cause</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Current Controls</t>
+  </si>
+  <si>
+    <t>DAILY</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>DEPT</t>
+  </si>
+  <si>
+    <t>DETECTION</t>
+  </si>
+  <si>
+    <t>DIMENSIONAL</t>
+  </si>
+  <si>
+    <t>DOCUMENT</t>
+  </si>
+  <si>
+    <t>DOC_STATUS</t>
+  </si>
+  <si>
+    <t>DOC_TYPE</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Department / Owner</t>
+  </si>
+  <si>
+    <t>Detection</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>EACH LOT</t>
+  </si>
+  <si>
+    <t>EFFECTIVE</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>ESCALATE</t>
+  </si>
+  <si>
+    <t>ESCALATED</t>
+  </si>
+  <si>
+    <t>ESCALATION</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Effect of Failure</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Excel Table — PFMEA rows with frozen header and filters</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>FIRST ARTICLE</t>
+  </si>
+  <si>
+    <t>FIRST OFF</t>
+  </si>
+  <si>
+    <t>FIRST PIECE</t>
+  </si>
+  <si>
+    <t>FMEA_RANK</t>
+  </si>
+  <si>
+    <t>FORM</t>
+  </si>
+  <si>
+    <t>FRM-132</t>
+  </si>
+  <si>
+    <t>FUNCTION</t>
+  </si>
+  <si>
+    <t>FUNCTIONAL</t>
+  </si>
+  <si>
+    <t>Failure Mode</t>
+  </si>
+  <si>
+    <t>Failure-mode logic only; convert controls into FRM-133 and downstream release / inspection forms.</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>GATE</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HOURLY</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IMPACT_LEVEL</t>
+  </si>
+  <si>
+    <t>IMPACT_SCOPE</t>
+  </si>
+  <si>
+    <t>IN PROCESS</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>IN-PROCESS</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Issue or Item</t>
+  </si>
+  <si>
+    <t>KPI-COST</t>
+  </si>
+  <si>
+    <t>KPI-DELIVERY</t>
+  </si>
+  <si>
+    <t>KPI-QUALITY</t>
+  </si>
+  <si>
+    <t>KPI-SAFETY</t>
+  </si>
+  <si>
+    <t>KPI-TRAINING</t>
+  </si>
+  <si>
+    <t>KPI_OWNER_SET</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>LESSON_CLASS</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
+  </si>
+  <si>
+    <t>MAJOR</t>
+  </si>
+  <si>
+    <t>MANAGEMENT</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MEETING</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MINOR</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>NOT AUTHORIZED</t>
+  </si>
+  <si>
+    <t>NOT TRAINED</t>
+  </si>
+  <si>
+    <t>NOTICE</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
+  </si>
+  <si>
+    <t>NOTICE: PFMEA entries shall stay process-step specific. Record failure mode, effect, cause, current controls, severity, occurrence, detection and action ownership with ranking discipline.</t>
+  </si>
+  <si>
+    <t>NOTICE: Use one row per action. Record issue, owner, due date, status and verification evidence; do not close actions without objective evidence.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVED</t>
+  </si>
+  <si>
+    <t>OBSOLETE</t>
+  </si>
+  <si>
+    <t>ON HOLD</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>Occurrence</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PEOPLE</t>
+  </si>
+  <si>
+    <t>PESTLE</t>
+  </si>
+  <si>
+    <t>PFMEA ID</t>
+  </si>
+  <si>
+    <t>PFMEA LITE</t>
+  </si>
+  <si>
+    <t>PFMEA LITE — ACTION TRACKER</t>
+  </si>
+  <si>
+    <t>PFMEA LITE — CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>PFMEA LITE — RANKING REFERENCE</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PO</t>
+  </si>
+  <si>
+    <t>POLICY</t>
+  </si>
+  <si>
+    <t>PORTAL</t>
+  </si>
+  <si>
+    <t>PRESENT</t>
+  </si>
+  <si>
+    <t>PREVENTION</t>
+  </si>
+  <si>
+    <t>PROCESS</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Part / Process / Operation</t>
+  </si>
+  <si>
+    <t>Per authority matrix</t>
+  </si>
+  <si>
+    <t>Post-Action Reassessment</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Prepared Date</t>
+  </si>
+  <si>
+    <t>Priority or RPN</t>
+  </si>
+  <si>
+    <t>Process Function or Step</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QMS</t>
+  </si>
+  <si>
+    <t>QUALITY</t>
+  </si>
+  <si>
+    <t>QUOTE</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REACTION_CLASS</t>
+  </si>
+  <si>
+    <t>RECHECK</t>
+  </si>
+  <si>
+    <t>RECORD</t>
+  </si>
+  <si>
+    <t>RECOVERING</t>
+  </si>
+  <si>
+    <t>RECOVERY_STATUS</t>
+  </si>
+  <si>
+    <t>REGULATORY</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>REMOVE</t>
+  </si>
+  <si>
+    <t>REQUESTER</t>
+  </si>
+  <si>
+    <t>RESPONSE</t>
+  </si>
+  <si>
+    <t>RESTORED</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>REVIEWER</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>RISK_CATEGORY</t>
+  </si>
+  <si>
+    <t>ROLE</t>
+  </si>
+  <si>
+    <t>ROLE_ACCESS_PROFILE</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Record ID</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Reference / code-support sheet for controlled vocabulary or approved code mappings.</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SAFETY</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SAMPLE_FREQUENCY</t>
+  </si>
+  <si>
+    <t>SEGREGATE</t>
+  </si>
+  <si>
+    <t>SHIFT</t>
+  </si>
+  <si>
+    <t>SHIPPING</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>SOP</t>
+  </si>
+  <si>
+    <t>SOP: SOP-103 | ANNEX: ANNEX-QA-004, ANNEX-QA-006, ANNEX-QMS-027</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>STOP</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>SUPERVISED</t>
+  </si>
+  <si>
+    <t>SUSPENDED</t>
+  </si>
+  <si>
+    <t>SWOT</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Source Links</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>TRAINER</t>
+  </si>
+  <si>
+    <t>TRAINING</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VIEWER</t>
+  </si>
+  <si>
+    <t>VISUAL</t>
+  </si>
+  <si>
+    <t>Verification or Evidence</t>
+  </si>
+  <si>
+    <t>WEEKLY</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +868,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +931,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="145">
+  <borders count="148">
     <border>
       <left/>
       <right/>
@@ -1757,11 +2495,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="384">
+  <cellXfs count="387">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2788,6 +3560,15 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6212,93 +6993,93 @@
       <c r="CC33" s="32" t="n"/>
       <c r="CD33" s="343" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="335" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="384" t="inlineStr">
         <is>
           <t>NOTICE: PFMEA entries shall stay process-step specific. Record failure mode, effect, cause, current controls, severity, occurrence, detection and action ownership with ranking discipline.</t>
         </is>
       </c>
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="22" t="n"/>
-      <c r="J34" s="22" t="n"/>
-      <c r="K34" s="22" t="n"/>
-      <c r="L34" s="22" t="n"/>
-      <c r="M34" s="22" t="n"/>
-      <c r="N34" s="22" t="n"/>
-      <c r="O34" s="22" t="n"/>
-      <c r="P34" s="22" t="n"/>
-      <c r="Q34" s="22" t="n"/>
-      <c r="R34" s="22" t="n"/>
-      <c r="S34" s="22" t="n"/>
-      <c r="T34" s="22" t="n"/>
-      <c r="U34" s="22" t="n"/>
-      <c r="V34" s="22" t="n"/>
-      <c r="W34" s="22" t="n"/>
-      <c r="X34" s="22" t="n"/>
-      <c r="Y34" s="22" t="n"/>
-      <c r="Z34" s="22" t="n"/>
-      <c r="AA34" s="22" t="n"/>
-      <c r="AB34" s="22" t="n"/>
-      <c r="AC34" s="22" t="n"/>
-      <c r="AD34" s="22" t="n"/>
-      <c r="AE34" s="22" t="n"/>
-      <c r="AF34" s="22" t="n"/>
-      <c r="AG34" s="22" t="n"/>
-      <c r="AH34" s="22" t="n"/>
-      <c r="AI34" s="22" t="n"/>
-      <c r="AJ34" s="22" t="n"/>
-      <c r="AK34" s="22" t="n"/>
-      <c r="AL34" s="22" t="n"/>
-      <c r="AM34" s="22" t="n"/>
-      <c r="AN34" s="22" t="n"/>
-      <c r="AO34" s="22" t="n"/>
-      <c r="AP34" s="22" t="n"/>
-      <c r="AQ34" s="22" t="n"/>
-      <c r="AR34" s="22" t="n"/>
-      <c r="AS34" s="22" t="n"/>
-      <c r="AT34" s="22" t="n"/>
-      <c r="AU34" s="22" t="n"/>
-      <c r="AV34" s="22" t="n"/>
-      <c r="AW34" s="22" t="n"/>
-      <c r="AX34" s="22" t="n"/>
-      <c r="AY34" s="22" t="n"/>
-      <c r="AZ34" s="22" t="n"/>
-      <c r="BA34" s="22" t="n"/>
-      <c r="BB34" s="22" t="n"/>
-      <c r="BC34" s="22" t="n"/>
-      <c r="BD34" s="22" t="n"/>
-      <c r="BE34" s="22" t="n"/>
-      <c r="BF34" s="22" t="n"/>
-      <c r="BG34" s="22" t="n"/>
-      <c r="BH34" s="22" t="n"/>
-      <c r="BI34" s="22" t="n"/>
-      <c r="BJ34" s="22" t="n"/>
-      <c r="BK34" s="22" t="n"/>
-      <c r="BL34" s="22" t="n"/>
-      <c r="BM34" s="22" t="n"/>
-      <c r="BN34" s="22" t="n"/>
-      <c r="BO34" s="22" t="n"/>
-      <c r="BP34" s="22" t="n"/>
-      <c r="BQ34" s="22" t="n"/>
-      <c r="BR34" s="22" t="n"/>
-      <c r="BS34" s="22" t="n"/>
-      <c r="BT34" s="22" t="n"/>
-      <c r="BU34" s="22" t="n"/>
-      <c r="BV34" s="22" t="n"/>
-      <c r="BW34" s="22" t="n"/>
-      <c r="BX34" s="22" t="n"/>
-      <c r="BY34" s="22" t="n"/>
-      <c r="BZ34" s="22" t="n"/>
-      <c r="CA34" s="22" t="n"/>
-      <c r="CB34" s="22" t="n"/>
-      <c r="CC34" s="22" t="n"/>
-      <c r="CD34" s="23" t="n"/>
+      <c r="B34" s="385" t="n"/>
+      <c r="C34" s="385" t="n"/>
+      <c r="D34" s="385" t="n"/>
+      <c r="E34" s="385" t="n"/>
+      <c r="F34" s="385" t="n"/>
+      <c r="G34" s="385" t="n"/>
+      <c r="H34" s="385" t="n"/>
+      <c r="I34" s="385" t="n"/>
+      <c r="J34" s="385" t="n"/>
+      <c r="K34" s="385" t="n"/>
+      <c r="L34" s="385" t="n"/>
+      <c r="M34" s="385" t="n"/>
+      <c r="N34" s="385" t="n"/>
+      <c r="O34" s="385" t="n"/>
+      <c r="P34" s="385" t="n"/>
+      <c r="Q34" s="385" t="n"/>
+      <c r="R34" s="385" t="n"/>
+      <c r="S34" s="385" t="n"/>
+      <c r="T34" s="385" t="n"/>
+      <c r="U34" s="385" t="n"/>
+      <c r="V34" s="385" t="n"/>
+      <c r="W34" s="385" t="n"/>
+      <c r="X34" s="385" t="n"/>
+      <c r="Y34" s="385" t="n"/>
+      <c r="Z34" s="385" t="n"/>
+      <c r="AA34" s="385" t="n"/>
+      <c r="AB34" s="385" t="n"/>
+      <c r="AC34" s="385" t="n"/>
+      <c r="AD34" s="385" t="n"/>
+      <c r="AE34" s="385" t="n"/>
+      <c r="AF34" s="385" t="n"/>
+      <c r="AG34" s="385" t="n"/>
+      <c r="AH34" s="385" t="n"/>
+      <c r="AI34" s="385" t="n"/>
+      <c r="AJ34" s="385" t="n"/>
+      <c r="AK34" s="385" t="n"/>
+      <c r="AL34" s="385" t="n"/>
+      <c r="AM34" s="385" t="n"/>
+      <c r="AN34" s="385" t="n"/>
+      <c r="AO34" s="385" t="n"/>
+      <c r="AP34" s="385" t="n"/>
+      <c r="AQ34" s="385" t="n"/>
+      <c r="AR34" s="385" t="n"/>
+      <c r="AS34" s="385" t="n"/>
+      <c r="AT34" s="385" t="n"/>
+      <c r="AU34" s="385" t="n"/>
+      <c r="AV34" s="385" t="n"/>
+      <c r="AW34" s="385" t="n"/>
+      <c r="AX34" s="385" t="n"/>
+      <c r="AY34" s="385" t="n"/>
+      <c r="AZ34" s="385" t="n"/>
+      <c r="BA34" s="385" t="n"/>
+      <c r="BB34" s="385" t="n"/>
+      <c r="BC34" s="385" t="n"/>
+      <c r="BD34" s="385" t="n"/>
+      <c r="BE34" s="385" t="n"/>
+      <c r="BF34" s="385" t="n"/>
+      <c r="BG34" s="385" t="n"/>
+      <c r="BH34" s="385" t="n"/>
+      <c r="BI34" s="385" t="n"/>
+      <c r="BJ34" s="385" t="n"/>
+      <c r="BK34" s="385" t="n"/>
+      <c r="BL34" s="385" t="n"/>
+      <c r="BM34" s="385" t="n"/>
+      <c r="BN34" s="385" t="n"/>
+      <c r="BO34" s="385" t="n"/>
+      <c r="BP34" s="385" t="n"/>
+      <c r="BQ34" s="385" t="n"/>
+      <c r="BR34" s="385" t="n"/>
+      <c r="BS34" s="385" t="n"/>
+      <c r="BT34" s="385" t="n"/>
+      <c r="BU34" s="385" t="n"/>
+      <c r="BV34" s="385" t="n"/>
+      <c r="BW34" s="385" t="n"/>
+      <c r="BX34" s="385" t="n"/>
+      <c r="BY34" s="385" t="n"/>
+      <c r="BZ34" s="385" t="n"/>
+      <c r="CA34" s="385" t="n"/>
+      <c r="CB34" s="385" t="n"/>
+      <c r="CC34" s="385" t="n"/>
+      <c r="CD34" s="386" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -6360,8 +7141,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="A10:N10"/>
-    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>
@@ -9744,93 +10525,93 @@
       <c r="CC18" s="346" t="n"/>
       <c r="CD18" s="350" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="335" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="384" t="inlineStr">
         <is>
           <t>NOTICE: Use one row per action. Record issue, owner, due date, status and verification evidence; do not close actions without objective evidence.</t>
         </is>
       </c>
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="22" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="22" t="n"/>
-      <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="22" t="n"/>
-      <c r="M19" s="22" t="n"/>
-      <c r="N19" s="22" t="n"/>
-      <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
-      <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="22" t="n"/>
-      <c r="S19" s="22" t="n"/>
-      <c r="T19" s="22" t="n"/>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="22" t="n"/>
-      <c r="W19" s="22" t="n"/>
-      <c r="X19" s="22" t="n"/>
-      <c r="Y19" s="22" t="n"/>
-      <c r="Z19" s="22" t="n"/>
-      <c r="AA19" s="22" t="n"/>
-      <c r="AB19" s="22" t="n"/>
-      <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="22" t="n"/>
-      <c r="AE19" s="22" t="n"/>
-      <c r="AF19" s="22" t="n"/>
-      <c r="AG19" s="22" t="n"/>
-      <c r="AH19" s="22" t="n"/>
-      <c r="AI19" s="22" t="n"/>
-      <c r="AJ19" s="22" t="n"/>
-      <c r="AK19" s="22" t="n"/>
-      <c r="AL19" s="22" t="n"/>
-      <c r="AM19" s="22" t="n"/>
-      <c r="AN19" s="22" t="n"/>
-      <c r="AO19" s="22" t="n"/>
-      <c r="AP19" s="22" t="n"/>
-      <c r="AQ19" s="22" t="n"/>
-      <c r="AR19" s="22" t="n"/>
-      <c r="AS19" s="22" t="n"/>
-      <c r="AT19" s="22" t="n"/>
-      <c r="AU19" s="22" t="n"/>
-      <c r="AV19" s="22" t="n"/>
-      <c r="AW19" s="22" t="n"/>
-      <c r="AX19" s="22" t="n"/>
-      <c r="AY19" s="22" t="n"/>
-      <c r="AZ19" s="22" t="n"/>
-      <c r="BA19" s="22" t="n"/>
-      <c r="BB19" s="22" t="n"/>
-      <c r="BC19" s="22" t="n"/>
-      <c r="BD19" s="22" t="n"/>
-      <c r="BE19" s="22" t="n"/>
-      <c r="BF19" s="22" t="n"/>
-      <c r="BG19" s="22" t="n"/>
-      <c r="BH19" s="22" t="n"/>
-      <c r="BI19" s="22" t="n"/>
-      <c r="BJ19" s="22" t="n"/>
-      <c r="BK19" s="22" t="n"/>
-      <c r="BL19" s="22" t="n"/>
-      <c r="BM19" s="22" t="n"/>
-      <c r="BN19" s="22" t="n"/>
-      <c r="BO19" s="22" t="n"/>
-      <c r="BP19" s="22" t="n"/>
-      <c r="BQ19" s="22" t="n"/>
-      <c r="BR19" s="22" t="n"/>
-      <c r="BS19" s="22" t="n"/>
-      <c r="BT19" s="22" t="n"/>
-      <c r="BU19" s="22" t="n"/>
-      <c r="BV19" s="22" t="n"/>
-      <c r="BW19" s="22" t="n"/>
-      <c r="BX19" s="22" t="n"/>
-      <c r="BY19" s="22" t="n"/>
-      <c r="BZ19" s="22" t="n"/>
-      <c r="CA19" s="22" t="n"/>
-      <c r="CB19" s="22" t="n"/>
-      <c r="CC19" s="22" t="n"/>
-      <c r="CD19" s="23" t="n"/>
+      <c r="B19" s="385" t="n"/>
+      <c r="C19" s="385" t="n"/>
+      <c r="D19" s="385" t="n"/>
+      <c r="E19" s="385" t="n"/>
+      <c r="F19" s="385" t="n"/>
+      <c r="G19" s="385" t="n"/>
+      <c r="H19" s="385" t="n"/>
+      <c r="I19" s="385" t="n"/>
+      <c r="J19" s="385" t="n"/>
+      <c r="K19" s="385" t="n"/>
+      <c r="L19" s="385" t="n"/>
+      <c r="M19" s="385" t="n"/>
+      <c r="N19" s="385" t="n"/>
+      <c r="O19" s="385" t="n"/>
+      <c r="P19" s="385" t="n"/>
+      <c r="Q19" s="385" t="n"/>
+      <c r="R19" s="385" t="n"/>
+      <c r="S19" s="385" t="n"/>
+      <c r="T19" s="385" t="n"/>
+      <c r="U19" s="385" t="n"/>
+      <c r="V19" s="385" t="n"/>
+      <c r="W19" s="385" t="n"/>
+      <c r="X19" s="385" t="n"/>
+      <c r="Y19" s="385" t="n"/>
+      <c r="Z19" s="385" t="n"/>
+      <c r="AA19" s="385" t="n"/>
+      <c r="AB19" s="385" t="n"/>
+      <c r="AC19" s="385" t="n"/>
+      <c r="AD19" s="385" t="n"/>
+      <c r="AE19" s="385" t="n"/>
+      <c r="AF19" s="385" t="n"/>
+      <c r="AG19" s="385" t="n"/>
+      <c r="AH19" s="385" t="n"/>
+      <c r="AI19" s="385" t="n"/>
+      <c r="AJ19" s="385" t="n"/>
+      <c r="AK19" s="385" t="n"/>
+      <c r="AL19" s="385" t="n"/>
+      <c r="AM19" s="385" t="n"/>
+      <c r="AN19" s="385" t="n"/>
+      <c r="AO19" s="385" t="n"/>
+      <c r="AP19" s="385" t="n"/>
+      <c r="AQ19" s="385" t="n"/>
+      <c r="AR19" s="385" t="n"/>
+      <c r="AS19" s="385" t="n"/>
+      <c r="AT19" s="385" t="n"/>
+      <c r="AU19" s="385" t="n"/>
+      <c r="AV19" s="385" t="n"/>
+      <c r="AW19" s="385" t="n"/>
+      <c r="AX19" s="385" t="n"/>
+      <c r="AY19" s="385" t="n"/>
+      <c r="AZ19" s="385" t="n"/>
+      <c r="BA19" s="385" t="n"/>
+      <c r="BB19" s="385" t="n"/>
+      <c r="BC19" s="385" t="n"/>
+      <c r="BD19" s="385" t="n"/>
+      <c r="BE19" s="385" t="n"/>
+      <c r="BF19" s="385" t="n"/>
+      <c r="BG19" s="385" t="n"/>
+      <c r="BH19" s="385" t="n"/>
+      <c r="BI19" s="385" t="n"/>
+      <c r="BJ19" s="385" t="n"/>
+      <c r="BK19" s="385" t="n"/>
+      <c r="BL19" s="385" t="n"/>
+      <c r="BM19" s="385" t="n"/>
+      <c r="BN19" s="385" t="n"/>
+      <c r="BO19" s="385" t="n"/>
+      <c r="BP19" s="385" t="n"/>
+      <c r="BQ19" s="385" t="n"/>
+      <c r="BR19" s="385" t="n"/>
+      <c r="BS19" s="385" t="n"/>
+      <c r="BT19" s="385" t="n"/>
+      <c r="BU19" s="385" t="n"/>
+      <c r="BV19" s="385" t="n"/>
+      <c r="BW19" s="385" t="n"/>
+      <c r="BX19" s="385" t="n"/>
+      <c r="BY19" s="385" t="n"/>
+      <c r="BZ19" s="385" t="n"/>
+      <c r="CA19" s="385" t="n"/>
+      <c r="CB19" s="385" t="n"/>
+      <c r="CC19" s="385" t="n"/>
+      <c r="CD19" s="386" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -8,26 +8,23 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM132_PFMEA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM132_RankRef" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM132_Actions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM132_Actions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="3" state="veryHidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM132_PFMEA'!$1:$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FRM132_PFMEA'!$A$1:$CD$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FRM132_RankRef'!$1:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'FRM132_RankRef'!$A$1:$CD$18</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'FRM132_Actions'!$1:$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'FRM132_Actions'!$A$1:$CD$19</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'zLISTS'!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'zLISTS'!$A$1:$BD$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FRM132_Actions'!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'FRM132_Actions'!$A$1:$CD$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'zLISTS'!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'zLISTS'!$A$1:$BD$20</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" calcOnSave="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t>  1. CONTROLLED LOOKUP LISTS</t>
   </si>
@@ -407,9 +404,6 @@
     <t>LOW</t>
   </si>
   <si>
-    <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
-  </si>
-  <si>
     <t>MAJOR</t>
   </si>
   <si>
@@ -431,9 +425,6 @@
     <t>MONITORING</t>
   </si>
   <si>
-    <t>Meaning</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
@@ -458,9 +449,6 @@
     <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
   </si>
   <si>
-    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
-  </si>
-  <si>
     <t>NOTICE: PFMEA entries shall stay process-step specific. Record failure mode, effect, cause, current controls, severity, occurrence, detection and action ownership with ranking discipline.</t>
   </si>
   <si>
@@ -473,9 +461,6 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>OBSERVED</t>
   </si>
   <si>
@@ -518,9 +503,6 @@
     <t>PFMEA LITE — CONTROLLED LOOKUP LISTS</t>
   </si>
   <si>
-    <t>PFMEA LITE — RANKING REFERENCE</t>
-  </si>
-  <si>
     <t>PLANNING</t>
   </si>
   <si>
@@ -638,18 +620,12 @@
     <t>ROLE_ACCESS_PROFILE</t>
   </si>
   <si>
-    <t>Rank</t>
-  </si>
-  <si>
     <t>Record ID</t>
   </si>
   <si>
     <t>Record Status</t>
   </si>
   <si>
-    <t>Reference / code-support sheet for controlled vocabulary or approved code mappings.</t>
-  </si>
-  <si>
     <t>Reviewed By</t>
   </si>
   <si>
@@ -705,9 +681,6 @@
   </si>
   <si>
     <t>Severity</t>
-  </si>
-  <si>
-    <t>Source</t>
   </si>
   <si>
     <t>Source Links</t>
@@ -937,7 +910,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="148">
+  <borders count="153">
     <border>
       <left/>
       <right/>
@@ -2529,11 +2502,69 @@
         <color rgb="00F9A825"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="387">
+  <cellXfs count="390">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3570,6 +3601,11 @@
     <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3713,39 +3749,6 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>622620</colOff>
-      <row>0</row>
-      <rowOff>238275</rowOff>
-    </from>
-    <ext cx="1652040" cy="476550"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -7141,8 +7144,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="A10:N10"/>
     <mergeCell ref="BV21:BY21"/>
-    <mergeCell ref="A10:N10"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>
@@ -7391,1601 +7394,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:CD18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-    <col width="2.33" customWidth="1" min="41" max="41"/>
-    <col width="2.33" customWidth="1" min="42" max="42"/>
-    <col width="2.33" customWidth="1" min="43" max="43"/>
-    <col width="2.33" customWidth="1" min="44" max="44"/>
-    <col width="2.33" customWidth="1" min="45" max="45"/>
-    <col width="2.33" customWidth="1" min="46" max="46"/>
-    <col width="2.33" customWidth="1" min="47" max="47"/>
-    <col width="2.33" customWidth="1" min="48" max="48"/>
-    <col width="2.33" customWidth="1" min="49" max="49"/>
-    <col width="2.33" customWidth="1" min="50" max="50"/>
-    <col width="2.33" customWidth="1" min="51" max="51"/>
-    <col width="2.33" customWidth="1" min="52" max="52"/>
-    <col width="2.33" customWidth="1" min="53" max="53"/>
-    <col width="2.33" customWidth="1" min="54" max="54"/>
-    <col width="2.33" customWidth="1" min="55" max="55"/>
-    <col width="2.33" customWidth="1" min="56" max="56"/>
-    <col width="2.33" customWidth="1" min="57" max="57"/>
-    <col width="2.33" customWidth="1" min="58" max="58"/>
-    <col width="2.33" customWidth="1" min="59" max="59"/>
-    <col width="2.33" customWidth="1" min="60" max="60"/>
-    <col width="2.33" customWidth="1" min="61" max="61"/>
-    <col width="2.33" customWidth="1" min="62" max="62"/>
-    <col width="2.33" customWidth="1" min="63" max="63"/>
-    <col width="2.33" customWidth="1" min="64" max="64"/>
-    <col width="2.33" customWidth="1" min="65" max="65"/>
-    <col width="2.33" customWidth="1" min="66" max="66"/>
-    <col width="2.33" customWidth="1" min="67" max="67"/>
-    <col width="2.33" customWidth="1" min="68" max="68"/>
-    <col width="2.33" customWidth="1" min="69" max="69"/>
-    <col width="2.33" customWidth="1" min="70" max="70"/>
-    <col width="2.33" customWidth="1" min="71" max="71"/>
-    <col width="2.33" customWidth="1" min="72" max="72"/>
-    <col width="2.33" customWidth="1" min="73" max="73"/>
-    <col width="2.33" customWidth="1" min="74" max="74"/>
-    <col width="2.33" customWidth="1" min="75" max="75"/>
-    <col width="2.33" customWidth="1" min="76" max="76"/>
-    <col width="2.33" customWidth="1" min="77" max="77"/>
-    <col width="2.33" customWidth="1" min="78" max="78"/>
-    <col width="2.33" customWidth="1" min="79" max="79"/>
-    <col width="2.33" customWidth="1" min="80" max="80"/>
-    <col width="2.33" customWidth="1" min="81" max="81"/>
-    <col width="2.33" customWidth="1" min="82" max="82"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="321" t="n"/>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="227" t="inlineStr">
-        <is>
-          <t>PFMEA LITE — RANKING REFERENCE</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
-      <c r="W1" s="2" t="n"/>
-      <c r="X1" s="2" t="n"/>
-      <c r="Y1" s="2" t="n"/>
-      <c r="Z1" s="2" t="n"/>
-      <c r="AA1" s="2" t="n"/>
-      <c r="AB1" s="2" t="n"/>
-      <c r="AC1" s="2" t="n"/>
-      <c r="AD1" s="2" t="n"/>
-      <c r="AE1" s="2" t="n"/>
-      <c r="AF1" s="2" t="n"/>
-      <c r="AG1" s="2" t="n"/>
-      <c r="AH1" s="2" t="n"/>
-      <c r="AI1" s="2" t="n"/>
-      <c r="AJ1" s="2" t="n"/>
-      <c r="AK1" s="2" t="n"/>
-      <c r="AL1" s="2" t="n"/>
-      <c r="AM1" s="2" t="n"/>
-      <c r="AN1" s="2" t="n"/>
-      <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
-      <c r="AQ1" s="2" t="n"/>
-      <c r="AR1" s="2" t="n"/>
-      <c r="AS1" s="2" t="n"/>
-      <c r="AT1" s="2" t="n"/>
-      <c r="AU1" s="2" t="n"/>
-      <c r="AV1" s="2" t="n"/>
-      <c r="AW1" s="2" t="n"/>
-      <c r="AX1" s="2" t="n"/>
-      <c r="AY1" s="2" t="n"/>
-      <c r="AZ1" s="2" t="n"/>
-      <c r="BA1" s="2" t="n"/>
-      <c r="BB1" s="2" t="n"/>
-      <c r="BC1" s="2" t="n"/>
-      <c r="BD1" s="2" t="n"/>
-      <c r="BE1" s="2" t="n"/>
-      <c r="BF1" s="2" t="n"/>
-      <c r="BG1" s="2" t="n"/>
-      <c r="BH1" s="2" t="n"/>
-      <c r="BI1" s="2" t="n"/>
-      <c r="BJ1" s="2" t="n"/>
-      <c r="BK1" s="322" t="inlineStr">
-        <is>
-          <t>Form Code</t>
-        </is>
-      </c>
-      <c r="BL1" s="2" t="n"/>
-      <c r="BM1" s="2" t="n"/>
-      <c r="BN1" s="2" t="n"/>
-      <c r="BO1" s="2" t="n"/>
-      <c r="BP1" s="2" t="n"/>
-      <c r="BQ1" s="2" t="n"/>
-      <c r="BR1" s="323" t="n"/>
-      <c r="BS1" s="324" t="inlineStr">
-        <is>
-          <t>FRM-132</t>
-        </is>
-      </c>
-      <c r="BT1" s="2" t="n"/>
-      <c r="BU1" s="2" t="n"/>
-      <c r="BV1" s="2" t="n"/>
-      <c r="BW1" s="2" t="n"/>
-      <c r="BX1" s="2" t="n"/>
-      <c r="BY1" s="2" t="n"/>
-      <c r="BZ1" s="2" t="n"/>
-      <c r="CA1" s="2" t="n"/>
-      <c r="CB1" s="2" t="n"/>
-      <c r="CC1" s="2" t="n"/>
-      <c r="CD1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="BK2" s="325" t="inlineStr">
-        <is>
-          <t>Revision</t>
-        </is>
-      </c>
-      <c r="BL2" s="326" t="n"/>
-      <c r="BM2" s="326" t="n"/>
-      <c r="BN2" s="326" t="n"/>
-      <c r="BO2" s="326" t="n"/>
-      <c r="BP2" s="326" t="n"/>
-      <c r="BQ2" s="326" t="n"/>
-      <c r="BR2" s="327" t="n"/>
-      <c r="BS2" s="328" t="inlineStr">
-        <is>
-          <t>V0</t>
-        </is>
-      </c>
-      <c r="BT2" s="326" t="n"/>
-      <c r="BU2" s="326" t="n"/>
-      <c r="BV2" s="326" t="n"/>
-      <c r="BW2" s="326" t="n"/>
-      <c r="BX2" s="326" t="n"/>
-      <c r="BY2" s="326" t="n"/>
-      <c r="BZ2" s="326" t="n"/>
-      <c r="CA2" s="326" t="n"/>
-      <c r="CB2" s="326" t="n"/>
-      <c r="CC2" s="326" t="n"/>
-      <c r="CD2" s="329" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="BK3" s="325" t="inlineStr">
-        <is>
-          <t>Eff. Date</t>
-        </is>
-      </c>
-      <c r="BL3" s="326" t="n"/>
-      <c r="BM3" s="326" t="n"/>
-      <c r="BN3" s="326" t="n"/>
-      <c r="BO3" s="326" t="n"/>
-      <c r="BP3" s="326" t="n"/>
-      <c r="BQ3" s="326" t="n"/>
-      <c r="BR3" s="327" t="n"/>
-      <c r="BS3" s="328" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
-      <c r="BT3" s="326" t="n"/>
-      <c r="BU3" s="326" t="n"/>
-      <c r="BV3" s="326" t="n"/>
-      <c r="BW3" s="326" t="n"/>
-      <c r="BX3" s="326" t="n"/>
-      <c r="BY3" s="326" t="n"/>
-      <c r="BZ3" s="326" t="n"/>
-      <c r="CA3" s="326" t="n"/>
-      <c r="CB3" s="326" t="n"/>
-      <c r="CC3" s="326" t="n"/>
-      <c r="CD3" s="329" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="239" t="inlineStr">
-        <is>
-          <t>Quality Management System · Controlled Document</t>
-        </is>
-      </c>
-      <c r="BK4" s="325" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="BL4" s="326" t="n"/>
-      <c r="BM4" s="326" t="n"/>
-      <c r="BN4" s="326" t="n"/>
-      <c r="BO4" s="326" t="n"/>
-      <c r="BP4" s="326" t="n"/>
-      <c r="BQ4" s="326" t="n"/>
-      <c r="BR4" s="327" t="n"/>
-      <c r="BS4" s="328" t="inlineStr">
-        <is>
-          <t>QMS</t>
-        </is>
-      </c>
-      <c r="BT4" s="326" t="n"/>
-      <c r="BU4" s="326" t="n"/>
-      <c r="BV4" s="326" t="n"/>
-      <c r="BW4" s="326" t="n"/>
-      <c r="BX4" s="326" t="n"/>
-      <c r="BY4" s="326" t="n"/>
-      <c r="BZ4" s="326" t="n"/>
-      <c r="CA4" s="326" t="n"/>
-      <c r="CB4" s="326" t="n"/>
-      <c r="CC4" s="326" t="n"/>
-      <c r="CD4" s="329" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="18" t="n"/>
-      <c r="Q5" s="50" t="inlineStr">
-        <is>
-          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-        </is>
-      </c>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="17" t="n"/>
-      <c r="AR5" s="17" t="n"/>
-      <c r="AS5" s="17" t="n"/>
-      <c r="AT5" s="17" t="n"/>
-      <c r="AU5" s="17" t="n"/>
-      <c r="AV5" s="17" t="n"/>
-      <c r="AW5" s="17" t="n"/>
-      <c r="AX5" s="17" t="n"/>
-      <c r="AY5" s="17" t="n"/>
-      <c r="AZ5" s="17" t="n"/>
-      <c r="BA5" s="17" t="n"/>
-      <c r="BB5" s="17" t="n"/>
-      <c r="BC5" s="17" t="n"/>
-      <c r="BD5" s="17" t="n"/>
-      <c r="BE5" s="17" t="n"/>
-      <c r="BF5" s="17" t="n"/>
-      <c r="BG5" s="17" t="n"/>
-      <c r="BH5" s="17" t="n"/>
-      <c r="BI5" s="17" t="n"/>
-      <c r="BJ5" s="17" t="n"/>
-      <c r="BK5" s="330" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="BL5" s="331" t="n"/>
-      <c r="BM5" s="331" t="n"/>
-      <c r="BN5" s="331" t="n"/>
-      <c r="BO5" s="331" t="n"/>
-      <c r="BP5" s="331" t="n"/>
-      <c r="BQ5" s="331" t="n"/>
-      <c r="BR5" s="332" t="n"/>
-      <c r="BS5" s="333" t="inlineStr">
-        <is>
-          <t>Per authority matrix</t>
-        </is>
-      </c>
-      <c r="BT5" s="331" t="n"/>
-      <c r="BU5" s="331" t="n"/>
-      <c r="BV5" s="331" t="n"/>
-      <c r="BW5" s="331" t="n"/>
-      <c r="BX5" s="331" t="n"/>
-      <c r="BY5" s="331" t="n"/>
-      <c r="BZ5" s="331" t="n"/>
-      <c r="CA5" s="331" t="n"/>
-      <c r="CB5" s="331" t="n"/>
-      <c r="CC5" s="331" t="n"/>
-      <c r="CD5" s="334" t="n"/>
-    </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="248" t="n"/>
-      <c r="B6" s="248" t="n"/>
-      <c r="C6" s="248" t="n"/>
-      <c r="D6" s="248" t="n"/>
-      <c r="E6" s="248" t="n"/>
-      <c r="F6" s="248" t="n"/>
-      <c r="G6" s="248" t="n"/>
-      <c r="H6" s="248" t="n"/>
-      <c r="I6" s="248" t="n"/>
-      <c r="J6" s="248" t="n"/>
-      <c r="K6" s="248" t="n"/>
-      <c r="L6" s="248" t="n"/>
-      <c r="M6" s="248" t="n"/>
-      <c r="N6" s="248" t="n"/>
-      <c r="O6" s="248" t="n"/>
-      <c r="P6" s="248" t="n"/>
-      <c r="Q6" s="248" t="n"/>
-      <c r="R6" s="248" t="n"/>
-      <c r="S6" s="248" t="n"/>
-      <c r="T6" s="248" t="n"/>
-      <c r="U6" s="248" t="n"/>
-      <c r="V6" s="248" t="n"/>
-      <c r="W6" s="248" t="n"/>
-      <c r="X6" s="248" t="n"/>
-      <c r="Y6" s="248" t="n"/>
-      <c r="Z6" s="248" t="n"/>
-      <c r="AA6" s="248" t="n"/>
-      <c r="AB6" s="248" t="n"/>
-      <c r="AC6" s="248" t="n"/>
-      <c r="AD6" s="248" t="n"/>
-      <c r="AE6" s="248" t="n"/>
-      <c r="AF6" s="248" t="n"/>
-      <c r="AG6" s="248" t="n"/>
-      <c r="AH6" s="248" t="n"/>
-      <c r="AI6" s="248" t="n"/>
-      <c r="AJ6" s="248" t="n"/>
-      <c r="AK6" s="248" t="n"/>
-      <c r="AL6" s="248" t="n"/>
-      <c r="AM6" s="248" t="n"/>
-      <c r="AN6" s="248" t="n"/>
-      <c r="AO6" s="248" t="n"/>
-      <c r="AP6" s="248" t="n"/>
-      <c r="AQ6" s="248" t="n"/>
-      <c r="AR6" s="248" t="n"/>
-      <c r="AS6" s="248" t="n"/>
-      <c r="AT6" s="248" t="n"/>
-      <c r="AU6" s="248" t="n"/>
-      <c r="AV6" s="248" t="n"/>
-      <c r="AW6" s="248" t="n"/>
-      <c r="AX6" s="248" t="n"/>
-      <c r="AY6" s="248" t="n"/>
-      <c r="AZ6" s="248" t="n"/>
-      <c r="BA6" s="248" t="n"/>
-      <c r="BB6" s="248" t="n"/>
-      <c r="BC6" s="248" t="n"/>
-      <c r="BD6" s="248" t="n"/>
-      <c r="BE6" s="248" t="n"/>
-      <c r="BF6" s="248" t="n"/>
-      <c r="BG6" s="248" t="n"/>
-      <c r="BH6" s="248" t="n"/>
-      <c r="BI6" s="248" t="n"/>
-      <c r="BJ6" s="248" t="n"/>
-      <c r="BK6" s="248" t="n"/>
-      <c r="BL6" s="248" t="n"/>
-      <c r="BM6" s="248" t="n"/>
-      <c r="BN6" s="248" t="n"/>
-      <c r="BO6" s="248" t="n"/>
-      <c r="BP6" s="248" t="n"/>
-      <c r="BQ6" s="248" t="n"/>
-      <c r="BR6" s="248" t="n"/>
-      <c r="BS6" s="248" t="n"/>
-      <c r="BT6" s="248" t="n"/>
-      <c r="BU6" s="248" t="n"/>
-      <c r="BV6" s="248" t="n"/>
-      <c r="BW6" s="248" t="n"/>
-      <c r="BX6" s="248" t="n"/>
-      <c r="BY6" s="248" t="n"/>
-      <c r="BZ6" s="248" t="n"/>
-      <c r="CA6" s="248" t="n"/>
-      <c r="CB6" s="248" t="n"/>
-      <c r="CC6" s="248" t="n"/>
-      <c r="CD6" s="248" t="n"/>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="22" t="n"/>
-      <c r="BE7" s="22" t="n"/>
-      <c r="BF7" s="22" t="n"/>
-      <c r="BG7" s="22" t="n"/>
-      <c r="BH7" s="22" t="n"/>
-      <c r="BI7" s="22" t="n"/>
-      <c r="BJ7" s="22" t="n"/>
-      <c r="BK7" s="22" t="n"/>
-      <c r="BL7" s="22" t="n"/>
-      <c r="BM7" s="22" t="n"/>
-      <c r="BN7" s="22" t="n"/>
-      <c r="BO7" s="22" t="n"/>
-      <c r="BP7" s="22" t="n"/>
-      <c r="BQ7" s="22" t="n"/>
-      <c r="BR7" s="22" t="n"/>
-      <c r="BS7" s="22" t="n"/>
-      <c r="BT7" s="22" t="n"/>
-      <c r="BU7" s="22" t="n"/>
-      <c r="BV7" s="22" t="n"/>
-      <c r="BW7" s="22" t="n"/>
-      <c r="BX7" s="22" t="n"/>
-      <c r="BY7" s="22" t="n"/>
-      <c r="BZ7" s="22" t="n"/>
-      <c r="CA7" s="22" t="n"/>
-      <c r="CB7" s="22" t="n"/>
-      <c r="CC7" s="22" t="n"/>
-      <c r="CD7" s="23" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="336" t="inlineStr">
-        <is>
-          <t>Source Links</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="43" t="inlineStr">
-        <is>
-          <t>M365 evidence stays SSOT; workbook captures the formal study / gate / decision record while annex rules, criteria dictionaries and authority matrices are referenced, not re-keyed.</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="6" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="6" t="n"/>
-      <c r="V8" s="6" t="n"/>
-      <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="6" t="n"/>
-      <c r="AC8" s="6" t="n"/>
-      <c r="AD8" s="6" t="n"/>
-      <c r="AE8" s="6" t="n"/>
-      <c r="AF8" s="6" t="n"/>
-      <c r="AG8" s="6" t="n"/>
-      <c r="AH8" s="6" t="n"/>
-      <c r="AI8" s="6" t="n"/>
-      <c r="AJ8" s="6" t="n"/>
-      <c r="AK8" s="6" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="6" t="n"/>
-      <c r="AN8" s="6" t="n"/>
-      <c r="AO8" s="7" t="n"/>
-      <c r="AP8" s="367" t="inlineStr"/>
-      <c r="AQ8" s="6" t="n"/>
-      <c r="AR8" s="6" t="n"/>
-      <c r="AS8" s="6" t="n"/>
-      <c r="AT8" s="6" t="n"/>
-      <c r="AU8" s="6" t="n"/>
-      <c r="AV8" s="6" t="n"/>
-      <c r="AW8" s="6" t="n"/>
-      <c r="AX8" s="6" t="n"/>
-      <c r="AY8" s="6" t="n"/>
-      <c r="AZ8" s="6" t="n"/>
-      <c r="BA8" s="6" t="n"/>
-      <c r="BB8" s="6" t="n"/>
-      <c r="BC8" s="7" t="n"/>
-      <c r="BD8" s="368" t="inlineStr"/>
-      <c r="BE8" s="6" t="n"/>
-      <c r="BF8" s="6" t="n"/>
-      <c r="BG8" s="6" t="n"/>
-      <c r="BH8" s="6" t="n"/>
-      <c r="BI8" s="6" t="n"/>
-      <c r="BJ8" s="6" t="n"/>
-      <c r="BK8" s="6" t="n"/>
-      <c r="BL8" s="6" t="n"/>
-      <c r="BM8" s="6" t="n"/>
-      <c r="BN8" s="6" t="n"/>
-      <c r="BO8" s="6" t="n"/>
-      <c r="BP8" s="6" t="n"/>
-      <c r="BQ8" s="6" t="n"/>
-      <c r="BR8" s="6" t="n"/>
-      <c r="BS8" s="6" t="n"/>
-      <c r="BT8" s="6" t="n"/>
-      <c r="BU8" s="6" t="n"/>
-      <c r="BV8" s="6" t="n"/>
-      <c r="BW8" s="6" t="n"/>
-      <c r="BX8" s="6" t="n"/>
-      <c r="BY8" s="6" t="n"/>
-      <c r="BZ8" s="6" t="n"/>
-      <c r="CA8" s="6" t="n"/>
-      <c r="CB8" s="6" t="n"/>
-      <c r="CC8" s="6" t="n"/>
-      <c r="CD8" s="9" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="344" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="17" t="n"/>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="52" t="n"/>
-      <c r="O9" s="369" t="inlineStr">
-        <is>
-          <t>Reference / code-support sheet for controlled vocabulary or approved code mappings.</t>
-        </is>
-      </c>
-      <c r="P9" s="17" t="n"/>
-      <c r="Q9" s="17" t="n"/>
-      <c r="R9" s="17" t="n"/>
-      <c r="S9" s="17" t="n"/>
-      <c r="T9" s="17" t="n"/>
-      <c r="U9" s="17" t="n"/>
-      <c r="V9" s="17" t="n"/>
-      <c r="W9" s="17" t="n"/>
-      <c r="X9" s="17" t="n"/>
-      <c r="Y9" s="17" t="n"/>
-      <c r="Z9" s="17" t="n"/>
-      <c r="AA9" s="17" t="n"/>
-      <c r="AB9" s="17" t="n"/>
-      <c r="AC9" s="17" t="n"/>
-      <c r="AD9" s="17" t="n"/>
-      <c r="AE9" s="17" t="n"/>
-      <c r="AF9" s="17" t="n"/>
-      <c r="AG9" s="17" t="n"/>
-      <c r="AH9" s="17" t="n"/>
-      <c r="AI9" s="17" t="n"/>
-      <c r="AJ9" s="17" t="n"/>
-      <c r="AK9" s="17" t="n"/>
-      <c r="AL9" s="17" t="n"/>
-      <c r="AM9" s="17" t="n"/>
-      <c r="AN9" s="17" t="n"/>
-      <c r="AO9" s="52" t="n"/>
-      <c r="AP9" s="370" t="inlineStr"/>
-      <c r="AQ9" s="17" t="n"/>
-      <c r="AR9" s="17" t="n"/>
-      <c r="AS9" s="17" t="n"/>
-      <c r="AT9" s="17" t="n"/>
-      <c r="AU9" s="17" t="n"/>
-      <c r="AV9" s="17" t="n"/>
-      <c r="AW9" s="17" t="n"/>
-      <c r="AX9" s="17" t="n"/>
-      <c r="AY9" s="17" t="n"/>
-      <c r="AZ9" s="17" t="n"/>
-      <c r="BA9" s="17" t="n"/>
-      <c r="BB9" s="17" t="n"/>
-      <c r="BC9" s="52" t="n"/>
-      <c r="BD9" s="371" t="inlineStr"/>
-      <c r="BE9" s="17" t="n"/>
-      <c r="BF9" s="17" t="n"/>
-      <c r="BG9" s="17" t="n"/>
-      <c r="BH9" s="17" t="n"/>
-      <c r="BI9" s="17" t="n"/>
-      <c r="BJ9" s="17" t="n"/>
-      <c r="BK9" s="17" t="n"/>
-      <c r="BL9" s="17" t="n"/>
-      <c r="BM9" s="17" t="n"/>
-      <c r="BN9" s="17" t="n"/>
-      <c r="BO9" s="17" t="n"/>
-      <c r="BP9" s="17" t="n"/>
-      <c r="BQ9" s="17" t="n"/>
-      <c r="BR9" s="17" t="n"/>
-      <c r="BS9" s="17" t="n"/>
-      <c r="BT9" s="17" t="n"/>
-      <c r="BU9" s="17" t="n"/>
-      <c r="BV9" s="17" t="n"/>
-      <c r="BW9" s="17" t="n"/>
-      <c r="BX9" s="17" t="n"/>
-      <c r="BY9" s="17" t="n"/>
-      <c r="BZ9" s="17" t="n"/>
-      <c r="CA9" s="17" t="n"/>
-      <c r="CB9" s="17" t="n"/>
-      <c r="CC9" s="17" t="n"/>
-      <c r="CD9" s="18" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SUPPORT TABLE</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="22" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="22" t="n"/>
-      <c r="K10" s="22" t="n"/>
-      <c r="L10" s="22" t="n"/>
-      <c r="M10" s="22" t="n"/>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n"/>
-      <c r="P10" s="22" t="n"/>
-      <c r="Q10" s="22" t="n"/>
-      <c r="R10" s="22" t="n"/>
-      <c r="S10" s="22" t="n"/>
-      <c r="T10" s="22" t="n"/>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="22" t="n"/>
-      <c r="W10" s="22" t="n"/>
-      <c r="X10" s="22" t="n"/>
-      <c r="Y10" s="22" t="n"/>
-      <c r="Z10" s="22" t="n"/>
-      <c r="AA10" s="22" t="n"/>
-      <c r="AB10" s="22" t="n"/>
-      <c r="AC10" s="22" t="n"/>
-      <c r="AD10" s="22" t="n"/>
-      <c r="AE10" s="22" t="n"/>
-      <c r="AF10" s="22" t="n"/>
-      <c r="AG10" s="22" t="n"/>
-      <c r="AH10" s="22" t="n"/>
-      <c r="AI10" s="22" t="n"/>
-      <c r="AJ10" s="22" t="n"/>
-      <c r="AK10" s="22" t="n"/>
-      <c r="AL10" s="22" t="n"/>
-      <c r="AM10" s="22" t="n"/>
-      <c r="AN10" s="22" t="n"/>
-      <c r="AO10" s="22" t="n"/>
-      <c r="AP10" s="22" t="n"/>
-      <c r="AQ10" s="22" t="n"/>
-      <c r="AR10" s="22" t="n"/>
-      <c r="AS10" s="22" t="n"/>
-      <c r="AT10" s="22" t="n"/>
-      <c r="AU10" s="22" t="n"/>
-      <c r="AV10" s="22" t="n"/>
-      <c r="AW10" s="22" t="n"/>
-      <c r="AX10" s="22" t="n"/>
-      <c r="AY10" s="22" t="n"/>
-      <c r="AZ10" s="22" t="n"/>
-      <c r="BA10" s="22" t="n"/>
-      <c r="BB10" s="22" t="n"/>
-      <c r="BC10" s="22" t="n"/>
-      <c r="BD10" s="22" t="n"/>
-      <c r="BE10" s="22" t="n"/>
-      <c r="BF10" s="22" t="n"/>
-      <c r="BG10" s="22" t="n"/>
-      <c r="BH10" s="22" t="n"/>
-      <c r="BI10" s="22" t="n"/>
-      <c r="BJ10" s="22" t="n"/>
-      <c r="BK10" s="22" t="n"/>
-      <c r="BL10" s="22" t="n"/>
-      <c r="BM10" s="22" t="n"/>
-      <c r="BN10" s="22" t="n"/>
-      <c r="BO10" s="22" t="n"/>
-      <c r="BP10" s="22" t="n"/>
-      <c r="BQ10" s="22" t="n"/>
-      <c r="BR10" s="22" t="n"/>
-      <c r="BS10" s="22" t="n"/>
-      <c r="BT10" s="22" t="n"/>
-      <c r="BU10" s="22" t="n"/>
-      <c r="BV10" s="22" t="n"/>
-      <c r="BW10" s="22" t="n"/>
-      <c r="BX10" s="22" t="n"/>
-      <c r="BY10" s="22" t="n"/>
-      <c r="BZ10" s="22" t="n"/>
-      <c r="CA10" s="22" t="n"/>
-      <c r="CB10" s="22" t="n"/>
-      <c r="CC10" s="22" t="n"/>
-      <c r="CD10" s="23" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="7" t="n"/>
-      <c r="S11" s="351" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-      <c r="T11" s="6" t="n"/>
-      <c r="U11" s="6" t="n"/>
-      <c r="V11" s="6" t="n"/>
-      <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
-      <c r="AA11" s="6" t="n"/>
-      <c r="AB11" s="6" t="n"/>
-      <c r="AC11" s="6" t="n"/>
-      <c r="AD11" s="6" t="n"/>
-      <c r="AE11" s="6" t="n"/>
-      <c r="AF11" s="6" t="n"/>
-      <c r="AG11" s="6" t="n"/>
-      <c r="AH11" s="6" t="n"/>
-      <c r="AI11" s="7" t="n"/>
-      <c r="AJ11" s="351" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="AK11" s="6" t="n"/>
-      <c r="AL11" s="6" t="n"/>
-      <c r="AM11" s="6" t="n"/>
-      <c r="AN11" s="6" t="n"/>
-      <c r="AO11" s="6" t="n"/>
-      <c r="AP11" s="6" t="n"/>
-      <c r="AQ11" s="6" t="n"/>
-      <c r="AR11" s="6" t="n"/>
-      <c r="AS11" s="6" t="n"/>
-      <c r="AT11" s="6" t="n"/>
-      <c r="AU11" s="6" t="n"/>
-      <c r="AV11" s="6" t="n"/>
-      <c r="AW11" s="6" t="n"/>
-      <c r="AX11" s="6" t="n"/>
-      <c r="AY11" s="6" t="n"/>
-      <c r="AZ11" s="7" t="n"/>
-      <c r="BA11" s="352" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="BB11" s="6" t="n"/>
-      <c r="BC11" s="6" t="n"/>
-      <c r="BD11" s="6" t="n"/>
-      <c r="BE11" s="6" t="n"/>
-      <c r="BF11" s="6" t="n"/>
-      <c r="BG11" s="6" t="n"/>
-      <c r="BH11" s="6" t="n"/>
-      <c r="BI11" s="6" t="n"/>
-      <c r="BJ11" s="6" t="n"/>
-      <c r="BK11" s="6" t="n"/>
-      <c r="BL11" s="6" t="n"/>
-      <c r="BM11" s="6" t="n"/>
-      <c r="BN11" s="6" t="n"/>
-      <c r="BO11" s="6" t="n"/>
-      <c r="BP11" s="6" t="n"/>
-      <c r="BQ11" s="6" t="n"/>
-      <c r="BR11" s="6" t="n"/>
-      <c r="BS11" s="6" t="n"/>
-      <c r="BT11" s="6" t="n"/>
-      <c r="BU11" s="6" t="n"/>
-      <c r="BV11" s="6" t="n"/>
-      <c r="BW11" s="6" t="n"/>
-      <c r="BX11" s="6" t="n"/>
-      <c r="BY11" s="6" t="n"/>
-      <c r="BZ11" s="6" t="n"/>
-      <c r="CA11" s="6" t="n"/>
-      <c r="CB11" s="6" t="n"/>
-      <c r="CC11" s="6" t="n"/>
-      <c r="CD11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="353" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="7" t="n"/>
-      <c r="S12" s="25" t="n"/>
-      <c r="T12" s="26" t="n"/>
-      <c r="U12" s="26" t="n"/>
-      <c r="V12" s="26" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
-      <c r="Y12" s="26" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="26" t="n"/>
-      <c r="AB12" s="26" t="n"/>
-      <c r="AC12" s="26" t="n"/>
-      <c r="AD12" s="26" t="n"/>
-      <c r="AE12" s="26" t="n"/>
-      <c r="AF12" s="26" t="n"/>
-      <c r="AG12" s="26" t="n"/>
-      <c r="AH12" s="26" t="n"/>
-      <c r="AI12" s="27" t="n"/>
-      <c r="AJ12" s="25" t="n"/>
-      <c r="AK12" s="26" t="n"/>
-      <c r="AL12" s="26" t="n"/>
-      <c r="AM12" s="26" t="n"/>
-      <c r="AN12" s="26" t="n"/>
-      <c r="AO12" s="26" t="n"/>
-      <c r="AP12" s="26" t="n"/>
-      <c r="AQ12" s="26" t="n"/>
-      <c r="AR12" s="26" t="n"/>
-      <c r="AS12" s="26" t="n"/>
-      <c r="AT12" s="26" t="n"/>
-      <c r="AU12" s="26" t="n"/>
-      <c r="AV12" s="26" t="n"/>
-      <c r="AW12" s="26" t="n"/>
-      <c r="AX12" s="26" t="n"/>
-      <c r="AY12" s="26" t="n"/>
-      <c r="AZ12" s="27" t="n"/>
-      <c r="BA12" s="338" t="n"/>
-      <c r="BB12" s="26" t="n"/>
-      <c r="BC12" s="26" t="n"/>
-      <c r="BD12" s="26" t="n"/>
-      <c r="BE12" s="26" t="n"/>
-      <c r="BF12" s="26" t="n"/>
-      <c r="BG12" s="26" t="n"/>
-      <c r="BH12" s="26" t="n"/>
-      <c r="BI12" s="26" t="n"/>
-      <c r="BJ12" s="26" t="n"/>
-      <c r="BK12" s="26" t="n"/>
-      <c r="BL12" s="26" t="n"/>
-      <c r="BM12" s="26" t="n"/>
-      <c r="BN12" s="26" t="n"/>
-      <c r="BO12" s="26" t="n"/>
-      <c r="BP12" s="26" t="n"/>
-      <c r="BQ12" s="26" t="n"/>
-      <c r="BR12" s="26" t="n"/>
-      <c r="BS12" s="26" t="n"/>
-      <c r="BT12" s="26" t="n"/>
-      <c r="BU12" s="26" t="n"/>
-      <c r="BV12" s="26" t="n"/>
-      <c r="BW12" s="26" t="n"/>
-      <c r="BX12" s="26" t="n"/>
-      <c r="BY12" s="26" t="n"/>
-      <c r="BZ12" s="26" t="n"/>
-      <c r="CA12" s="26" t="n"/>
-      <c r="CB12" s="26" t="n"/>
-      <c r="CC12" s="26" t="n"/>
-      <c r="CD12" s="339" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="355" t="n"/>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="n"/>
-      <c r="I13" s="14" t="n"/>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="14" t="n"/>
-      <c r="N13" s="14" t="n"/>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="14" t="n"/>
-      <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="30" t="n"/>
-      <c r="S13" s="35" t="n"/>
-      <c r="T13" s="32" t="n"/>
-      <c r="U13" s="32" t="n"/>
-      <c r="V13" s="32" t="n"/>
-      <c r="W13" s="32" t="n"/>
-      <c r="X13" s="32" t="n"/>
-      <c r="Y13" s="32" t="n"/>
-      <c r="Z13" s="32" t="n"/>
-      <c r="AA13" s="32" t="n"/>
-      <c r="AB13" s="32" t="n"/>
-      <c r="AC13" s="32" t="n"/>
-      <c r="AD13" s="32" t="n"/>
-      <c r="AE13" s="32" t="n"/>
-      <c r="AF13" s="32" t="n"/>
-      <c r="AG13" s="32" t="n"/>
-      <c r="AH13" s="32" t="n"/>
-      <c r="AI13" s="33" t="n"/>
-      <c r="AJ13" s="35" t="n"/>
-      <c r="AK13" s="32" t="n"/>
-      <c r="AL13" s="32" t="n"/>
-      <c r="AM13" s="32" t="n"/>
-      <c r="AN13" s="32" t="n"/>
-      <c r="AO13" s="32" t="n"/>
-      <c r="AP13" s="32" t="n"/>
-      <c r="AQ13" s="32" t="n"/>
-      <c r="AR13" s="32" t="n"/>
-      <c r="AS13" s="32" t="n"/>
-      <c r="AT13" s="32" t="n"/>
-      <c r="AU13" s="32" t="n"/>
-      <c r="AV13" s="32" t="n"/>
-      <c r="AW13" s="32" t="n"/>
-      <c r="AX13" s="32" t="n"/>
-      <c r="AY13" s="32" t="n"/>
-      <c r="AZ13" s="33" t="n"/>
-      <c r="BA13" s="356" t="n"/>
-      <c r="BB13" s="32" t="n"/>
-      <c r="BC13" s="32" t="n"/>
-      <c r="BD13" s="32" t="n"/>
-      <c r="BE13" s="32" t="n"/>
-      <c r="BF13" s="32" t="n"/>
-      <c r="BG13" s="32" t="n"/>
-      <c r="BH13" s="32" t="n"/>
-      <c r="BI13" s="32" t="n"/>
-      <c r="BJ13" s="32" t="n"/>
-      <c r="BK13" s="32" t="n"/>
-      <c r="BL13" s="32" t="n"/>
-      <c r="BM13" s="32" t="n"/>
-      <c r="BN13" s="32" t="n"/>
-      <c r="BO13" s="32" t="n"/>
-      <c r="BP13" s="32" t="n"/>
-      <c r="BQ13" s="32" t="n"/>
-      <c r="BR13" s="32" t="n"/>
-      <c r="BS13" s="32" t="n"/>
-      <c r="BT13" s="32" t="n"/>
-      <c r="BU13" s="32" t="n"/>
-      <c r="BV13" s="32" t="n"/>
-      <c r="BW13" s="32" t="n"/>
-      <c r="BX13" s="32" t="n"/>
-      <c r="BY13" s="32" t="n"/>
-      <c r="BZ13" s="32" t="n"/>
-      <c r="CA13" s="32" t="n"/>
-      <c r="CB13" s="32" t="n"/>
-      <c r="CC13" s="32" t="n"/>
-      <c r="CD13" s="343" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="355" t="n"/>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="n"/>
-      <c r="I14" s="14" t="n"/>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="14" t="n"/>
-      <c r="N14" s="14" t="n"/>
-      <c r="O14" s="14" t="n"/>
-      <c r="P14" s="14" t="n"/>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="30" t="n"/>
-      <c r="S14" s="31" t="n"/>
-      <c r="T14" s="32" t="n"/>
-      <c r="U14" s="32" t="n"/>
-      <c r="V14" s="32" t="n"/>
-      <c r="W14" s="32" t="n"/>
-      <c r="X14" s="32" t="n"/>
-      <c r="Y14" s="32" t="n"/>
-      <c r="Z14" s="32" t="n"/>
-      <c r="AA14" s="32" t="n"/>
-      <c r="AB14" s="32" t="n"/>
-      <c r="AC14" s="32" t="n"/>
-      <c r="AD14" s="32" t="n"/>
-      <c r="AE14" s="32" t="n"/>
-      <c r="AF14" s="32" t="n"/>
-      <c r="AG14" s="32" t="n"/>
-      <c r="AH14" s="32" t="n"/>
-      <c r="AI14" s="33" t="n"/>
-      <c r="AJ14" s="31" t="n"/>
-      <c r="AK14" s="32" t="n"/>
-      <c r="AL14" s="32" t="n"/>
-      <c r="AM14" s="32" t="n"/>
-      <c r="AN14" s="32" t="n"/>
-      <c r="AO14" s="32" t="n"/>
-      <c r="AP14" s="32" t="n"/>
-      <c r="AQ14" s="32" t="n"/>
-      <c r="AR14" s="32" t="n"/>
-      <c r="AS14" s="32" t="n"/>
-      <c r="AT14" s="32" t="n"/>
-      <c r="AU14" s="32" t="n"/>
-      <c r="AV14" s="32" t="n"/>
-      <c r="AW14" s="32" t="n"/>
-      <c r="AX14" s="32" t="n"/>
-      <c r="AY14" s="32" t="n"/>
-      <c r="AZ14" s="33" t="n"/>
-      <c r="BA14" s="342" t="n"/>
-      <c r="BB14" s="32" t="n"/>
-      <c r="BC14" s="32" t="n"/>
-      <c r="BD14" s="32" t="n"/>
-      <c r="BE14" s="32" t="n"/>
-      <c r="BF14" s="32" t="n"/>
-      <c r="BG14" s="32" t="n"/>
-      <c r="BH14" s="32" t="n"/>
-      <c r="BI14" s="32" t="n"/>
-      <c r="BJ14" s="32" t="n"/>
-      <c r="BK14" s="32" t="n"/>
-      <c r="BL14" s="32" t="n"/>
-      <c r="BM14" s="32" t="n"/>
-      <c r="BN14" s="32" t="n"/>
-      <c r="BO14" s="32" t="n"/>
-      <c r="BP14" s="32" t="n"/>
-      <c r="BQ14" s="32" t="n"/>
-      <c r="BR14" s="32" t="n"/>
-      <c r="BS14" s="32" t="n"/>
-      <c r="BT14" s="32" t="n"/>
-      <c r="BU14" s="32" t="n"/>
-      <c r="BV14" s="32" t="n"/>
-      <c r="BW14" s="32" t="n"/>
-      <c r="BX14" s="32" t="n"/>
-      <c r="BY14" s="32" t="n"/>
-      <c r="BZ14" s="32" t="n"/>
-      <c r="CA14" s="32" t="n"/>
-      <c r="CB14" s="32" t="n"/>
-      <c r="CC14" s="32" t="n"/>
-      <c r="CD14" s="343" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="355" t="n"/>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="14" t="n"/>
-      <c r="I15" s="14" t="n"/>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="14" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="14" t="n"/>
-      <c r="N15" s="14" t="n"/>
-      <c r="O15" s="14" t="n"/>
-      <c r="P15" s="14" t="n"/>
-      <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="30" t="n"/>
-      <c r="S15" s="35" t="n"/>
-      <c r="T15" s="32" t="n"/>
-      <c r="U15" s="32" t="n"/>
-      <c r="V15" s="32" t="n"/>
-      <c r="W15" s="32" t="n"/>
-      <c r="X15" s="32" t="n"/>
-      <c r="Y15" s="32" t="n"/>
-      <c r="Z15" s="32" t="n"/>
-      <c r="AA15" s="32" t="n"/>
-      <c r="AB15" s="32" t="n"/>
-      <c r="AC15" s="32" t="n"/>
-      <c r="AD15" s="32" t="n"/>
-      <c r="AE15" s="32" t="n"/>
-      <c r="AF15" s="32" t="n"/>
-      <c r="AG15" s="32" t="n"/>
-      <c r="AH15" s="32" t="n"/>
-      <c r="AI15" s="33" t="n"/>
-      <c r="AJ15" s="35" t="n"/>
-      <c r="AK15" s="32" t="n"/>
-      <c r="AL15" s="32" t="n"/>
-      <c r="AM15" s="32" t="n"/>
-      <c r="AN15" s="32" t="n"/>
-      <c r="AO15" s="32" t="n"/>
-      <c r="AP15" s="32" t="n"/>
-      <c r="AQ15" s="32" t="n"/>
-      <c r="AR15" s="32" t="n"/>
-      <c r="AS15" s="32" t="n"/>
-      <c r="AT15" s="32" t="n"/>
-      <c r="AU15" s="32" t="n"/>
-      <c r="AV15" s="32" t="n"/>
-      <c r="AW15" s="32" t="n"/>
-      <c r="AX15" s="32" t="n"/>
-      <c r="AY15" s="32" t="n"/>
-      <c r="AZ15" s="33" t="n"/>
-      <c r="BA15" s="356" t="n"/>
-      <c r="BB15" s="32" t="n"/>
-      <c r="BC15" s="32" t="n"/>
-      <c r="BD15" s="32" t="n"/>
-      <c r="BE15" s="32" t="n"/>
-      <c r="BF15" s="32" t="n"/>
-      <c r="BG15" s="32" t="n"/>
-      <c r="BH15" s="32" t="n"/>
-      <c r="BI15" s="32" t="n"/>
-      <c r="BJ15" s="32" t="n"/>
-      <c r="BK15" s="32" t="n"/>
-      <c r="BL15" s="32" t="n"/>
-      <c r="BM15" s="32" t="n"/>
-      <c r="BN15" s="32" t="n"/>
-      <c r="BO15" s="32" t="n"/>
-      <c r="BP15" s="32" t="n"/>
-      <c r="BQ15" s="32" t="n"/>
-      <c r="BR15" s="32" t="n"/>
-      <c r="BS15" s="32" t="n"/>
-      <c r="BT15" s="32" t="n"/>
-      <c r="BU15" s="32" t="n"/>
-      <c r="BV15" s="32" t="n"/>
-      <c r="BW15" s="32" t="n"/>
-      <c r="BX15" s="32" t="n"/>
-      <c r="BY15" s="32" t="n"/>
-      <c r="BZ15" s="32" t="n"/>
-      <c r="CA15" s="32" t="n"/>
-      <c r="CB15" s="32" t="n"/>
-      <c r="CC15" s="32" t="n"/>
-      <c r="CD15" s="343" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="355" t="n"/>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="30" t="n"/>
-      <c r="S16" s="31" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
-      <c r="W16" s="32" t="n"/>
-      <c r="X16" s="32" t="n"/>
-      <c r="Y16" s="32" t="n"/>
-      <c r="Z16" s="32" t="n"/>
-      <c r="AA16" s="32" t="n"/>
-      <c r="AB16" s="32" t="n"/>
-      <c r="AC16" s="32" t="n"/>
-      <c r="AD16" s="32" t="n"/>
-      <c r="AE16" s="32" t="n"/>
-      <c r="AF16" s="32" t="n"/>
-      <c r="AG16" s="32" t="n"/>
-      <c r="AH16" s="32" t="n"/>
-      <c r="AI16" s="33" t="n"/>
-      <c r="AJ16" s="31" t="n"/>
-      <c r="AK16" s="32" t="n"/>
-      <c r="AL16" s="32" t="n"/>
-      <c r="AM16" s="32" t="n"/>
-      <c r="AN16" s="32" t="n"/>
-      <c r="AO16" s="32" t="n"/>
-      <c r="AP16" s="32" t="n"/>
-      <c r="AQ16" s="32" t="n"/>
-      <c r="AR16" s="32" t="n"/>
-      <c r="AS16" s="32" t="n"/>
-      <c r="AT16" s="32" t="n"/>
-      <c r="AU16" s="32" t="n"/>
-      <c r="AV16" s="32" t="n"/>
-      <c r="AW16" s="32" t="n"/>
-      <c r="AX16" s="32" t="n"/>
-      <c r="AY16" s="32" t="n"/>
-      <c r="AZ16" s="33" t="n"/>
-      <c r="BA16" s="342" t="n"/>
-      <c r="BB16" s="32" t="n"/>
-      <c r="BC16" s="32" t="n"/>
-      <c r="BD16" s="32" t="n"/>
-      <c r="BE16" s="32" t="n"/>
-      <c r="BF16" s="32" t="n"/>
-      <c r="BG16" s="32" t="n"/>
-      <c r="BH16" s="32" t="n"/>
-      <c r="BI16" s="32" t="n"/>
-      <c r="BJ16" s="32" t="n"/>
-      <c r="BK16" s="32" t="n"/>
-      <c r="BL16" s="32" t="n"/>
-      <c r="BM16" s="32" t="n"/>
-      <c r="BN16" s="32" t="n"/>
-      <c r="BO16" s="32" t="n"/>
-      <c r="BP16" s="32" t="n"/>
-      <c r="BQ16" s="32" t="n"/>
-      <c r="BR16" s="32" t="n"/>
-      <c r="BS16" s="32" t="n"/>
-      <c r="BT16" s="32" t="n"/>
-      <c r="BU16" s="32" t="n"/>
-      <c r="BV16" s="32" t="n"/>
-      <c r="BW16" s="32" t="n"/>
-      <c r="BX16" s="32" t="n"/>
-      <c r="BY16" s="32" t="n"/>
-      <c r="BZ16" s="32" t="n"/>
-      <c r="CA16" s="32" t="n"/>
-      <c r="CB16" s="32" t="n"/>
-      <c r="CC16" s="32" t="n"/>
-      <c r="CD16" s="343" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="357" t="n"/>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="17" t="n"/>
-      <c r="L17" s="17" t="n"/>
-      <c r="M17" s="17" t="n"/>
-      <c r="N17" s="17" t="n"/>
-      <c r="O17" s="17" t="n"/>
-      <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="17" t="n"/>
-      <c r="R17" s="52" t="n"/>
-      <c r="S17" s="358" t="n"/>
-      <c r="T17" s="346" t="n"/>
-      <c r="U17" s="346" t="n"/>
-      <c r="V17" s="346" t="n"/>
-      <c r="W17" s="346" t="n"/>
-      <c r="X17" s="346" t="n"/>
-      <c r="Y17" s="346" t="n"/>
-      <c r="Z17" s="346" t="n"/>
-      <c r="AA17" s="346" t="n"/>
-      <c r="AB17" s="346" t="n"/>
-      <c r="AC17" s="346" t="n"/>
-      <c r="AD17" s="346" t="n"/>
-      <c r="AE17" s="346" t="n"/>
-      <c r="AF17" s="346" t="n"/>
-      <c r="AG17" s="346" t="n"/>
-      <c r="AH17" s="346" t="n"/>
-      <c r="AI17" s="347" t="n"/>
-      <c r="AJ17" s="358" t="n"/>
-      <c r="AK17" s="346" t="n"/>
-      <c r="AL17" s="346" t="n"/>
-      <c r="AM17" s="346" t="n"/>
-      <c r="AN17" s="346" t="n"/>
-      <c r="AO17" s="346" t="n"/>
-      <c r="AP17" s="346" t="n"/>
-      <c r="AQ17" s="346" t="n"/>
-      <c r="AR17" s="346" t="n"/>
-      <c r="AS17" s="346" t="n"/>
-      <c r="AT17" s="346" t="n"/>
-      <c r="AU17" s="346" t="n"/>
-      <c r="AV17" s="346" t="n"/>
-      <c r="AW17" s="346" t="n"/>
-      <c r="AX17" s="346" t="n"/>
-      <c r="AY17" s="346" t="n"/>
-      <c r="AZ17" s="347" t="n"/>
-      <c r="BA17" s="360" t="n"/>
-      <c r="BB17" s="346" t="n"/>
-      <c r="BC17" s="346" t="n"/>
-      <c r="BD17" s="346" t="n"/>
-      <c r="BE17" s="346" t="n"/>
-      <c r="BF17" s="346" t="n"/>
-      <c r="BG17" s="346" t="n"/>
-      <c r="BH17" s="346" t="n"/>
-      <c r="BI17" s="346" t="n"/>
-      <c r="BJ17" s="346" t="n"/>
-      <c r="BK17" s="346" t="n"/>
-      <c r="BL17" s="346" t="n"/>
-      <c r="BM17" s="346" t="n"/>
-      <c r="BN17" s="346" t="n"/>
-      <c r="BO17" s="346" t="n"/>
-      <c r="BP17" s="346" t="n"/>
-      <c r="BQ17" s="346" t="n"/>
-      <c r="BR17" s="346" t="n"/>
-      <c r="BS17" s="346" t="n"/>
-      <c r="BT17" s="346" t="n"/>
-      <c r="BU17" s="346" t="n"/>
-      <c r="BV17" s="346" t="n"/>
-      <c r="BW17" s="346" t="n"/>
-      <c r="BX17" s="346" t="n"/>
-      <c r="BY17" s="346" t="n"/>
-      <c r="BZ17" s="346" t="n"/>
-      <c r="CA17" s="346" t="n"/>
-      <c r="CB17" s="346" t="n"/>
-      <c r="CC17" s="346" t="n"/>
-      <c r="CD17" s="350" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="335" t="inlineStr">
-        <is>
-          <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
-        </is>
-      </c>
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="22" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="22" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
-      <c r="J18" s="22" t="n"/>
-      <c r="K18" s="22" t="n"/>
-      <c r="L18" s="22" t="n"/>
-      <c r="M18" s="22" t="n"/>
-      <c r="N18" s="22" t="n"/>
-      <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
-      <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="22" t="n"/>
-      <c r="S18" s="22" t="n"/>
-      <c r="T18" s="22" t="n"/>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="22" t="n"/>
-      <c r="W18" s="22" t="n"/>
-      <c r="X18" s="22" t="n"/>
-      <c r="Y18" s="22" t="n"/>
-      <c r="Z18" s="22" t="n"/>
-      <c r="AA18" s="22" t="n"/>
-      <c r="AB18" s="22" t="n"/>
-      <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="22" t="n"/>
-      <c r="AE18" s="22" t="n"/>
-      <c r="AF18" s="22" t="n"/>
-      <c r="AG18" s="22" t="n"/>
-      <c r="AH18" s="22" t="n"/>
-      <c r="AI18" s="22" t="n"/>
-      <c r="AJ18" s="22" t="n"/>
-      <c r="AK18" s="22" t="n"/>
-      <c r="AL18" s="22" t="n"/>
-      <c r="AM18" s="22" t="n"/>
-      <c r="AN18" s="22" t="n"/>
-      <c r="AO18" s="22" t="n"/>
-      <c r="AP18" s="22" t="n"/>
-      <c r="AQ18" s="22" t="n"/>
-      <c r="AR18" s="22" t="n"/>
-      <c r="AS18" s="22" t="n"/>
-      <c r="AT18" s="22" t="n"/>
-      <c r="AU18" s="22" t="n"/>
-      <c r="AV18" s="22" t="n"/>
-      <c r="AW18" s="22" t="n"/>
-      <c r="AX18" s="22" t="n"/>
-      <c r="AY18" s="22" t="n"/>
-      <c r="AZ18" s="22" t="n"/>
-      <c r="BA18" s="22" t="n"/>
-      <c r="BB18" s="22" t="n"/>
-      <c r="BC18" s="22" t="n"/>
-      <c r="BD18" s="22" t="n"/>
-      <c r="BE18" s="22" t="n"/>
-      <c r="BF18" s="22" t="n"/>
-      <c r="BG18" s="22" t="n"/>
-      <c r="BH18" s="22" t="n"/>
-      <c r="BI18" s="22" t="n"/>
-      <c r="BJ18" s="22" t="n"/>
-      <c r="BK18" s="22" t="n"/>
-      <c r="BL18" s="22" t="n"/>
-      <c r="BM18" s="22" t="n"/>
-      <c r="BN18" s="22" t="n"/>
-      <c r="BO18" s="22" t="n"/>
-      <c r="BP18" s="22" t="n"/>
-      <c r="BQ18" s="22" t="n"/>
-      <c r="BR18" s="22" t="n"/>
-      <c r="BS18" s="22" t="n"/>
-      <c r="BT18" s="22" t="n"/>
-      <c r="BU18" s="22" t="n"/>
-      <c r="BV18" s="22" t="n"/>
-      <c r="BW18" s="22" t="n"/>
-      <c r="BX18" s="22" t="n"/>
-      <c r="BY18" s="22" t="n"/>
-      <c r="BZ18" s="22" t="n"/>
-      <c r="CA18" s="22" t="n"/>
-      <c r="CB18" s="22" t="n"/>
-      <c r="CC18" s="22" t="n"/>
-      <c r="CD18" s="23" t="n"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="53">
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="O9:AO9"/>
-    <mergeCell ref="Q1:BJ3"/>
-    <mergeCell ref="Q4:BJ4"/>
-    <mergeCell ref="BS4:CD4"/>
-    <mergeCell ref="A7:CD7"/>
-    <mergeCell ref="A16:R16"/>
-    <mergeCell ref="BD9:CD9"/>
-    <mergeCell ref="BA17:CD17"/>
-    <mergeCell ref="S16:AI16"/>
-    <mergeCell ref="BS1:CD1"/>
-    <mergeCell ref="BD8:CD8"/>
-    <mergeCell ref="S12:AI12"/>
-    <mergeCell ref="AJ12:AZ12"/>
-    <mergeCell ref="AJ11:AZ11"/>
-    <mergeCell ref="A12:R12"/>
-    <mergeCell ref="BA13:CD13"/>
-    <mergeCell ref="A18:CD18"/>
-    <mergeCell ref="AP9:BC9"/>
-    <mergeCell ref="AJ14:AZ14"/>
-    <mergeCell ref="AP8:BC8"/>
-    <mergeCell ref="S17:AI17"/>
-    <mergeCell ref="AJ17:AZ17"/>
-    <mergeCell ref="S11:AI11"/>
-    <mergeCell ref="A14:R14"/>
-    <mergeCell ref="BA15:CD15"/>
-    <mergeCell ref="A17:R17"/>
-    <mergeCell ref="S14:AI14"/>
-    <mergeCell ref="BA14:CD14"/>
-    <mergeCell ref="S13:AI13"/>
-    <mergeCell ref="AJ13:AZ13"/>
-    <mergeCell ref="BK4:BR4"/>
-    <mergeCell ref="BS2:CD2"/>
-    <mergeCell ref="O8:AO8"/>
-    <mergeCell ref="BK3:BR3"/>
-    <mergeCell ref="A10:CD10"/>
-    <mergeCell ref="A13:R13"/>
-    <mergeCell ref="S15:AI15"/>
-    <mergeCell ref="AJ15:AZ15"/>
-    <mergeCell ref="BA16:CD16"/>
-    <mergeCell ref="BK5:BR5"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A1:P5"/>
-    <mergeCell ref="BS3:CD3"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="BA12:CD12"/>
-    <mergeCell ref="BK2:BR2"/>
-    <mergeCell ref="BK1:BR1"/>
-    <mergeCell ref="BA11:CD11"/>
-    <mergeCell ref="AJ16:AZ16"/>
-    <mergeCell ref="Q5:BJ5"/>
-    <mergeCell ref="BS5:CD5"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;"Segoe UI"&amp;7 FRM-132  ·  Rev.01  ·  HESEM Engineering — PRECISION  ·  Page &amp;P of &amp;N  ·  Printed: &amp;D</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10718,7 +9126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -21,710 +21,6 @@
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" calcOnSave="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
-  <si>
-    <t>  1. CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. ACTIVE TABLE / MATRIX</t>
-  </si>
-  <si>
-    <t>  3. REVIEW / DECISION</t>
-  </si>
-  <si>
-    <t>  REFERENCE / SOURCE CONTEXT</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLE</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$14)+1</t>
-  </si>
-  <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>ACCESS</t>
-  </si>
-  <si>
-    <t>ACCESS_ACTION_TYPE</t>
-  </si>
-  <si>
-    <t>ADJUST</t>
-  </si>
-  <si>
-    <t>ADMIN</t>
-  </si>
-  <si>
-    <t>ALL HANDS</t>
-  </si>
-  <si>
-    <t>ANNEX</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>APPROVER</t>
-  </si>
-  <si>
-    <t>ATTENDANCE_STATUS</t>
-  </si>
-  <si>
-    <t>AUDIENCE_CLASS</t>
-  </si>
-  <si>
-    <t>AUDIT_FINDING_SEVERITY</t>
-  </si>
-  <si>
-    <t>AUTHORITY_ROLE</t>
-  </si>
-  <si>
-    <t>AUTHORIZATION_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZED</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Action ID</t>
-  </si>
-  <si>
-    <t>Action Plan</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>BACKUP_FLAG</t>
-  </si>
-  <si>
-    <t>Boundary / SoR</t>
-  </si>
-  <si>
-    <t>CHANGE</t>
-  </si>
-  <si>
-    <t>CHANGE_PRIORITY</t>
-  </si>
-  <si>
-    <t>CHANGE_TYPE</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>COMMERCIAL_REFERENCE</t>
-  </si>
-  <si>
-    <t>COMM_CHANNEL</t>
-  </si>
-  <si>
-    <t>COMPETENCY_LEVEL</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CONFIGURATION</t>
-  </si>
-  <si>
-    <t>CONTAINED</t>
-  </si>
-  <si>
-    <t>CONTEXT_CLASS</t>
-  </si>
-  <si>
-    <t>CONTRACT</t>
-  </si>
-  <si>
-    <t>CONTRACT REVIEW</t>
-  </si>
-  <si>
-    <t>CONTRIBUTOR</t>
-  </si>
-  <si>
-    <t>CONTROL_METHOD</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>CREATE</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Cause</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Current Controls</t>
-  </si>
-  <si>
-    <t>DAILY</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DEPT</t>
-  </si>
-  <si>
-    <t>DETECTION</t>
-  </si>
-  <si>
-    <t>DIMENSIONAL</t>
-  </si>
-  <si>
-    <t>DOCUMENT</t>
-  </si>
-  <si>
-    <t>DOC_STATUS</t>
-  </si>
-  <si>
-    <t>DOC_TYPE</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Department / Owner</t>
-  </si>
-  <si>
-    <t>Detection</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>EACH LOT</t>
-  </si>
-  <si>
-    <t>EFFECTIVE</t>
-  </si>
-  <si>
-    <t>EMAIL</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>ESCALATE</t>
-  </si>
-  <si>
-    <t>ESCALATED</t>
-  </si>
-  <si>
-    <t>ESCALATION</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Effect of Failure</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Excel Table — PFMEA rows with frozen header and filters</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>FIRST ARTICLE</t>
-  </si>
-  <si>
-    <t>FIRST OFF</t>
-  </si>
-  <si>
-    <t>FIRST PIECE</t>
-  </si>
-  <si>
-    <t>FMEA_RANK</t>
-  </si>
-  <si>
-    <t>FORM</t>
-  </si>
-  <si>
-    <t>FRM-132</t>
-  </si>
-  <si>
-    <t>FUNCTION</t>
-  </si>
-  <si>
-    <t>FUNCTIONAL</t>
-  </si>
-  <si>
-    <t>Failure Mode</t>
-  </si>
-  <si>
-    <t>Failure-mode logic only; convert controls into FRM-133 and downstream release / inspection forms.</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>GATE</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HOURLY</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>IMPACT_LEVEL</t>
-  </si>
-  <si>
-    <t>IMPACT_SCOPE</t>
-  </si>
-  <si>
-    <t>IN PROCESS</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>IN-PROCESS</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Issue or Item</t>
-  </si>
-  <si>
-    <t>KPI-COST</t>
-  </si>
-  <si>
-    <t>KPI-DELIVERY</t>
-  </si>
-  <si>
-    <t>KPI-QUALITY</t>
-  </si>
-  <si>
-    <t>KPI-SAFETY</t>
-  </si>
-  <si>
-    <t>KPI-TRAINING</t>
-  </si>
-  <si>
-    <t>KPI_OWNER_SET</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>LESSON_CLASS</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>MAJOR</t>
-  </si>
-  <si>
-    <t>MANAGEMENT</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MEETING</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MINOR</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>NOT AUTHORIZED</t>
-  </si>
-  <si>
-    <t>NOT TRAINED</t>
-  </si>
-  <si>
-    <t>NOTICE</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: PFMEA entries shall stay process-step specific. Record failure mode, effect, cause, current controls, severity, occurrence, detection and action ownership with ranking discipline.</t>
-  </si>
-  <si>
-    <t>NOTICE: Use one row per action. Record issue, owner, due date, status and verification evidence; do not close actions without objective evidence.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>OBSERVED</t>
-  </si>
-  <si>
-    <t>OBSOLETE</t>
-  </si>
-  <si>
-    <t>ON HOLD</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OWNER</t>
-  </si>
-  <si>
-    <t>Occurrence</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PEOPLE</t>
-  </si>
-  <si>
-    <t>PESTLE</t>
-  </si>
-  <si>
-    <t>PFMEA ID</t>
-  </si>
-  <si>
-    <t>PFMEA LITE</t>
-  </si>
-  <si>
-    <t>PFMEA LITE — ACTION TRACKER</t>
-  </si>
-  <si>
-    <t>PFMEA LITE — CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PO</t>
-  </si>
-  <si>
-    <t>POLICY</t>
-  </si>
-  <si>
-    <t>PORTAL</t>
-  </si>
-  <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
-    <t>PREVENTION</t>
-  </si>
-  <si>
-    <t>PROCESS</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Part / Process / Operation</t>
-  </si>
-  <si>
-    <t>Per authority matrix</t>
-  </si>
-  <si>
-    <t>Post-Action Reassessment</t>
-  </si>
-  <si>
-    <t>Prepared By</t>
-  </si>
-  <si>
-    <t>Prepared Date</t>
-  </si>
-  <si>
-    <t>Priority or RPN</t>
-  </si>
-  <si>
-    <t>Process Function or Step</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>QMS</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
-  </si>
-  <si>
-    <t>QUOTE</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REACTION_CLASS</t>
-  </si>
-  <si>
-    <t>RECHECK</t>
-  </si>
-  <si>
-    <t>RECORD</t>
-  </si>
-  <si>
-    <t>RECOVERING</t>
-  </si>
-  <si>
-    <t>RECOVERY_STATUS</t>
-  </si>
-  <si>
-    <t>REGULATORY</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>REMOVE</t>
-  </si>
-  <si>
-    <t>REQUESTER</t>
-  </si>
-  <si>
-    <t>RESPONSE</t>
-  </si>
-  <si>
-    <t>RESTORED</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>REVIEWER</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>RISK_CATEGORY</t>
-  </si>
-  <si>
-    <t>ROLE</t>
-  </si>
-  <si>
-    <t>ROLE_ACCESS_PROFILE</t>
-  </si>
-  <si>
-    <t>Record ID</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SAFETY</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SAMPLE_FREQUENCY</t>
-  </si>
-  <si>
-    <t>SEGREGATE</t>
-  </si>
-  <si>
-    <t>SHIFT</t>
-  </si>
-  <si>
-    <t>SHIPPING</t>
-  </si>
-  <si>
-    <t>SO</t>
-  </si>
-  <si>
-    <t>SOP</t>
-  </si>
-  <si>
-    <t>SOP: SOP-103 | ANNEX: ANNEX-QA-004, ANNEX-QA-006, ANNEX-QMS-027</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>STOP</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>SUPERVISED</t>
-  </si>
-  <si>
-    <t>SUSPENDED</t>
-  </si>
-  <si>
-    <t>SWOT</t>
-  </si>
-  <si>
-    <t>SYSTEM</t>
-  </si>
-  <si>
-    <t>Severity</t>
-  </si>
-  <si>
-    <t>Source Links</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>TRAINER</t>
-  </si>
-  <si>
-    <t>TRAINING</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VIEWER</t>
-  </si>
-  <si>
-    <t>VISUAL</t>
-  </si>
-  <si>
-    <t>Verification or Evidence</t>
-  </si>
-  <si>
-    <t>WEEKLY</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7144,8 +6440,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="A10:N10"/>
-    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>
@@ -9483,67 +8779,67 @@
       <c r="BC7" s="22" t="n"/>
       <c r="BD7" s="23" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="42" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="384" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="22" t="n"/>
-      <c r="E8" s="22" t="n"/>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n"/>
-      <c r="H8" s="22" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="22" t="n"/>
-      <c r="M8" s="22" t="n"/>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n"/>
-      <c r="P8" s="22" t="n"/>
-      <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n"/>
-      <c r="T8" s="22" t="n"/>
-      <c r="U8" s="22" t="n"/>
-      <c r="V8" s="22" t="n"/>
-      <c r="W8" s="22" t="n"/>
-      <c r="X8" s="22" t="n"/>
-      <c r="Y8" s="22" t="n"/>
-      <c r="Z8" s="22" t="n"/>
-      <c r="AA8" s="22" t="n"/>
-      <c r="AB8" s="22" t="n"/>
-      <c r="AC8" s="22" t="n"/>
-      <c r="AD8" s="22" t="n"/>
-      <c r="AE8" s="22" t="n"/>
-      <c r="AF8" s="22" t="n"/>
-      <c r="AG8" s="22" t="n"/>
-      <c r="AH8" s="22" t="n"/>
-      <c r="AI8" s="22" t="n"/>
-      <c r="AJ8" s="22" t="n"/>
-      <c r="AK8" s="22" t="n"/>
-      <c r="AL8" s="22" t="n"/>
-      <c r="AM8" s="22" t="n"/>
-      <c r="AN8" s="22" t="n"/>
-      <c r="AO8" s="22" t="n"/>
-      <c r="AP8" s="22" t="n"/>
-      <c r="AQ8" s="22" t="n"/>
-      <c r="AR8" s="22" t="n"/>
-      <c r="AS8" s="22" t="n"/>
-      <c r="AT8" s="22" t="n"/>
-      <c r="AU8" s="22" t="n"/>
-      <c r="AV8" s="22" t="n"/>
-      <c r="AW8" s="22" t="n"/>
-      <c r="AX8" s="22" t="n"/>
-      <c r="AY8" s="22" t="n"/>
-      <c r="AZ8" s="22" t="n"/>
-      <c r="BA8" s="22" t="n"/>
-      <c r="BB8" s="22" t="n"/>
-      <c r="BC8" s="22" t="n"/>
-      <c r="BD8" s="23" t="n"/>
+      <c r="B8" s="385" t="n"/>
+      <c r="C8" s="385" t="n"/>
+      <c r="D8" s="385" t="n"/>
+      <c r="E8" s="385" t="n"/>
+      <c r="F8" s="385" t="n"/>
+      <c r="G8" s="385" t="n"/>
+      <c r="H8" s="385" t="n"/>
+      <c r="I8" s="385" t="n"/>
+      <c r="J8" s="385" t="n"/>
+      <c r="K8" s="385" t="n"/>
+      <c r="L8" s="385" t="n"/>
+      <c r="M8" s="385" t="n"/>
+      <c r="N8" s="385" t="n"/>
+      <c r="O8" s="385" t="n"/>
+      <c r="P8" s="385" t="n"/>
+      <c r="Q8" s="385" t="n"/>
+      <c r="R8" s="385" t="n"/>
+      <c r="S8" s="385" t="n"/>
+      <c r="T8" s="385" t="n"/>
+      <c r="U8" s="385" t="n"/>
+      <c r="V8" s="385" t="n"/>
+      <c r="W8" s="385" t="n"/>
+      <c r="X8" s="385" t="n"/>
+      <c r="Y8" s="385" t="n"/>
+      <c r="Z8" s="385" t="n"/>
+      <c r="AA8" s="385" t="n"/>
+      <c r="AB8" s="385" t="n"/>
+      <c r="AC8" s="385" t="n"/>
+      <c r="AD8" s="385" t="n"/>
+      <c r="AE8" s="385" t="n"/>
+      <c r="AF8" s="385" t="n"/>
+      <c r="AG8" s="385" t="n"/>
+      <c r="AH8" s="385" t="n"/>
+      <c r="AI8" s="385" t="n"/>
+      <c r="AJ8" s="385" t="n"/>
+      <c r="AK8" s="385" t="n"/>
+      <c r="AL8" s="385" t="n"/>
+      <c r="AM8" s="385" t="n"/>
+      <c r="AN8" s="385" t="n"/>
+      <c r="AO8" s="385" t="n"/>
+      <c r="AP8" s="385" t="n"/>
+      <c r="AQ8" s="385" t="n"/>
+      <c r="AR8" s="385" t="n"/>
+      <c r="AS8" s="385" t="n"/>
+      <c r="AT8" s="385" t="n"/>
+      <c r="AU8" s="385" t="n"/>
+      <c r="AV8" s="385" t="n"/>
+      <c r="AW8" s="385" t="n"/>
+      <c r="AX8" s="385" t="n"/>
+      <c r="AY8" s="385" t="n"/>
+      <c r="AZ8" s="385" t="n"/>
+      <c r="BA8" s="385" t="n"/>
+      <c r="BB8" s="385" t="n"/>
+      <c r="BC8" s="385" t="n"/>
+      <c r="BD8" s="386" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="275" t="inlineStr">
@@ -10991,67 +10287,67 @@
       <c r="BC19" s="319" t="n"/>
       <c r="BD19" s="320" t="n"/>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="42" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="384" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="22" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="22" t="n"/>
-      <c r="H20" s="22" t="n"/>
-      <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
-      <c r="M20" s="22" t="n"/>
-      <c r="N20" s="22" t="n"/>
-      <c r="O20" s="22" t="n"/>
-      <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
-      <c r="S20" s="22" t="n"/>
-      <c r="T20" s="22" t="n"/>
-      <c r="U20" s="22" t="n"/>
-      <c r="V20" s="22" t="n"/>
-      <c r="W20" s="22" t="n"/>
-      <c r="X20" s="22" t="n"/>
-      <c r="Y20" s="22" t="n"/>
-      <c r="Z20" s="22" t="n"/>
-      <c r="AA20" s="22" t="n"/>
-      <c r="AB20" s="22" t="n"/>
-      <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="22" t="n"/>
-      <c r="AE20" s="22" t="n"/>
-      <c r="AF20" s="22" t="n"/>
-      <c r="AG20" s="22" t="n"/>
-      <c r="AH20" s="22" t="n"/>
-      <c r="AI20" s="22" t="n"/>
-      <c r="AJ20" s="22" t="n"/>
-      <c r="AK20" s="22" t="n"/>
-      <c r="AL20" s="22" t="n"/>
-      <c r="AM20" s="22" t="n"/>
-      <c r="AN20" s="22" t="n"/>
-      <c r="AO20" s="22" t="n"/>
-      <c r="AP20" s="22" t="n"/>
-      <c r="AQ20" s="22" t="n"/>
-      <c r="AR20" s="22" t="n"/>
-      <c r="AS20" s="22" t="n"/>
-      <c r="AT20" s="22" t="n"/>
-      <c r="AU20" s="22" t="n"/>
-      <c r="AV20" s="22" t="n"/>
-      <c r="AW20" s="22" t="n"/>
-      <c r="AX20" s="22" t="n"/>
-      <c r="AY20" s="22" t="n"/>
-      <c r="AZ20" s="22" t="n"/>
-      <c r="BA20" s="22" t="n"/>
-      <c r="BB20" s="22" t="n"/>
-      <c r="BC20" s="22" t="n"/>
-      <c r="BD20" s="23" t="n"/>
+      <c r="B20" s="385" t="n"/>
+      <c r="C20" s="385" t="n"/>
+      <c r="D20" s="385" t="n"/>
+      <c r="E20" s="385" t="n"/>
+      <c r="F20" s="385" t="n"/>
+      <c r="G20" s="385" t="n"/>
+      <c r="H20" s="385" t="n"/>
+      <c r="I20" s="385" t="n"/>
+      <c r="J20" s="385" t="n"/>
+      <c r="K20" s="385" t="n"/>
+      <c r="L20" s="385" t="n"/>
+      <c r="M20" s="385" t="n"/>
+      <c r="N20" s="385" t="n"/>
+      <c r="O20" s="385" t="n"/>
+      <c r="P20" s="385" t="n"/>
+      <c r="Q20" s="385" t="n"/>
+      <c r="R20" s="385" t="n"/>
+      <c r="S20" s="385" t="n"/>
+      <c r="T20" s="385" t="n"/>
+      <c r="U20" s="385" t="n"/>
+      <c r="V20" s="385" t="n"/>
+      <c r="W20" s="385" t="n"/>
+      <c r="X20" s="385" t="n"/>
+      <c r="Y20" s="385" t="n"/>
+      <c r="Z20" s="385" t="n"/>
+      <c r="AA20" s="385" t="n"/>
+      <c r="AB20" s="385" t="n"/>
+      <c r="AC20" s="385" t="n"/>
+      <c r="AD20" s="385" t="n"/>
+      <c r="AE20" s="385" t="n"/>
+      <c r="AF20" s="385" t="n"/>
+      <c r="AG20" s="385" t="n"/>
+      <c r="AH20" s="385" t="n"/>
+      <c r="AI20" s="385" t="n"/>
+      <c r="AJ20" s="385" t="n"/>
+      <c r="AK20" s="385" t="n"/>
+      <c r="AL20" s="385" t="n"/>
+      <c r="AM20" s="385" t="n"/>
+      <c r="AN20" s="385" t="n"/>
+      <c r="AO20" s="385" t="n"/>
+      <c r="AP20" s="385" t="n"/>
+      <c r="AQ20" s="385" t="n"/>
+      <c r="AR20" s="385" t="n"/>
+      <c r="AS20" s="385" t="n"/>
+      <c r="AT20" s="385" t="n"/>
+      <c r="AU20" s="385" t="n"/>
+      <c r="AV20" s="385" t="n"/>
+      <c r="AW20" s="385" t="n"/>
+      <c r="AX20" s="385" t="n"/>
+      <c r="AY20" s="385" t="n"/>
+      <c r="AZ20" s="385" t="n"/>
+      <c r="BA20" s="385" t="n"/>
+      <c r="BB20" s="385" t="n"/>
+      <c r="BC20" s="385" t="n"/>
+      <c r="BD20" s="386" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -206,7 +206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="153">
+  <borders count="155">
     <border>
       <left/>
       <right/>
@@ -1856,11 +1856,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="390">
+  <cellXfs count="428">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -2902,6 +2926,98 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2983,11 +3099,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>622620</colOff>
-      <row>0</row>
-      <rowOff>238275</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1652040" cy="476550"/>
+    <ext cx="2257425" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3001,9 +3117,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3016,11 +3129,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>622620</colOff>
-      <row>0</row>
-      <rowOff>238275</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1652040" cy="476550"/>
+    <ext cx="2257425" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3034,9 +3147,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3049,11 +3159,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3067,9 +3177,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3453,7 +3560,7 @@
     <col width="2.33" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="321" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -3470,7 +3577,7 @@
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="227" t="inlineStr">
+      <c r="Q1" s="426" t="inlineStr">
         <is>
           <t>PFMEA LITE</t>
         </is>
@@ -3519,7 +3626,7 @@
       <c r="BG1" s="2" t="n"/>
       <c r="BH1" s="2" t="n"/>
       <c r="BI1" s="2" t="n"/>
-      <c r="BJ1" s="2" t="n"/>
+      <c r="BJ1" s="3" t="n"/>
       <c r="BK1" s="322" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -3550,375 +3657,548 @@
       <c r="CD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="BK2" s="325" t="inlineStr">
+      <c r="A2" s="390" t="n"/>
+      <c r="B2" s="391" t="n"/>
+      <c r="C2" s="391" t="n"/>
+      <c r="D2" s="391" t="n"/>
+      <c r="E2" s="391" t="n"/>
+      <c r="F2" s="391" t="n"/>
+      <c r="G2" s="391" t="n"/>
+      <c r="H2" s="391" t="n"/>
+      <c r="I2" s="391" t="n"/>
+      <c r="J2" s="391" t="n"/>
+      <c r="K2" s="391" t="n"/>
+      <c r="L2" s="391" t="n"/>
+      <c r="M2" s="391" t="n"/>
+      <c r="N2" s="391" t="n"/>
+      <c r="O2" s="391" t="n"/>
+      <c r="P2" s="392" t="n"/>
+      <c r="Q2" s="391" t="n"/>
+      <c r="R2" s="391" t="n"/>
+      <c r="S2" s="391" t="n"/>
+      <c r="T2" s="391" t="n"/>
+      <c r="U2" s="391" t="n"/>
+      <c r="V2" s="391" t="n"/>
+      <c r="W2" s="391" t="n"/>
+      <c r="X2" s="391" t="n"/>
+      <c r="Y2" s="391" t="n"/>
+      <c r="Z2" s="391" t="n"/>
+      <c r="AA2" s="391" t="n"/>
+      <c r="AB2" s="391" t="n"/>
+      <c r="AC2" s="391" t="n"/>
+      <c r="AD2" s="391" t="n"/>
+      <c r="AE2" s="391" t="n"/>
+      <c r="AF2" s="391" t="n"/>
+      <c r="AG2" s="391" t="n"/>
+      <c r="AH2" s="391" t="n"/>
+      <c r="AI2" s="391" t="n"/>
+      <c r="AJ2" s="391" t="n"/>
+      <c r="AK2" s="391" t="n"/>
+      <c r="AL2" s="391" t="n"/>
+      <c r="AM2" s="391" t="n"/>
+      <c r="AN2" s="391" t="n"/>
+      <c r="AO2" s="391" t="n"/>
+      <c r="AP2" s="391" t="n"/>
+      <c r="AQ2" s="391" t="n"/>
+      <c r="AR2" s="391" t="n"/>
+      <c r="AS2" s="391" t="n"/>
+      <c r="AT2" s="391" t="n"/>
+      <c r="AU2" s="391" t="n"/>
+      <c r="AV2" s="391" t="n"/>
+      <c r="AW2" s="391" t="n"/>
+      <c r="AX2" s="391" t="n"/>
+      <c r="AY2" s="391" t="n"/>
+      <c r="AZ2" s="391" t="n"/>
+      <c r="BA2" s="391" t="n"/>
+      <c r="BB2" s="391" t="n"/>
+      <c r="BC2" s="391" t="n"/>
+      <c r="BD2" s="391" t="n"/>
+      <c r="BE2" s="391" t="n"/>
+      <c r="BF2" s="391" t="n"/>
+      <c r="BG2" s="391" t="n"/>
+      <c r="BH2" s="391" t="n"/>
+      <c r="BI2" s="391" t="n"/>
+      <c r="BJ2" s="392" t="n"/>
+      <c r="BK2" s="393" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="BL2" s="326" t="n"/>
-      <c r="BM2" s="326" t="n"/>
-      <c r="BN2" s="326" t="n"/>
-      <c r="BO2" s="326" t="n"/>
-      <c r="BP2" s="326" t="n"/>
-      <c r="BQ2" s="326" t="n"/>
-      <c r="BR2" s="327" t="n"/>
-      <c r="BS2" s="328" t="inlineStr">
+      <c r="BL2" s="394" t="n"/>
+      <c r="BM2" s="394" t="n"/>
+      <c r="BN2" s="394" t="n"/>
+      <c r="BO2" s="394" t="n"/>
+      <c r="BP2" s="394" t="n"/>
+      <c r="BQ2" s="394" t="n"/>
+      <c r="BR2" s="395" t="n"/>
+      <c r="BS2" s="396" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="BT2" s="326" t="n"/>
-      <c r="BU2" s="326" t="n"/>
-      <c r="BV2" s="326" t="n"/>
-      <c r="BW2" s="326" t="n"/>
-      <c r="BX2" s="326" t="n"/>
-      <c r="BY2" s="326" t="n"/>
-      <c r="BZ2" s="326" t="n"/>
-      <c r="CA2" s="326" t="n"/>
-      <c r="CB2" s="326" t="n"/>
-      <c r="CC2" s="326" t="n"/>
-      <c r="CD2" s="329" t="n"/>
+      <c r="BT2" s="397" t="n"/>
+      <c r="BU2" s="397" t="n"/>
+      <c r="BV2" s="397" t="n"/>
+      <c r="BW2" s="397" t="n"/>
+      <c r="BX2" s="397" t="n"/>
+      <c r="BY2" s="397" t="n"/>
+      <c r="BZ2" s="397" t="n"/>
+      <c r="CA2" s="397" t="n"/>
+      <c r="CB2" s="397" t="n"/>
+      <c r="CC2" s="397" t="n"/>
+      <c r="CD2" s="398" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="BK3" s="325" t="inlineStr">
+      <c r="A3" s="399" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="400" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
+      <c r="Z3" s="54" t="n"/>
+      <c r="AA3" s="54" t="n"/>
+      <c r="AB3" s="54" t="n"/>
+      <c r="AC3" s="54" t="n"/>
+      <c r="AD3" s="54" t="n"/>
+      <c r="AE3" s="54" t="n"/>
+      <c r="AF3" s="54" t="n"/>
+      <c r="AG3" s="54" t="n"/>
+      <c r="AH3" s="54" t="n"/>
+      <c r="AI3" s="54" t="n"/>
+      <c r="AJ3" s="54" t="n"/>
+      <c r="AK3" s="54" t="n"/>
+      <c r="AL3" s="54" t="n"/>
+      <c r="AM3" s="54" t="n"/>
+      <c r="AN3" s="54" t="n"/>
+      <c r="AO3" s="54" t="n"/>
+      <c r="AP3" s="54" t="n"/>
+      <c r="AQ3" s="54" t="n"/>
+      <c r="AR3" s="54" t="n"/>
+      <c r="AS3" s="54" t="n"/>
+      <c r="AT3" s="54" t="n"/>
+      <c r="AU3" s="54" t="n"/>
+      <c r="AV3" s="54" t="n"/>
+      <c r="AW3" s="54" t="n"/>
+      <c r="AX3" s="54" t="n"/>
+      <c r="AY3" s="54" t="n"/>
+      <c r="AZ3" s="54" t="n"/>
+      <c r="BA3" s="54" t="n"/>
+      <c r="BB3" s="54" t="n"/>
+      <c r="BC3" s="54" t="n"/>
+      <c r="BD3" s="54" t="n"/>
+      <c r="BE3" s="54" t="n"/>
+      <c r="BF3" s="54" t="n"/>
+      <c r="BG3" s="54" t="n"/>
+      <c r="BH3" s="54" t="n"/>
+      <c r="BI3" s="54" t="n"/>
+      <c r="BJ3" s="400" t="n"/>
+      <c r="BK3" s="401" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="BL3" s="326" t="n"/>
-      <c r="BM3" s="326" t="n"/>
-      <c r="BN3" s="326" t="n"/>
-      <c r="BO3" s="326" t="n"/>
-      <c r="BP3" s="326" t="n"/>
-      <c r="BQ3" s="326" t="n"/>
-      <c r="BR3" s="327" t="n"/>
-      <c r="BS3" s="328" t="inlineStr">
+      <c r="BL3" s="402" t="n"/>
+      <c r="BM3" s="402" t="n"/>
+      <c r="BN3" s="402" t="n"/>
+      <c r="BO3" s="402" t="n"/>
+      <c r="BP3" s="402" t="n"/>
+      <c r="BQ3" s="402" t="n"/>
+      <c r="BR3" s="403" t="n"/>
+      <c r="BS3" s="297" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="BT3" s="326" t="n"/>
-      <c r="BU3" s="326" t="n"/>
-      <c r="BV3" s="326" t="n"/>
-      <c r="BW3" s="326" t="n"/>
-      <c r="BX3" s="326" t="n"/>
-      <c r="BY3" s="326" t="n"/>
-      <c r="BZ3" s="326" t="n"/>
-      <c r="CA3" s="326" t="n"/>
-      <c r="CB3" s="326" t="n"/>
-      <c r="CC3" s="326" t="n"/>
-      <c r="CD3" s="329" t="n"/>
+      <c r="BT3" s="404" t="n"/>
+      <c r="BU3" s="404" t="n"/>
+      <c r="BV3" s="404" t="n"/>
+      <c r="BW3" s="404" t="n"/>
+      <c r="BX3" s="404" t="n"/>
+      <c r="BY3" s="404" t="n"/>
+      <c r="BZ3" s="404" t="n"/>
+      <c r="CA3" s="404" t="n"/>
+      <c r="CB3" s="404" t="n"/>
+      <c r="CC3" s="404" t="n"/>
+      <c r="CD3" s="405" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="239" t="inlineStr">
+      <c r="A4" s="399" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="54" t="n"/>
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="400" t="n"/>
+      <c r="Q4" s="406" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="BK4" s="325" t="inlineStr">
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="54" t="n"/>
+      <c r="AD4" s="54" t="n"/>
+      <c r="AE4" s="54" t="n"/>
+      <c r="AF4" s="54" t="n"/>
+      <c r="AG4" s="54" t="n"/>
+      <c r="AH4" s="54" t="n"/>
+      <c r="AI4" s="54" t="n"/>
+      <c r="AJ4" s="54" t="n"/>
+      <c r="AK4" s="54" t="n"/>
+      <c r="AL4" s="54" t="n"/>
+      <c r="AM4" s="54" t="n"/>
+      <c r="AN4" s="54" t="n"/>
+      <c r="AO4" s="54" t="n"/>
+      <c r="AP4" s="54" t="n"/>
+      <c r="AQ4" s="54" t="n"/>
+      <c r="AR4" s="54" t="n"/>
+      <c r="AS4" s="54" t="n"/>
+      <c r="AT4" s="54" t="n"/>
+      <c r="AU4" s="54" t="n"/>
+      <c r="AV4" s="54" t="n"/>
+      <c r="AW4" s="54" t="n"/>
+      <c r="AX4" s="54" t="n"/>
+      <c r="AY4" s="54" t="n"/>
+      <c r="AZ4" s="54" t="n"/>
+      <c r="BA4" s="54" t="n"/>
+      <c r="BB4" s="54" t="n"/>
+      <c r="BC4" s="54" t="n"/>
+      <c r="BD4" s="54" t="n"/>
+      <c r="BE4" s="54" t="n"/>
+      <c r="BF4" s="54" t="n"/>
+      <c r="BG4" s="54" t="n"/>
+      <c r="BH4" s="54" t="n"/>
+      <c r="BI4" s="54" t="n"/>
+      <c r="BJ4" s="400" t="n"/>
+      <c r="BK4" s="401" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="BL4" s="326" t="n"/>
-      <c r="BM4" s="326" t="n"/>
-      <c r="BN4" s="326" t="n"/>
-      <c r="BO4" s="326" t="n"/>
-      <c r="BP4" s="326" t="n"/>
-      <c r="BQ4" s="326" t="n"/>
-      <c r="BR4" s="327" t="n"/>
-      <c r="BS4" s="328" t="inlineStr">
+      <c r="BL4" s="402" t="n"/>
+      <c r="BM4" s="402" t="n"/>
+      <c r="BN4" s="402" t="n"/>
+      <c r="BO4" s="402" t="n"/>
+      <c r="BP4" s="402" t="n"/>
+      <c r="BQ4" s="402" t="n"/>
+      <c r="BR4" s="403" t="n"/>
+      <c r="BS4" s="297" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="BT4" s="326" t="n"/>
-      <c r="BU4" s="326" t="n"/>
-      <c r="BV4" s="326" t="n"/>
-      <c r="BW4" s="326" t="n"/>
-      <c r="BX4" s="326" t="n"/>
-      <c r="BY4" s="326" t="n"/>
-      <c r="BZ4" s="326" t="n"/>
-      <c r="CA4" s="326" t="n"/>
-      <c r="CB4" s="326" t="n"/>
-      <c r="CC4" s="326" t="n"/>
-      <c r="CD4" s="329" t="n"/>
+      <c r="BT4" s="404" t="n"/>
+      <c r="BU4" s="404" t="n"/>
+      <c r="BV4" s="404" t="n"/>
+      <c r="BW4" s="404" t="n"/>
+      <c r="BX4" s="404" t="n"/>
+      <c r="BY4" s="404" t="n"/>
+      <c r="BZ4" s="404" t="n"/>
+      <c r="CA4" s="404" t="n"/>
+      <c r="CB4" s="404" t="n"/>
+      <c r="CC4" s="404" t="n"/>
+      <c r="CD4" s="405" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="18" t="n"/>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="A5" s="399" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="54" t="n"/>
+      <c r="L5" s="54" t="n"/>
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="400" t="n"/>
+      <c r="Q5" s="407" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="17" t="n"/>
-      <c r="AR5" s="17" t="n"/>
-      <c r="AS5" s="17" t="n"/>
-      <c r="AT5" s="17" t="n"/>
-      <c r="AU5" s="17" t="n"/>
-      <c r="AV5" s="17" t="n"/>
-      <c r="AW5" s="17" t="n"/>
-      <c r="AX5" s="17" t="n"/>
-      <c r="AY5" s="17" t="n"/>
-      <c r="AZ5" s="17" t="n"/>
-      <c r="BA5" s="17" t="n"/>
-      <c r="BB5" s="17" t="n"/>
-      <c r="BC5" s="17" t="n"/>
-      <c r="BD5" s="17" t="n"/>
-      <c r="BE5" s="17" t="n"/>
-      <c r="BF5" s="17" t="n"/>
-      <c r="BG5" s="17" t="n"/>
-      <c r="BH5" s="17" t="n"/>
-      <c r="BI5" s="17" t="n"/>
-      <c r="BJ5" s="17" t="n"/>
-      <c r="BK5" s="330" t="inlineStr">
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="54" t="n"/>
+      <c r="AB5" s="54" t="n"/>
+      <c r="AC5" s="54" t="n"/>
+      <c r="AD5" s="54" t="n"/>
+      <c r="AE5" s="54" t="n"/>
+      <c r="AF5" s="54" t="n"/>
+      <c r="AG5" s="54" t="n"/>
+      <c r="AH5" s="54" t="n"/>
+      <c r="AI5" s="54" t="n"/>
+      <c r="AJ5" s="54" t="n"/>
+      <c r="AK5" s="54" t="n"/>
+      <c r="AL5" s="54" t="n"/>
+      <c r="AM5" s="54" t="n"/>
+      <c r="AN5" s="54" t="n"/>
+      <c r="AO5" s="54" t="n"/>
+      <c r="AP5" s="54" t="n"/>
+      <c r="AQ5" s="54" t="n"/>
+      <c r="AR5" s="54" t="n"/>
+      <c r="AS5" s="54" t="n"/>
+      <c r="AT5" s="54" t="n"/>
+      <c r="AU5" s="54" t="n"/>
+      <c r="AV5" s="54" t="n"/>
+      <c r="AW5" s="54" t="n"/>
+      <c r="AX5" s="54" t="n"/>
+      <c r="AY5" s="54" t="n"/>
+      <c r="AZ5" s="54" t="n"/>
+      <c r="BA5" s="54" t="n"/>
+      <c r="BB5" s="54" t="n"/>
+      <c r="BC5" s="54" t="n"/>
+      <c r="BD5" s="54" t="n"/>
+      <c r="BE5" s="54" t="n"/>
+      <c r="BF5" s="54" t="n"/>
+      <c r="BG5" s="54" t="n"/>
+      <c r="BH5" s="54" t="n"/>
+      <c r="BI5" s="54" t="n"/>
+      <c r="BJ5" s="400" t="n"/>
+      <c r="BK5" s="401" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="BL5" s="331" t="n"/>
-      <c r="BM5" s="331" t="n"/>
-      <c r="BN5" s="331" t="n"/>
-      <c r="BO5" s="331" t="n"/>
-      <c r="BP5" s="331" t="n"/>
-      <c r="BQ5" s="331" t="n"/>
-      <c r="BR5" s="332" t="n"/>
-      <c r="BS5" s="333" t="inlineStr">
+      <c r="BL5" s="402" t="n"/>
+      <c r="BM5" s="402" t="n"/>
+      <c r="BN5" s="402" t="n"/>
+      <c r="BO5" s="402" t="n"/>
+      <c r="BP5" s="402" t="n"/>
+      <c r="BQ5" s="402" t="n"/>
+      <c r="BR5" s="403" t="n"/>
+      <c r="BS5" s="297" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="BT5" s="331" t="n"/>
-      <c r="BU5" s="331" t="n"/>
-      <c r="BV5" s="331" t="n"/>
-      <c r="BW5" s="331" t="n"/>
-      <c r="BX5" s="331" t="n"/>
-      <c r="BY5" s="331" t="n"/>
-      <c r="BZ5" s="331" t="n"/>
-      <c r="CA5" s="331" t="n"/>
-      <c r="CB5" s="331" t="n"/>
-      <c r="CC5" s="331" t="n"/>
-      <c r="CD5" s="334" t="n"/>
+      <c r="BT5" s="404" t="n"/>
+      <c r="BU5" s="404" t="n"/>
+      <c r="BV5" s="404" t="n"/>
+      <c r="BW5" s="404" t="n"/>
+      <c r="BX5" s="404" t="n"/>
+      <c r="BY5" s="404" t="n"/>
+      <c r="BZ5" s="404" t="n"/>
+      <c r="CA5" s="404" t="n"/>
+      <c r="CB5" s="404" t="n"/>
+      <c r="CC5" s="404" t="n"/>
+      <c r="CD5" s="405" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="248" t="n"/>
-      <c r="B6" s="248" t="n"/>
-      <c r="C6" s="248" t="n"/>
-      <c r="D6" s="248" t="n"/>
-      <c r="E6" s="248" t="n"/>
-      <c r="F6" s="248" t="n"/>
-      <c r="G6" s="248" t="n"/>
-      <c r="H6" s="248" t="n"/>
-      <c r="I6" s="248" t="n"/>
-      <c r="J6" s="248" t="n"/>
-      <c r="K6" s="248" t="n"/>
-      <c r="L6" s="248" t="n"/>
-      <c r="M6" s="248" t="n"/>
-      <c r="N6" s="248" t="n"/>
-      <c r="O6" s="248" t="n"/>
-      <c r="P6" s="248" t="n"/>
-      <c r="Q6" s="248" t="n"/>
-      <c r="R6" s="248" t="n"/>
-      <c r="S6" s="248" t="n"/>
-      <c r="T6" s="248" t="n"/>
-      <c r="U6" s="248" t="n"/>
-      <c r="V6" s="248" t="n"/>
-      <c r="W6" s="248" t="n"/>
-      <c r="X6" s="248" t="n"/>
-      <c r="Y6" s="248" t="n"/>
-      <c r="Z6" s="248" t="n"/>
-      <c r="AA6" s="248" t="n"/>
-      <c r="AB6" s="248" t="n"/>
-      <c r="AC6" s="248" t="n"/>
-      <c r="AD6" s="248" t="n"/>
-      <c r="AE6" s="248" t="n"/>
-      <c r="AF6" s="248" t="n"/>
-      <c r="AG6" s="248" t="n"/>
-      <c r="AH6" s="248" t="n"/>
-      <c r="AI6" s="248" t="n"/>
-      <c r="AJ6" s="248" t="n"/>
-      <c r="AK6" s="248" t="n"/>
-      <c r="AL6" s="248" t="n"/>
-      <c r="AM6" s="248" t="n"/>
-      <c r="AN6" s="248" t="n"/>
-      <c r="AO6" s="248" t="n"/>
-      <c r="AP6" s="248" t="n"/>
-      <c r="AQ6" s="248" t="n"/>
-      <c r="AR6" s="248" t="n"/>
-      <c r="AS6" s="248" t="n"/>
-      <c r="AT6" s="248" t="n"/>
-      <c r="AU6" s="248" t="n"/>
-      <c r="AV6" s="248" t="n"/>
-      <c r="AW6" s="248" t="n"/>
-      <c r="AX6" s="248" t="n"/>
-      <c r="AY6" s="248" t="n"/>
-      <c r="AZ6" s="248" t="n"/>
-      <c r="BA6" s="248" t="n"/>
-      <c r="BB6" s="248" t="n"/>
-      <c r="BC6" s="248" t="n"/>
-      <c r="BD6" s="248" t="n"/>
-      <c r="BE6" s="248" t="n"/>
-      <c r="BF6" s="248" t="n"/>
-      <c r="BG6" s="248" t="n"/>
-      <c r="BH6" s="248" t="n"/>
-      <c r="BI6" s="248" t="n"/>
-      <c r="BJ6" s="248" t="n"/>
-      <c r="BK6" s="248" t="n"/>
-      <c r="BL6" s="248" t="n"/>
-      <c r="BM6" s="248" t="n"/>
-      <c r="BN6" s="248" t="n"/>
-      <c r="BO6" s="248" t="n"/>
-      <c r="BP6" s="248" t="n"/>
-      <c r="BQ6" s="248" t="n"/>
-      <c r="BR6" s="248" t="n"/>
-      <c r="BS6" s="248" t="n"/>
-      <c r="BT6" s="248" t="n"/>
-      <c r="BU6" s="248" t="n"/>
-      <c r="BV6" s="248" t="n"/>
-      <c r="BW6" s="248" t="n"/>
-      <c r="BX6" s="248" t="n"/>
-      <c r="BY6" s="248" t="n"/>
-      <c r="BZ6" s="248" t="n"/>
-      <c r="CA6" s="248" t="n"/>
-      <c r="CB6" s="248" t="n"/>
-      <c r="CC6" s="248" t="n"/>
-      <c r="CD6" s="248" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="408" t="n"/>
+      <c r="B6" s="409" t="n"/>
+      <c r="C6" s="409" t="n"/>
+      <c r="D6" s="409" t="n"/>
+      <c r="E6" s="409" t="n"/>
+      <c r="F6" s="409" t="n"/>
+      <c r="G6" s="409" t="n"/>
+      <c r="H6" s="409" t="n"/>
+      <c r="I6" s="409" t="n"/>
+      <c r="J6" s="409" t="n"/>
+      <c r="K6" s="409" t="n"/>
+      <c r="L6" s="409" t="n"/>
+      <c r="M6" s="409" t="n"/>
+      <c r="N6" s="409" t="n"/>
+      <c r="O6" s="409" t="n"/>
+      <c r="P6" s="410" t="n"/>
+      <c r="Q6" s="409" t="n"/>
+      <c r="R6" s="409" t="n"/>
+      <c r="S6" s="409" t="n"/>
+      <c r="T6" s="409" t="n"/>
+      <c r="U6" s="409" t="n"/>
+      <c r="V6" s="409" t="n"/>
+      <c r="W6" s="409" t="n"/>
+      <c r="X6" s="409" t="n"/>
+      <c r="Y6" s="409" t="n"/>
+      <c r="Z6" s="409" t="n"/>
+      <c r="AA6" s="409" t="n"/>
+      <c r="AB6" s="409" t="n"/>
+      <c r="AC6" s="409" t="n"/>
+      <c r="AD6" s="409" t="n"/>
+      <c r="AE6" s="409" t="n"/>
+      <c r="AF6" s="409" t="n"/>
+      <c r="AG6" s="409" t="n"/>
+      <c r="AH6" s="409" t="n"/>
+      <c r="AI6" s="409" t="n"/>
+      <c r="AJ6" s="409" t="n"/>
+      <c r="AK6" s="409" t="n"/>
+      <c r="AL6" s="409" t="n"/>
+      <c r="AM6" s="409" t="n"/>
+      <c r="AN6" s="409" t="n"/>
+      <c r="AO6" s="409" t="n"/>
+      <c r="AP6" s="409" t="n"/>
+      <c r="AQ6" s="409" t="n"/>
+      <c r="AR6" s="409" t="n"/>
+      <c r="AS6" s="409" t="n"/>
+      <c r="AT6" s="409" t="n"/>
+      <c r="AU6" s="409" t="n"/>
+      <c r="AV6" s="409" t="n"/>
+      <c r="AW6" s="409" t="n"/>
+      <c r="AX6" s="409" t="n"/>
+      <c r="AY6" s="409" t="n"/>
+      <c r="AZ6" s="409" t="n"/>
+      <c r="BA6" s="409" t="n"/>
+      <c r="BB6" s="409" t="n"/>
+      <c r="BC6" s="409" t="n"/>
+      <c r="BD6" s="409" t="n"/>
+      <c r="BE6" s="409" t="n"/>
+      <c r="BF6" s="409" t="n"/>
+      <c r="BG6" s="409" t="n"/>
+      <c r="BH6" s="409" t="n"/>
+      <c r="BI6" s="409" t="n"/>
+      <c r="BJ6" s="410" t="n"/>
+      <c r="BK6" s="411" t="n"/>
+      <c r="BL6" s="411" t="n"/>
+      <c r="BM6" s="411" t="n"/>
+      <c r="BN6" s="411" t="n"/>
+      <c r="BO6" s="411" t="n"/>
+      <c r="BP6" s="411" t="n"/>
+      <c r="BQ6" s="411" t="n"/>
+      <c r="BR6" s="412" t="n"/>
+      <c r="BS6" s="413" t="n"/>
+      <c r="BT6" s="413" t="n"/>
+      <c r="BU6" s="413" t="n"/>
+      <c r="BV6" s="413" t="n"/>
+      <c r="BW6" s="413" t="n"/>
+      <c r="BX6" s="413" t="n"/>
+      <c r="BY6" s="413" t="n"/>
+      <c r="BZ6" s="413" t="n"/>
+      <c r="CA6" s="413" t="n"/>
+      <c r="CB6" s="413" t="n"/>
+      <c r="CC6" s="413" t="n"/>
+      <c r="CD6" s="414" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="22" t="n"/>
-      <c r="BE7" s="22" t="n"/>
-      <c r="BF7" s="22" t="n"/>
-      <c r="BG7" s="22" t="n"/>
-      <c r="BH7" s="22" t="n"/>
-      <c r="BI7" s="22" t="n"/>
-      <c r="BJ7" s="22" t="n"/>
-      <c r="BK7" s="22" t="n"/>
-      <c r="BL7" s="22" t="n"/>
-      <c r="BM7" s="22" t="n"/>
-      <c r="BN7" s="22" t="n"/>
-      <c r="BO7" s="22" t="n"/>
-      <c r="BP7" s="22" t="n"/>
-      <c r="BQ7" s="22" t="n"/>
-      <c r="BR7" s="22" t="n"/>
-      <c r="BS7" s="22" t="n"/>
-      <c r="BT7" s="22" t="n"/>
-      <c r="BU7" s="22" t="n"/>
-      <c r="BV7" s="22" t="n"/>
-      <c r="BW7" s="22" t="n"/>
-      <c r="BX7" s="22" t="n"/>
-      <c r="BY7" s="22" t="n"/>
-      <c r="BZ7" s="22" t="n"/>
-      <c r="CA7" s="22" t="n"/>
-      <c r="CB7" s="22" t="n"/>
-      <c r="CC7" s="22" t="n"/>
-      <c r="CD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="415" t="n"/>
+      <c r="B7" s="416" t="n"/>
+      <c r="C7" s="416" t="n"/>
+      <c r="D7" s="416" t="n"/>
+      <c r="E7" s="416" t="n"/>
+      <c r="F7" s="416" t="n"/>
+      <c r="G7" s="416" t="n"/>
+      <c r="H7" s="416" t="n"/>
+      <c r="I7" s="416" t="n"/>
+      <c r="J7" s="416" t="n"/>
+      <c r="K7" s="416" t="n"/>
+      <c r="L7" s="416" t="n"/>
+      <c r="M7" s="416" t="n"/>
+      <c r="N7" s="416" t="n"/>
+      <c r="O7" s="416" t="n"/>
+      <c r="P7" s="416" t="n"/>
+      <c r="Q7" s="416" t="n"/>
+      <c r="R7" s="416" t="n"/>
+      <c r="S7" s="416" t="n"/>
+      <c r="T7" s="416" t="n"/>
+      <c r="U7" s="416" t="n"/>
+      <c r="V7" s="416" t="n"/>
+      <c r="W7" s="416" t="n"/>
+      <c r="X7" s="416" t="n"/>
+      <c r="Y7" s="416" t="n"/>
+      <c r="Z7" s="416" t="n"/>
+      <c r="AA7" s="416" t="n"/>
+      <c r="AB7" s="416" t="n"/>
+      <c r="AC7" s="416" t="n"/>
+      <c r="AD7" s="416" t="n"/>
+      <c r="AE7" s="416" t="n"/>
+      <c r="AF7" s="416" t="n"/>
+      <c r="AG7" s="416" t="n"/>
+      <c r="AH7" s="416" t="n"/>
+      <c r="AI7" s="416" t="n"/>
+      <c r="AJ7" s="416" t="n"/>
+      <c r="AK7" s="416" t="n"/>
+      <c r="AL7" s="416" t="n"/>
+      <c r="AM7" s="416" t="n"/>
+      <c r="AN7" s="416" t="n"/>
+      <c r="AO7" s="416" t="n"/>
+      <c r="AP7" s="416" t="n"/>
+      <c r="AQ7" s="416" t="n"/>
+      <c r="AR7" s="416" t="n"/>
+      <c r="AS7" s="416" t="n"/>
+      <c r="AT7" s="416" t="n"/>
+      <c r="AU7" s="416" t="n"/>
+      <c r="AV7" s="416" t="n"/>
+      <c r="AW7" s="416" t="n"/>
+      <c r="AX7" s="416" t="n"/>
+      <c r="AY7" s="416" t="n"/>
+      <c r="AZ7" s="416" t="n"/>
+      <c r="BA7" s="416" t="n"/>
+      <c r="BB7" s="416" t="n"/>
+      <c r="BC7" s="416" t="n"/>
+      <c r="BD7" s="416" t="n"/>
+      <c r="BE7" s="416" t="n"/>
+      <c r="BF7" s="416" t="n"/>
+      <c r="BG7" s="416" t="n"/>
+      <c r="BH7" s="416" t="n"/>
+      <c r="BI7" s="416" t="n"/>
+      <c r="BJ7" s="416" t="n"/>
+      <c r="BK7" s="416" t="n"/>
+      <c r="BL7" s="416" t="n"/>
+      <c r="BM7" s="416" t="n"/>
+      <c r="BN7" s="416" t="n"/>
+      <c r="BO7" s="416" t="n"/>
+      <c r="BP7" s="416" t="n"/>
+      <c r="BQ7" s="416" t="n"/>
+      <c r="BR7" s="416" t="n"/>
+      <c r="BS7" s="416" t="n"/>
+      <c r="BT7" s="416" t="n"/>
+      <c r="BU7" s="416" t="n"/>
+      <c r="BV7" s="416" t="n"/>
+      <c r="BW7" s="416" t="n"/>
+      <c r="BX7" s="416" t="n"/>
+      <c r="BY7" s="416" t="n"/>
+      <c r="BZ7" s="416" t="n"/>
+      <c r="CA7" s="416" t="n"/>
+      <c r="CB7" s="416" t="n"/>
+      <c r="CC7" s="416" t="n"/>
+      <c r="CD7" s="416" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="336" t="inlineStr">
@@ -6293,92 +6573,92 @@
       <c r="CD33" s="343" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="384" t="inlineStr">
+      <c r="A34" s="311" t="inlineStr">
         <is>
           <t>NOTICE: PFMEA entries shall stay process-step specific. Record failure mode, effect, cause, current controls, severity, occurrence, detection and action ownership with ranking discipline.</t>
         </is>
       </c>
-      <c r="B34" s="385" t="n"/>
-      <c r="C34" s="385" t="n"/>
-      <c r="D34" s="385" t="n"/>
-      <c r="E34" s="385" t="n"/>
-      <c r="F34" s="385" t="n"/>
-      <c r="G34" s="385" t="n"/>
-      <c r="H34" s="385" t="n"/>
-      <c r="I34" s="385" t="n"/>
-      <c r="J34" s="385" t="n"/>
-      <c r="K34" s="385" t="n"/>
-      <c r="L34" s="385" t="n"/>
-      <c r="M34" s="385" t="n"/>
-      <c r="N34" s="385" t="n"/>
-      <c r="O34" s="385" t="n"/>
-      <c r="P34" s="385" t="n"/>
-      <c r="Q34" s="385" t="n"/>
-      <c r="R34" s="385" t="n"/>
-      <c r="S34" s="385" t="n"/>
-      <c r="T34" s="385" t="n"/>
-      <c r="U34" s="385" t="n"/>
-      <c r="V34" s="385" t="n"/>
-      <c r="W34" s="385" t="n"/>
-      <c r="X34" s="385" t="n"/>
-      <c r="Y34" s="385" t="n"/>
-      <c r="Z34" s="385" t="n"/>
-      <c r="AA34" s="385" t="n"/>
-      <c r="AB34" s="385" t="n"/>
-      <c r="AC34" s="385" t="n"/>
-      <c r="AD34" s="385" t="n"/>
-      <c r="AE34" s="385" t="n"/>
-      <c r="AF34" s="385" t="n"/>
-      <c r="AG34" s="385" t="n"/>
-      <c r="AH34" s="385" t="n"/>
-      <c r="AI34" s="385" t="n"/>
-      <c r="AJ34" s="385" t="n"/>
-      <c r="AK34" s="385" t="n"/>
-      <c r="AL34" s="385" t="n"/>
-      <c r="AM34" s="385" t="n"/>
-      <c r="AN34" s="385" t="n"/>
-      <c r="AO34" s="385" t="n"/>
-      <c r="AP34" s="385" t="n"/>
-      <c r="AQ34" s="385" t="n"/>
-      <c r="AR34" s="385" t="n"/>
-      <c r="AS34" s="385" t="n"/>
-      <c r="AT34" s="385" t="n"/>
-      <c r="AU34" s="385" t="n"/>
-      <c r="AV34" s="385" t="n"/>
-      <c r="AW34" s="385" t="n"/>
-      <c r="AX34" s="385" t="n"/>
-      <c r="AY34" s="385" t="n"/>
-      <c r="AZ34" s="385" t="n"/>
-      <c r="BA34" s="385" t="n"/>
-      <c r="BB34" s="385" t="n"/>
-      <c r="BC34" s="385" t="n"/>
-      <c r="BD34" s="385" t="n"/>
-      <c r="BE34" s="385" t="n"/>
-      <c r="BF34" s="385" t="n"/>
-      <c r="BG34" s="385" t="n"/>
-      <c r="BH34" s="385" t="n"/>
-      <c r="BI34" s="385" t="n"/>
-      <c r="BJ34" s="385" t="n"/>
-      <c r="BK34" s="385" t="n"/>
-      <c r="BL34" s="385" t="n"/>
-      <c r="BM34" s="385" t="n"/>
-      <c r="BN34" s="385" t="n"/>
-      <c r="BO34" s="385" t="n"/>
-      <c r="BP34" s="385" t="n"/>
-      <c r="BQ34" s="385" t="n"/>
-      <c r="BR34" s="385" t="n"/>
-      <c r="BS34" s="385" t="n"/>
-      <c r="BT34" s="385" t="n"/>
-      <c r="BU34" s="385" t="n"/>
-      <c r="BV34" s="385" t="n"/>
-      <c r="BW34" s="385" t="n"/>
-      <c r="BX34" s="385" t="n"/>
-      <c r="BY34" s="385" t="n"/>
-      <c r="BZ34" s="385" t="n"/>
-      <c r="CA34" s="385" t="n"/>
-      <c r="CB34" s="385" t="n"/>
-      <c r="CC34" s="385" t="n"/>
-      <c r="CD34" s="386" t="n"/>
+      <c r="B34" s="417" t="n"/>
+      <c r="C34" s="417" t="n"/>
+      <c r="D34" s="417" t="n"/>
+      <c r="E34" s="417" t="n"/>
+      <c r="F34" s="417" t="n"/>
+      <c r="G34" s="417" t="n"/>
+      <c r="H34" s="417" t="n"/>
+      <c r="I34" s="417" t="n"/>
+      <c r="J34" s="417" t="n"/>
+      <c r="K34" s="417" t="n"/>
+      <c r="L34" s="417" t="n"/>
+      <c r="M34" s="417" t="n"/>
+      <c r="N34" s="417" t="n"/>
+      <c r="O34" s="417" t="n"/>
+      <c r="P34" s="417" t="n"/>
+      <c r="Q34" s="417" t="n"/>
+      <c r="R34" s="417" t="n"/>
+      <c r="S34" s="417" t="n"/>
+      <c r="T34" s="417" t="n"/>
+      <c r="U34" s="417" t="n"/>
+      <c r="V34" s="417" t="n"/>
+      <c r="W34" s="417" t="n"/>
+      <c r="X34" s="417" t="n"/>
+      <c r="Y34" s="417" t="n"/>
+      <c r="Z34" s="417" t="n"/>
+      <c r="AA34" s="417" t="n"/>
+      <c r="AB34" s="417" t="n"/>
+      <c r="AC34" s="417" t="n"/>
+      <c r="AD34" s="417" t="n"/>
+      <c r="AE34" s="417" t="n"/>
+      <c r="AF34" s="417" t="n"/>
+      <c r="AG34" s="417" t="n"/>
+      <c r="AH34" s="417" t="n"/>
+      <c r="AI34" s="417" t="n"/>
+      <c r="AJ34" s="417" t="n"/>
+      <c r="AK34" s="417" t="n"/>
+      <c r="AL34" s="417" t="n"/>
+      <c r="AM34" s="417" t="n"/>
+      <c r="AN34" s="417" t="n"/>
+      <c r="AO34" s="417" t="n"/>
+      <c r="AP34" s="417" t="n"/>
+      <c r="AQ34" s="417" t="n"/>
+      <c r="AR34" s="417" t="n"/>
+      <c r="AS34" s="417" t="n"/>
+      <c r="AT34" s="417" t="n"/>
+      <c r="AU34" s="417" t="n"/>
+      <c r="AV34" s="417" t="n"/>
+      <c r="AW34" s="417" t="n"/>
+      <c r="AX34" s="417" t="n"/>
+      <c r="AY34" s="417" t="n"/>
+      <c r="AZ34" s="417" t="n"/>
+      <c r="BA34" s="417" t="n"/>
+      <c r="BB34" s="417" t="n"/>
+      <c r="BC34" s="417" t="n"/>
+      <c r="BD34" s="417" t="n"/>
+      <c r="BE34" s="417" t="n"/>
+      <c r="BF34" s="417" t="n"/>
+      <c r="BG34" s="417" t="n"/>
+      <c r="BH34" s="417" t="n"/>
+      <c r="BI34" s="417" t="n"/>
+      <c r="BJ34" s="417" t="n"/>
+      <c r="BK34" s="417" t="n"/>
+      <c r="BL34" s="417" t="n"/>
+      <c r="BM34" s="417" t="n"/>
+      <c r="BN34" s="417" t="n"/>
+      <c r="BO34" s="417" t="n"/>
+      <c r="BP34" s="417" t="n"/>
+      <c r="BQ34" s="417" t="n"/>
+      <c r="BR34" s="417" t="n"/>
+      <c r="BS34" s="417" t="n"/>
+      <c r="BT34" s="417" t="n"/>
+      <c r="BU34" s="417" t="n"/>
+      <c r="BV34" s="417" t="n"/>
+      <c r="BW34" s="417" t="n"/>
+      <c r="BX34" s="417" t="n"/>
+      <c r="BY34" s="417" t="n"/>
+      <c r="BZ34" s="417" t="n"/>
+      <c r="CA34" s="417" t="n"/>
+      <c r="CB34" s="417" t="n"/>
+      <c r="CC34" s="417" t="n"/>
+      <c r="CD34" s="418" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -6782,7 +7062,7 @@
     <col width="2.33" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="321" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -6799,7 +7079,7 @@
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="227" t="inlineStr">
+      <c r="Q1" s="426" t="inlineStr">
         <is>
           <t>PFMEA LITE — ACTION TRACKER</t>
         </is>
@@ -6848,7 +7128,7 @@
       <c r="BG1" s="2" t="n"/>
       <c r="BH1" s="2" t="n"/>
       <c r="BI1" s="2" t="n"/>
-      <c r="BJ1" s="2" t="n"/>
+      <c r="BJ1" s="3" t="n"/>
       <c r="BK1" s="322" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6879,375 +7159,548 @@
       <c r="CD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="BK2" s="325" t="inlineStr">
+      <c r="A2" s="390" t="n"/>
+      <c r="B2" s="391" t="n"/>
+      <c r="C2" s="391" t="n"/>
+      <c r="D2" s="391" t="n"/>
+      <c r="E2" s="391" t="n"/>
+      <c r="F2" s="391" t="n"/>
+      <c r="G2" s="391" t="n"/>
+      <c r="H2" s="391" t="n"/>
+      <c r="I2" s="391" t="n"/>
+      <c r="J2" s="391" t="n"/>
+      <c r="K2" s="391" t="n"/>
+      <c r="L2" s="391" t="n"/>
+      <c r="M2" s="391" t="n"/>
+      <c r="N2" s="391" t="n"/>
+      <c r="O2" s="391" t="n"/>
+      <c r="P2" s="392" t="n"/>
+      <c r="Q2" s="391" t="n"/>
+      <c r="R2" s="391" t="n"/>
+      <c r="S2" s="391" t="n"/>
+      <c r="T2" s="391" t="n"/>
+      <c r="U2" s="391" t="n"/>
+      <c r="V2" s="391" t="n"/>
+      <c r="W2" s="391" t="n"/>
+      <c r="X2" s="391" t="n"/>
+      <c r="Y2" s="391" t="n"/>
+      <c r="Z2" s="391" t="n"/>
+      <c r="AA2" s="391" t="n"/>
+      <c r="AB2" s="391" t="n"/>
+      <c r="AC2" s="391" t="n"/>
+      <c r="AD2" s="391" t="n"/>
+      <c r="AE2" s="391" t="n"/>
+      <c r="AF2" s="391" t="n"/>
+      <c r="AG2" s="391" t="n"/>
+      <c r="AH2" s="391" t="n"/>
+      <c r="AI2" s="391" t="n"/>
+      <c r="AJ2" s="391" t="n"/>
+      <c r="AK2" s="391" t="n"/>
+      <c r="AL2" s="391" t="n"/>
+      <c r="AM2" s="391" t="n"/>
+      <c r="AN2" s="391" t="n"/>
+      <c r="AO2" s="391" t="n"/>
+      <c r="AP2" s="391" t="n"/>
+      <c r="AQ2" s="391" t="n"/>
+      <c r="AR2" s="391" t="n"/>
+      <c r="AS2" s="391" t="n"/>
+      <c r="AT2" s="391" t="n"/>
+      <c r="AU2" s="391" t="n"/>
+      <c r="AV2" s="391" t="n"/>
+      <c r="AW2" s="391" t="n"/>
+      <c r="AX2" s="391" t="n"/>
+      <c r="AY2" s="391" t="n"/>
+      <c r="AZ2" s="391" t="n"/>
+      <c r="BA2" s="391" t="n"/>
+      <c r="BB2" s="391" t="n"/>
+      <c r="BC2" s="391" t="n"/>
+      <c r="BD2" s="391" t="n"/>
+      <c r="BE2" s="391" t="n"/>
+      <c r="BF2" s="391" t="n"/>
+      <c r="BG2" s="391" t="n"/>
+      <c r="BH2" s="391" t="n"/>
+      <c r="BI2" s="391" t="n"/>
+      <c r="BJ2" s="392" t="n"/>
+      <c r="BK2" s="393" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="BL2" s="326" t="n"/>
-      <c r="BM2" s="326" t="n"/>
-      <c r="BN2" s="326" t="n"/>
-      <c r="BO2" s="326" t="n"/>
-      <c r="BP2" s="326" t="n"/>
-      <c r="BQ2" s="326" t="n"/>
-      <c r="BR2" s="327" t="n"/>
-      <c r="BS2" s="328" t="inlineStr">
+      <c r="BL2" s="394" t="n"/>
+      <c r="BM2" s="394" t="n"/>
+      <c r="BN2" s="394" t="n"/>
+      <c r="BO2" s="394" t="n"/>
+      <c r="BP2" s="394" t="n"/>
+      <c r="BQ2" s="394" t="n"/>
+      <c r="BR2" s="395" t="n"/>
+      <c r="BS2" s="396" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="BT2" s="326" t="n"/>
-      <c r="BU2" s="326" t="n"/>
-      <c r="BV2" s="326" t="n"/>
-      <c r="BW2" s="326" t="n"/>
-      <c r="BX2" s="326" t="n"/>
-      <c r="BY2" s="326" t="n"/>
-      <c r="BZ2" s="326" t="n"/>
-      <c r="CA2" s="326" t="n"/>
-      <c r="CB2" s="326" t="n"/>
-      <c r="CC2" s="326" t="n"/>
-      <c r="CD2" s="329" t="n"/>
+      <c r="BT2" s="397" t="n"/>
+      <c r="BU2" s="397" t="n"/>
+      <c r="BV2" s="397" t="n"/>
+      <c r="BW2" s="397" t="n"/>
+      <c r="BX2" s="397" t="n"/>
+      <c r="BY2" s="397" t="n"/>
+      <c r="BZ2" s="397" t="n"/>
+      <c r="CA2" s="397" t="n"/>
+      <c r="CB2" s="397" t="n"/>
+      <c r="CC2" s="397" t="n"/>
+      <c r="CD2" s="398" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="P3" s="11" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="BK3" s="325" t="inlineStr">
+      <c r="A3" s="399" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="54" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="400" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
+      <c r="Z3" s="54" t="n"/>
+      <c r="AA3" s="54" t="n"/>
+      <c r="AB3" s="54" t="n"/>
+      <c r="AC3" s="54" t="n"/>
+      <c r="AD3" s="54" t="n"/>
+      <c r="AE3" s="54" t="n"/>
+      <c r="AF3" s="54" t="n"/>
+      <c r="AG3" s="54" t="n"/>
+      <c r="AH3" s="54" t="n"/>
+      <c r="AI3" s="54" t="n"/>
+      <c r="AJ3" s="54" t="n"/>
+      <c r="AK3" s="54" t="n"/>
+      <c r="AL3" s="54" t="n"/>
+      <c r="AM3" s="54" t="n"/>
+      <c r="AN3" s="54" t="n"/>
+      <c r="AO3" s="54" t="n"/>
+      <c r="AP3" s="54" t="n"/>
+      <c r="AQ3" s="54" t="n"/>
+      <c r="AR3" s="54" t="n"/>
+      <c r="AS3" s="54" t="n"/>
+      <c r="AT3" s="54" t="n"/>
+      <c r="AU3" s="54" t="n"/>
+      <c r="AV3" s="54" t="n"/>
+      <c r="AW3" s="54" t="n"/>
+      <c r="AX3" s="54" t="n"/>
+      <c r="AY3" s="54" t="n"/>
+      <c r="AZ3" s="54" t="n"/>
+      <c r="BA3" s="54" t="n"/>
+      <c r="BB3" s="54" t="n"/>
+      <c r="BC3" s="54" t="n"/>
+      <c r="BD3" s="54" t="n"/>
+      <c r="BE3" s="54" t="n"/>
+      <c r="BF3" s="54" t="n"/>
+      <c r="BG3" s="54" t="n"/>
+      <c r="BH3" s="54" t="n"/>
+      <c r="BI3" s="54" t="n"/>
+      <c r="BJ3" s="400" t="n"/>
+      <c r="BK3" s="401" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="BL3" s="326" t="n"/>
-      <c r="BM3" s="326" t="n"/>
-      <c r="BN3" s="326" t="n"/>
-      <c r="BO3" s="326" t="n"/>
-      <c r="BP3" s="326" t="n"/>
-      <c r="BQ3" s="326" t="n"/>
-      <c r="BR3" s="327" t="n"/>
-      <c r="BS3" s="328" t="inlineStr">
+      <c r="BL3" s="402" t="n"/>
+      <c r="BM3" s="402" t="n"/>
+      <c r="BN3" s="402" t="n"/>
+      <c r="BO3" s="402" t="n"/>
+      <c r="BP3" s="402" t="n"/>
+      <c r="BQ3" s="402" t="n"/>
+      <c r="BR3" s="403" t="n"/>
+      <c r="BS3" s="297" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="BT3" s="326" t="n"/>
-      <c r="BU3" s="326" t="n"/>
-      <c r="BV3" s="326" t="n"/>
-      <c r="BW3" s="326" t="n"/>
-      <c r="BX3" s="326" t="n"/>
-      <c r="BY3" s="326" t="n"/>
-      <c r="BZ3" s="326" t="n"/>
-      <c r="CA3" s="326" t="n"/>
-      <c r="CB3" s="326" t="n"/>
-      <c r="CC3" s="326" t="n"/>
-      <c r="CD3" s="329" t="n"/>
+      <c r="BT3" s="404" t="n"/>
+      <c r="BU3" s="404" t="n"/>
+      <c r="BV3" s="404" t="n"/>
+      <c r="BW3" s="404" t="n"/>
+      <c r="BX3" s="404" t="n"/>
+      <c r="BY3" s="404" t="n"/>
+      <c r="BZ3" s="404" t="n"/>
+      <c r="CA3" s="404" t="n"/>
+      <c r="CB3" s="404" t="n"/>
+      <c r="CC3" s="404" t="n"/>
+      <c r="CD3" s="405" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="P4" s="11" t="n"/>
-      <c r="Q4" s="239" t="inlineStr">
+      <c r="A4" s="399" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="n"/>
+      <c r="L4" s="54" t="n"/>
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="400" t="n"/>
+      <c r="Q4" s="406" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="BK4" s="325" t="inlineStr">
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="54" t="n"/>
+      <c r="AD4" s="54" t="n"/>
+      <c r="AE4" s="54" t="n"/>
+      <c r="AF4" s="54" t="n"/>
+      <c r="AG4" s="54" t="n"/>
+      <c r="AH4" s="54" t="n"/>
+      <c r="AI4" s="54" t="n"/>
+      <c r="AJ4" s="54" t="n"/>
+      <c r="AK4" s="54" t="n"/>
+      <c r="AL4" s="54" t="n"/>
+      <c r="AM4" s="54" t="n"/>
+      <c r="AN4" s="54" t="n"/>
+      <c r="AO4" s="54" t="n"/>
+      <c r="AP4" s="54" t="n"/>
+      <c r="AQ4" s="54" t="n"/>
+      <c r="AR4" s="54" t="n"/>
+      <c r="AS4" s="54" t="n"/>
+      <c r="AT4" s="54" t="n"/>
+      <c r="AU4" s="54" t="n"/>
+      <c r="AV4" s="54" t="n"/>
+      <c r="AW4" s="54" t="n"/>
+      <c r="AX4" s="54" t="n"/>
+      <c r="AY4" s="54" t="n"/>
+      <c r="AZ4" s="54" t="n"/>
+      <c r="BA4" s="54" t="n"/>
+      <c r="BB4" s="54" t="n"/>
+      <c r="BC4" s="54" t="n"/>
+      <c r="BD4" s="54" t="n"/>
+      <c r="BE4" s="54" t="n"/>
+      <c r="BF4" s="54" t="n"/>
+      <c r="BG4" s="54" t="n"/>
+      <c r="BH4" s="54" t="n"/>
+      <c r="BI4" s="54" t="n"/>
+      <c r="BJ4" s="400" t="n"/>
+      <c r="BK4" s="401" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="BL4" s="326" t="n"/>
-      <c r="BM4" s="326" t="n"/>
-      <c r="BN4" s="326" t="n"/>
-      <c r="BO4" s="326" t="n"/>
-      <c r="BP4" s="326" t="n"/>
-      <c r="BQ4" s="326" t="n"/>
-      <c r="BR4" s="327" t="n"/>
-      <c r="BS4" s="328" t="inlineStr">
+      <c r="BL4" s="402" t="n"/>
+      <c r="BM4" s="402" t="n"/>
+      <c r="BN4" s="402" t="n"/>
+      <c r="BO4" s="402" t="n"/>
+      <c r="BP4" s="402" t="n"/>
+      <c r="BQ4" s="402" t="n"/>
+      <c r="BR4" s="403" t="n"/>
+      <c r="BS4" s="297" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="BT4" s="326" t="n"/>
-      <c r="BU4" s="326" t="n"/>
-      <c r="BV4" s="326" t="n"/>
-      <c r="BW4" s="326" t="n"/>
-      <c r="BX4" s="326" t="n"/>
-      <c r="BY4" s="326" t="n"/>
-      <c r="BZ4" s="326" t="n"/>
-      <c r="CA4" s="326" t="n"/>
-      <c r="CB4" s="326" t="n"/>
-      <c r="CC4" s="326" t="n"/>
-      <c r="CD4" s="329" t="n"/>
+      <c r="BT4" s="404" t="n"/>
+      <c r="BU4" s="404" t="n"/>
+      <c r="BV4" s="404" t="n"/>
+      <c r="BW4" s="404" t="n"/>
+      <c r="BX4" s="404" t="n"/>
+      <c r="BY4" s="404" t="n"/>
+      <c r="BZ4" s="404" t="n"/>
+      <c r="CA4" s="404" t="n"/>
+      <c r="CB4" s="404" t="n"/>
+      <c r="CC4" s="404" t="n"/>
+      <c r="CD4" s="405" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="17" t="n"/>
-      <c r="L5" s="17" t="n"/>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="18" t="n"/>
-      <c r="Q5" s="50" t="inlineStr">
+      <c r="A5" s="399" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="54" t="n"/>
+      <c r="L5" s="54" t="n"/>
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="400" t="n"/>
+      <c r="Q5" s="407" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="17" t="n"/>
-      <c r="AR5" s="17" t="n"/>
-      <c r="AS5" s="17" t="n"/>
-      <c r="AT5" s="17" t="n"/>
-      <c r="AU5" s="17" t="n"/>
-      <c r="AV5" s="17" t="n"/>
-      <c r="AW5" s="17" t="n"/>
-      <c r="AX5" s="17" t="n"/>
-      <c r="AY5" s="17" t="n"/>
-      <c r="AZ5" s="17" t="n"/>
-      <c r="BA5" s="17" t="n"/>
-      <c r="BB5" s="17" t="n"/>
-      <c r="BC5" s="17" t="n"/>
-      <c r="BD5" s="17" t="n"/>
-      <c r="BE5" s="17" t="n"/>
-      <c r="BF5" s="17" t="n"/>
-      <c r="BG5" s="17" t="n"/>
-      <c r="BH5" s="17" t="n"/>
-      <c r="BI5" s="17" t="n"/>
-      <c r="BJ5" s="17" t="n"/>
-      <c r="BK5" s="330" t="inlineStr">
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="54" t="n"/>
+      <c r="AB5" s="54" t="n"/>
+      <c r="AC5" s="54" t="n"/>
+      <c r="AD5" s="54" t="n"/>
+      <c r="AE5" s="54" t="n"/>
+      <c r="AF5" s="54" t="n"/>
+      <c r="AG5" s="54" t="n"/>
+      <c r="AH5" s="54" t="n"/>
+      <c r="AI5" s="54" t="n"/>
+      <c r="AJ5" s="54" t="n"/>
+      <c r="AK5" s="54" t="n"/>
+      <c r="AL5" s="54" t="n"/>
+      <c r="AM5" s="54" t="n"/>
+      <c r="AN5" s="54" t="n"/>
+      <c r="AO5" s="54" t="n"/>
+      <c r="AP5" s="54" t="n"/>
+      <c r="AQ5" s="54" t="n"/>
+      <c r="AR5" s="54" t="n"/>
+      <c r="AS5" s="54" t="n"/>
+      <c r="AT5" s="54" t="n"/>
+      <c r="AU5" s="54" t="n"/>
+      <c r="AV5" s="54" t="n"/>
+      <c r="AW5" s="54" t="n"/>
+      <c r="AX5" s="54" t="n"/>
+      <c r="AY5" s="54" t="n"/>
+      <c r="AZ5" s="54" t="n"/>
+      <c r="BA5" s="54" t="n"/>
+      <c r="BB5" s="54" t="n"/>
+      <c r="BC5" s="54" t="n"/>
+      <c r="BD5" s="54" t="n"/>
+      <c r="BE5" s="54" t="n"/>
+      <c r="BF5" s="54" t="n"/>
+      <c r="BG5" s="54" t="n"/>
+      <c r="BH5" s="54" t="n"/>
+      <c r="BI5" s="54" t="n"/>
+      <c r="BJ5" s="400" t="n"/>
+      <c r="BK5" s="401" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="BL5" s="331" t="n"/>
-      <c r="BM5" s="331" t="n"/>
-      <c r="BN5" s="331" t="n"/>
-      <c r="BO5" s="331" t="n"/>
-      <c r="BP5" s="331" t="n"/>
-      <c r="BQ5" s="331" t="n"/>
-      <c r="BR5" s="332" t="n"/>
-      <c r="BS5" s="333" t="inlineStr">
+      <c r="BL5" s="402" t="n"/>
+      <c r="BM5" s="402" t="n"/>
+      <c r="BN5" s="402" t="n"/>
+      <c r="BO5" s="402" t="n"/>
+      <c r="BP5" s="402" t="n"/>
+      <c r="BQ5" s="402" t="n"/>
+      <c r="BR5" s="403" t="n"/>
+      <c r="BS5" s="297" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="BT5" s="331" t="n"/>
-      <c r="BU5" s="331" t="n"/>
-      <c r="BV5" s="331" t="n"/>
-      <c r="BW5" s="331" t="n"/>
-      <c r="BX5" s="331" t="n"/>
-      <c r="BY5" s="331" t="n"/>
-      <c r="BZ5" s="331" t="n"/>
-      <c r="CA5" s="331" t="n"/>
-      <c r="CB5" s="331" t="n"/>
-      <c r="CC5" s="331" t="n"/>
-      <c r="CD5" s="334" t="n"/>
+      <c r="BT5" s="404" t="n"/>
+      <c r="BU5" s="404" t="n"/>
+      <c r="BV5" s="404" t="n"/>
+      <c r="BW5" s="404" t="n"/>
+      <c r="BX5" s="404" t="n"/>
+      <c r="BY5" s="404" t="n"/>
+      <c r="BZ5" s="404" t="n"/>
+      <c r="CA5" s="404" t="n"/>
+      <c r="CB5" s="404" t="n"/>
+      <c r="CC5" s="404" t="n"/>
+      <c r="CD5" s="405" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="248" t="n"/>
-      <c r="B6" s="248" t="n"/>
-      <c r="C6" s="248" t="n"/>
-      <c r="D6" s="248" t="n"/>
-      <c r="E6" s="248" t="n"/>
-      <c r="F6" s="248" t="n"/>
-      <c r="G6" s="248" t="n"/>
-      <c r="H6" s="248" t="n"/>
-      <c r="I6" s="248" t="n"/>
-      <c r="J6" s="248" t="n"/>
-      <c r="K6" s="248" t="n"/>
-      <c r="L6" s="248" t="n"/>
-      <c r="M6" s="248" t="n"/>
-      <c r="N6" s="248" t="n"/>
-      <c r="O6" s="248" t="n"/>
-      <c r="P6" s="248" t="n"/>
-      <c r="Q6" s="248" t="n"/>
-      <c r="R6" s="248" t="n"/>
-      <c r="S6" s="248" t="n"/>
-      <c r="T6" s="248" t="n"/>
-      <c r="U6" s="248" t="n"/>
-      <c r="V6" s="248" t="n"/>
-      <c r="W6" s="248" t="n"/>
-      <c r="X6" s="248" t="n"/>
-      <c r="Y6" s="248" t="n"/>
-      <c r="Z6" s="248" t="n"/>
-      <c r="AA6" s="248" t="n"/>
-      <c r="AB6" s="248" t="n"/>
-      <c r="AC6" s="248" t="n"/>
-      <c r="AD6" s="248" t="n"/>
-      <c r="AE6" s="248" t="n"/>
-      <c r="AF6" s="248" t="n"/>
-      <c r="AG6" s="248" t="n"/>
-      <c r="AH6" s="248" t="n"/>
-      <c r="AI6" s="248" t="n"/>
-      <c r="AJ6" s="248" t="n"/>
-      <c r="AK6" s="248" t="n"/>
-      <c r="AL6" s="248" t="n"/>
-      <c r="AM6" s="248" t="n"/>
-      <c r="AN6" s="248" t="n"/>
-      <c r="AO6" s="248" t="n"/>
-      <c r="AP6" s="248" t="n"/>
-      <c r="AQ6" s="248" t="n"/>
-      <c r="AR6" s="248" t="n"/>
-      <c r="AS6" s="248" t="n"/>
-      <c r="AT6" s="248" t="n"/>
-      <c r="AU6" s="248" t="n"/>
-      <c r="AV6" s="248" t="n"/>
-      <c r="AW6" s="248" t="n"/>
-      <c r="AX6" s="248" t="n"/>
-      <c r="AY6" s="248" t="n"/>
-      <c r="AZ6" s="248" t="n"/>
-      <c r="BA6" s="248" t="n"/>
-      <c r="BB6" s="248" t="n"/>
-      <c r="BC6" s="248" t="n"/>
-      <c r="BD6" s="248" t="n"/>
-      <c r="BE6" s="248" t="n"/>
-      <c r="BF6" s="248" t="n"/>
-      <c r="BG6" s="248" t="n"/>
-      <c r="BH6" s="248" t="n"/>
-      <c r="BI6" s="248" t="n"/>
-      <c r="BJ6" s="248" t="n"/>
-      <c r="BK6" s="248" t="n"/>
-      <c r="BL6" s="248" t="n"/>
-      <c r="BM6" s="248" t="n"/>
-      <c r="BN6" s="248" t="n"/>
-      <c r="BO6" s="248" t="n"/>
-      <c r="BP6" s="248" t="n"/>
-      <c r="BQ6" s="248" t="n"/>
-      <c r="BR6" s="248" t="n"/>
-      <c r="BS6" s="248" t="n"/>
-      <c r="BT6" s="248" t="n"/>
-      <c r="BU6" s="248" t="n"/>
-      <c r="BV6" s="248" t="n"/>
-      <c r="BW6" s="248" t="n"/>
-      <c r="BX6" s="248" t="n"/>
-      <c r="BY6" s="248" t="n"/>
-      <c r="BZ6" s="248" t="n"/>
-      <c r="CA6" s="248" t="n"/>
-      <c r="CB6" s="248" t="n"/>
-      <c r="CC6" s="248" t="n"/>
-      <c r="CD6" s="248" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="408" t="n"/>
+      <c r="B6" s="409" t="n"/>
+      <c r="C6" s="409" t="n"/>
+      <c r="D6" s="409" t="n"/>
+      <c r="E6" s="409" t="n"/>
+      <c r="F6" s="409" t="n"/>
+      <c r="G6" s="409" t="n"/>
+      <c r="H6" s="409" t="n"/>
+      <c r="I6" s="409" t="n"/>
+      <c r="J6" s="409" t="n"/>
+      <c r="K6" s="409" t="n"/>
+      <c r="L6" s="409" t="n"/>
+      <c r="M6" s="409" t="n"/>
+      <c r="N6" s="409" t="n"/>
+      <c r="O6" s="409" t="n"/>
+      <c r="P6" s="410" t="n"/>
+      <c r="Q6" s="409" t="n"/>
+      <c r="R6" s="409" t="n"/>
+      <c r="S6" s="409" t="n"/>
+      <c r="T6" s="409" t="n"/>
+      <c r="U6" s="409" t="n"/>
+      <c r="V6" s="409" t="n"/>
+      <c r="W6" s="409" t="n"/>
+      <c r="X6" s="409" t="n"/>
+      <c r="Y6" s="409" t="n"/>
+      <c r="Z6" s="409" t="n"/>
+      <c r="AA6" s="409" t="n"/>
+      <c r="AB6" s="409" t="n"/>
+      <c r="AC6" s="409" t="n"/>
+      <c r="AD6" s="409" t="n"/>
+      <c r="AE6" s="409" t="n"/>
+      <c r="AF6" s="409" t="n"/>
+      <c r="AG6" s="409" t="n"/>
+      <c r="AH6" s="409" t="n"/>
+      <c r="AI6" s="409" t="n"/>
+      <c r="AJ6" s="409" t="n"/>
+      <c r="AK6" s="409" t="n"/>
+      <c r="AL6" s="409" t="n"/>
+      <c r="AM6" s="409" t="n"/>
+      <c r="AN6" s="409" t="n"/>
+      <c r="AO6" s="409" t="n"/>
+      <c r="AP6" s="409" t="n"/>
+      <c r="AQ6" s="409" t="n"/>
+      <c r="AR6" s="409" t="n"/>
+      <c r="AS6" s="409" t="n"/>
+      <c r="AT6" s="409" t="n"/>
+      <c r="AU6" s="409" t="n"/>
+      <c r="AV6" s="409" t="n"/>
+      <c r="AW6" s="409" t="n"/>
+      <c r="AX6" s="409" t="n"/>
+      <c r="AY6" s="409" t="n"/>
+      <c r="AZ6" s="409" t="n"/>
+      <c r="BA6" s="409" t="n"/>
+      <c r="BB6" s="409" t="n"/>
+      <c r="BC6" s="409" t="n"/>
+      <c r="BD6" s="409" t="n"/>
+      <c r="BE6" s="409" t="n"/>
+      <c r="BF6" s="409" t="n"/>
+      <c r="BG6" s="409" t="n"/>
+      <c r="BH6" s="409" t="n"/>
+      <c r="BI6" s="409" t="n"/>
+      <c r="BJ6" s="410" t="n"/>
+      <c r="BK6" s="411" t="n"/>
+      <c r="BL6" s="411" t="n"/>
+      <c r="BM6" s="411" t="n"/>
+      <c r="BN6" s="411" t="n"/>
+      <c r="BO6" s="411" t="n"/>
+      <c r="BP6" s="411" t="n"/>
+      <c r="BQ6" s="411" t="n"/>
+      <c r="BR6" s="412" t="n"/>
+      <c r="BS6" s="413" t="n"/>
+      <c r="BT6" s="413" t="n"/>
+      <c r="BU6" s="413" t="n"/>
+      <c r="BV6" s="413" t="n"/>
+      <c r="BW6" s="413" t="n"/>
+      <c r="BX6" s="413" t="n"/>
+      <c r="BY6" s="413" t="n"/>
+      <c r="BZ6" s="413" t="n"/>
+      <c r="CA6" s="413" t="n"/>
+      <c r="CB6" s="413" t="n"/>
+      <c r="CC6" s="413" t="n"/>
+      <c r="CD6" s="414" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="22" t="n"/>
-      <c r="BE7" s="22" t="n"/>
-      <c r="BF7" s="22" t="n"/>
-      <c r="BG7" s="22" t="n"/>
-      <c r="BH7" s="22" t="n"/>
-      <c r="BI7" s="22" t="n"/>
-      <c r="BJ7" s="22" t="n"/>
-      <c r="BK7" s="22" t="n"/>
-      <c r="BL7" s="22" t="n"/>
-      <c r="BM7" s="22" t="n"/>
-      <c r="BN7" s="22" t="n"/>
-      <c r="BO7" s="22" t="n"/>
-      <c r="BP7" s="22" t="n"/>
-      <c r="BQ7" s="22" t="n"/>
-      <c r="BR7" s="22" t="n"/>
-      <c r="BS7" s="22" t="n"/>
-      <c r="BT7" s="22" t="n"/>
-      <c r="BU7" s="22" t="n"/>
-      <c r="BV7" s="22" t="n"/>
-      <c r="BW7" s="22" t="n"/>
-      <c r="BX7" s="22" t="n"/>
-      <c r="BY7" s="22" t="n"/>
-      <c r="BZ7" s="22" t="n"/>
-      <c r="CA7" s="22" t="n"/>
-      <c r="CB7" s="22" t="n"/>
-      <c r="CC7" s="22" t="n"/>
-      <c r="CD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="415" t="n"/>
+      <c r="B7" s="416" t="n"/>
+      <c r="C7" s="416" t="n"/>
+      <c r="D7" s="416" t="n"/>
+      <c r="E7" s="416" t="n"/>
+      <c r="F7" s="416" t="n"/>
+      <c r="G7" s="416" t="n"/>
+      <c r="H7" s="416" t="n"/>
+      <c r="I7" s="416" t="n"/>
+      <c r="J7" s="416" t="n"/>
+      <c r="K7" s="416" t="n"/>
+      <c r="L7" s="416" t="n"/>
+      <c r="M7" s="416" t="n"/>
+      <c r="N7" s="416" t="n"/>
+      <c r="O7" s="416" t="n"/>
+      <c r="P7" s="416" t="n"/>
+      <c r="Q7" s="416" t="n"/>
+      <c r="R7" s="416" t="n"/>
+      <c r="S7" s="416" t="n"/>
+      <c r="T7" s="416" t="n"/>
+      <c r="U7" s="416" t="n"/>
+      <c r="V7" s="416" t="n"/>
+      <c r="W7" s="416" t="n"/>
+      <c r="X7" s="416" t="n"/>
+      <c r="Y7" s="416" t="n"/>
+      <c r="Z7" s="416" t="n"/>
+      <c r="AA7" s="416" t="n"/>
+      <c r="AB7" s="416" t="n"/>
+      <c r="AC7" s="416" t="n"/>
+      <c r="AD7" s="416" t="n"/>
+      <c r="AE7" s="416" t="n"/>
+      <c r="AF7" s="416" t="n"/>
+      <c r="AG7" s="416" t="n"/>
+      <c r="AH7" s="416" t="n"/>
+      <c r="AI7" s="416" t="n"/>
+      <c r="AJ7" s="416" t="n"/>
+      <c r="AK7" s="416" t="n"/>
+      <c r="AL7" s="416" t="n"/>
+      <c r="AM7" s="416" t="n"/>
+      <c r="AN7" s="416" t="n"/>
+      <c r="AO7" s="416" t="n"/>
+      <c r="AP7" s="416" t="n"/>
+      <c r="AQ7" s="416" t="n"/>
+      <c r="AR7" s="416" t="n"/>
+      <c r="AS7" s="416" t="n"/>
+      <c r="AT7" s="416" t="n"/>
+      <c r="AU7" s="416" t="n"/>
+      <c r="AV7" s="416" t="n"/>
+      <c r="AW7" s="416" t="n"/>
+      <c r="AX7" s="416" t="n"/>
+      <c r="AY7" s="416" t="n"/>
+      <c r="AZ7" s="416" t="n"/>
+      <c r="BA7" s="416" t="n"/>
+      <c r="BB7" s="416" t="n"/>
+      <c r="BC7" s="416" t="n"/>
+      <c r="BD7" s="416" t="n"/>
+      <c r="BE7" s="416" t="n"/>
+      <c r="BF7" s="416" t="n"/>
+      <c r="BG7" s="416" t="n"/>
+      <c r="BH7" s="416" t="n"/>
+      <c r="BI7" s="416" t="n"/>
+      <c r="BJ7" s="416" t="n"/>
+      <c r="BK7" s="416" t="n"/>
+      <c r="BL7" s="416" t="n"/>
+      <c r="BM7" s="416" t="n"/>
+      <c r="BN7" s="416" t="n"/>
+      <c r="BO7" s="416" t="n"/>
+      <c r="BP7" s="416" t="n"/>
+      <c r="BQ7" s="416" t="n"/>
+      <c r="BR7" s="416" t="n"/>
+      <c r="BS7" s="416" t="n"/>
+      <c r="BT7" s="416" t="n"/>
+      <c r="BU7" s="416" t="n"/>
+      <c r="BV7" s="416" t="n"/>
+      <c r="BW7" s="416" t="n"/>
+      <c r="BX7" s="416" t="n"/>
+      <c r="BY7" s="416" t="n"/>
+      <c r="BZ7" s="416" t="n"/>
+      <c r="CA7" s="416" t="n"/>
+      <c r="CB7" s="416" t="n"/>
+      <c r="CC7" s="416" t="n"/>
+      <c r="CD7" s="416" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="336" t="inlineStr">
@@ -8230,92 +8683,92 @@
       <c r="CD18" s="350" t="n"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="384" t="inlineStr">
+      <c r="A19" s="311" t="inlineStr">
         <is>
           <t>NOTICE: Use one row per action. Record issue, owner, due date, status and verification evidence; do not close actions without objective evidence.</t>
         </is>
       </c>
-      <c r="B19" s="385" t="n"/>
-      <c r="C19" s="385" t="n"/>
-      <c r="D19" s="385" t="n"/>
-      <c r="E19" s="385" t="n"/>
-      <c r="F19" s="385" t="n"/>
-      <c r="G19" s="385" t="n"/>
-      <c r="H19" s="385" t="n"/>
-      <c r="I19" s="385" t="n"/>
-      <c r="J19" s="385" t="n"/>
-      <c r="K19" s="385" t="n"/>
-      <c r="L19" s="385" t="n"/>
-      <c r="M19" s="385" t="n"/>
-      <c r="N19" s="385" t="n"/>
-      <c r="O19" s="385" t="n"/>
-      <c r="P19" s="385" t="n"/>
-      <c r="Q19" s="385" t="n"/>
-      <c r="R19" s="385" t="n"/>
-      <c r="S19" s="385" t="n"/>
-      <c r="T19" s="385" t="n"/>
-      <c r="U19" s="385" t="n"/>
-      <c r="V19" s="385" t="n"/>
-      <c r="W19" s="385" t="n"/>
-      <c r="X19" s="385" t="n"/>
-      <c r="Y19" s="385" t="n"/>
-      <c r="Z19" s="385" t="n"/>
-      <c r="AA19" s="385" t="n"/>
-      <c r="AB19" s="385" t="n"/>
-      <c r="AC19" s="385" t="n"/>
-      <c r="AD19" s="385" t="n"/>
-      <c r="AE19" s="385" t="n"/>
-      <c r="AF19" s="385" t="n"/>
-      <c r="AG19" s="385" t="n"/>
-      <c r="AH19" s="385" t="n"/>
-      <c r="AI19" s="385" t="n"/>
-      <c r="AJ19" s="385" t="n"/>
-      <c r="AK19" s="385" t="n"/>
-      <c r="AL19" s="385" t="n"/>
-      <c r="AM19" s="385" t="n"/>
-      <c r="AN19" s="385" t="n"/>
-      <c r="AO19" s="385" t="n"/>
-      <c r="AP19" s="385" t="n"/>
-      <c r="AQ19" s="385" t="n"/>
-      <c r="AR19" s="385" t="n"/>
-      <c r="AS19" s="385" t="n"/>
-      <c r="AT19" s="385" t="n"/>
-      <c r="AU19" s="385" t="n"/>
-      <c r="AV19" s="385" t="n"/>
-      <c r="AW19" s="385" t="n"/>
-      <c r="AX19" s="385" t="n"/>
-      <c r="AY19" s="385" t="n"/>
-      <c r="AZ19" s="385" t="n"/>
-      <c r="BA19" s="385" t="n"/>
-      <c r="BB19" s="385" t="n"/>
-      <c r="BC19" s="385" t="n"/>
-      <c r="BD19" s="385" t="n"/>
-      <c r="BE19" s="385" t="n"/>
-      <c r="BF19" s="385" t="n"/>
-      <c r="BG19" s="385" t="n"/>
-      <c r="BH19" s="385" t="n"/>
-      <c r="BI19" s="385" t="n"/>
-      <c r="BJ19" s="385" t="n"/>
-      <c r="BK19" s="385" t="n"/>
-      <c r="BL19" s="385" t="n"/>
-      <c r="BM19" s="385" t="n"/>
-      <c r="BN19" s="385" t="n"/>
-      <c r="BO19" s="385" t="n"/>
-      <c r="BP19" s="385" t="n"/>
-      <c r="BQ19" s="385" t="n"/>
-      <c r="BR19" s="385" t="n"/>
-      <c r="BS19" s="385" t="n"/>
-      <c r="BT19" s="385" t="n"/>
-      <c r="BU19" s="385" t="n"/>
-      <c r="BV19" s="385" t="n"/>
-      <c r="BW19" s="385" t="n"/>
-      <c r="BX19" s="385" t="n"/>
-      <c r="BY19" s="385" t="n"/>
-      <c r="BZ19" s="385" t="n"/>
-      <c r="CA19" s="385" t="n"/>
-      <c r="CB19" s="385" t="n"/>
-      <c r="CC19" s="385" t="n"/>
-      <c r="CD19" s="386" t="n"/>
+      <c r="B19" s="417" t="n"/>
+      <c r="C19" s="417" t="n"/>
+      <c r="D19" s="417" t="n"/>
+      <c r="E19" s="417" t="n"/>
+      <c r="F19" s="417" t="n"/>
+      <c r="G19" s="417" t="n"/>
+      <c r="H19" s="417" t="n"/>
+      <c r="I19" s="417" t="n"/>
+      <c r="J19" s="417" t="n"/>
+      <c r="K19" s="417" t="n"/>
+      <c r="L19" s="417" t="n"/>
+      <c r="M19" s="417" t="n"/>
+      <c r="N19" s="417" t="n"/>
+      <c r="O19" s="417" t="n"/>
+      <c r="P19" s="417" t="n"/>
+      <c r="Q19" s="417" t="n"/>
+      <c r="R19" s="417" t="n"/>
+      <c r="S19" s="417" t="n"/>
+      <c r="T19" s="417" t="n"/>
+      <c r="U19" s="417" t="n"/>
+      <c r="V19" s="417" t="n"/>
+      <c r="W19" s="417" t="n"/>
+      <c r="X19" s="417" t="n"/>
+      <c r="Y19" s="417" t="n"/>
+      <c r="Z19" s="417" t="n"/>
+      <c r="AA19" s="417" t="n"/>
+      <c r="AB19" s="417" t="n"/>
+      <c r="AC19" s="417" t="n"/>
+      <c r="AD19" s="417" t="n"/>
+      <c r="AE19" s="417" t="n"/>
+      <c r="AF19" s="417" t="n"/>
+      <c r="AG19" s="417" t="n"/>
+      <c r="AH19" s="417" t="n"/>
+      <c r="AI19" s="417" t="n"/>
+      <c r="AJ19" s="417" t="n"/>
+      <c r="AK19" s="417" t="n"/>
+      <c r="AL19" s="417" t="n"/>
+      <c r="AM19" s="417" t="n"/>
+      <c r="AN19" s="417" t="n"/>
+      <c r="AO19" s="417" t="n"/>
+      <c r="AP19" s="417" t="n"/>
+      <c r="AQ19" s="417" t="n"/>
+      <c r="AR19" s="417" t="n"/>
+      <c r="AS19" s="417" t="n"/>
+      <c r="AT19" s="417" t="n"/>
+      <c r="AU19" s="417" t="n"/>
+      <c r="AV19" s="417" t="n"/>
+      <c r="AW19" s="417" t="n"/>
+      <c r="AX19" s="417" t="n"/>
+      <c r="AY19" s="417" t="n"/>
+      <c r="AZ19" s="417" t="n"/>
+      <c r="BA19" s="417" t="n"/>
+      <c r="BB19" s="417" t="n"/>
+      <c r="BC19" s="417" t="n"/>
+      <c r="BD19" s="417" t="n"/>
+      <c r="BE19" s="417" t="n"/>
+      <c r="BF19" s="417" t="n"/>
+      <c r="BG19" s="417" t="n"/>
+      <c r="BH19" s="417" t="n"/>
+      <c r="BI19" s="417" t="n"/>
+      <c r="BJ19" s="417" t="n"/>
+      <c r="BK19" s="417" t="n"/>
+      <c r="BL19" s="417" t="n"/>
+      <c r="BM19" s="417" t="n"/>
+      <c r="BN19" s="417" t="n"/>
+      <c r="BO19" s="417" t="n"/>
+      <c r="BP19" s="417" t="n"/>
+      <c r="BQ19" s="417" t="n"/>
+      <c r="BR19" s="417" t="n"/>
+      <c r="BS19" s="417" t="n"/>
+      <c r="BT19" s="417" t="n"/>
+      <c r="BU19" s="417" t="n"/>
+      <c r="BV19" s="417" t="n"/>
+      <c r="BW19" s="417" t="n"/>
+      <c r="BX19" s="417" t="n"/>
+      <c r="BY19" s="417" t="n"/>
+      <c r="BZ19" s="417" t="n"/>
+      <c r="CA19" s="417" t="n"/>
+      <c r="CB19" s="417" t="n"/>
+      <c r="CC19" s="417" t="n"/>
+      <c r="CD19" s="418" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
@@ -8489,7 +8942,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="321" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -8501,7 +8954,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="302" t="inlineStr">
+      <c r="L1" s="427" t="inlineStr">
         <is>
           <t>PFMEA LITE — CONTROLLED LOOKUP LISTS</t>
         </is>
@@ -8535,7 +8988,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="378" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -8560,286 +9013,454 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="10" t="n"/>
-      <c r="K2" s="11" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="AQ2" s="380" t="inlineStr">
+      <c r="A2" s="390" t="n"/>
+      <c r="B2" s="391" t="n"/>
+      <c r="C2" s="391" t="n"/>
+      <c r="D2" s="391" t="n"/>
+      <c r="E2" s="391" t="n"/>
+      <c r="F2" s="391" t="n"/>
+      <c r="G2" s="391" t="n"/>
+      <c r="H2" s="391" t="n"/>
+      <c r="I2" s="391" t="n"/>
+      <c r="J2" s="391" t="n"/>
+      <c r="K2" s="392" t="n"/>
+      <c r="L2" s="391" t="n"/>
+      <c r="M2" s="391" t="n"/>
+      <c r="N2" s="391" t="n"/>
+      <c r="O2" s="391" t="n"/>
+      <c r="P2" s="391" t="n"/>
+      <c r="Q2" s="391" t="n"/>
+      <c r="R2" s="391" t="n"/>
+      <c r="S2" s="391" t="n"/>
+      <c r="T2" s="391" t="n"/>
+      <c r="U2" s="391" t="n"/>
+      <c r="V2" s="391" t="n"/>
+      <c r="W2" s="391" t="n"/>
+      <c r="X2" s="391" t="n"/>
+      <c r="Y2" s="391" t="n"/>
+      <c r="Z2" s="391" t="n"/>
+      <c r="AA2" s="391" t="n"/>
+      <c r="AB2" s="391" t="n"/>
+      <c r="AC2" s="391" t="n"/>
+      <c r="AD2" s="391" t="n"/>
+      <c r="AE2" s="391" t="n"/>
+      <c r="AF2" s="391" t="n"/>
+      <c r="AG2" s="391" t="n"/>
+      <c r="AH2" s="391" t="n"/>
+      <c r="AI2" s="391" t="n"/>
+      <c r="AJ2" s="391" t="n"/>
+      <c r="AK2" s="391" t="n"/>
+      <c r="AL2" s="391" t="n"/>
+      <c r="AM2" s="391" t="n"/>
+      <c r="AN2" s="391" t="n"/>
+      <c r="AO2" s="391" t="n"/>
+      <c r="AP2" s="392" t="n"/>
+      <c r="AQ2" s="393" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="326" t="n"/>
-      <c r="AS2" s="326" t="n"/>
-      <c r="AT2" s="326" t="n"/>
-      <c r="AU2" s="326" t="n"/>
-      <c r="AV2" s="327" t="n"/>
-      <c r="AW2" s="381" t="inlineStr">
+      <c r="AR2" s="394" t="n"/>
+      <c r="AS2" s="394" t="n"/>
+      <c r="AT2" s="394" t="n"/>
+      <c r="AU2" s="394" t="n"/>
+      <c r="AV2" s="395" t="n"/>
+      <c r="AW2" s="396" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="326" t="n"/>
-      <c r="AY2" s="326" t="n"/>
-      <c r="AZ2" s="326" t="n"/>
-      <c r="BA2" s="326" t="n"/>
-      <c r="BB2" s="326" t="n"/>
-      <c r="BC2" s="326" t="n"/>
-      <c r="BD2" s="329" t="n"/>
+      <c r="AX2" s="397" t="n"/>
+      <c r="AY2" s="397" t="n"/>
+      <c r="AZ2" s="397" t="n"/>
+      <c r="BA2" s="397" t="n"/>
+      <c r="BB2" s="397" t="n"/>
+      <c r="BC2" s="397" t="n"/>
+      <c r="BD2" s="398" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="10" t="n"/>
-      <c r="K3" s="11" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="AQ3" s="380" t="inlineStr">
+      <c r="A3" s="399" t="n"/>
+      <c r="B3" s="54" t="n"/>
+      <c r="C3" s="54" t="n"/>
+      <c r="D3" s="54" t="n"/>
+      <c r="E3" s="54" t="n"/>
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="54" t="n"/>
+      <c r="H3" s="54" t="n"/>
+      <c r="I3" s="54" t="n"/>
+      <c r="J3" s="54" t="n"/>
+      <c r="K3" s="400" t="n"/>
+      <c r="L3" s="54" t="n"/>
+      <c r="M3" s="54" t="n"/>
+      <c r="N3" s="54" t="n"/>
+      <c r="O3" s="54" t="n"/>
+      <c r="P3" s="54" t="n"/>
+      <c r="Q3" s="54" t="n"/>
+      <c r="R3" s="54" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
+      <c r="X3" s="54" t="n"/>
+      <c r="Y3" s="54" t="n"/>
+      <c r="Z3" s="54" t="n"/>
+      <c r="AA3" s="54" t="n"/>
+      <c r="AB3" s="54" t="n"/>
+      <c r="AC3" s="54" t="n"/>
+      <c r="AD3" s="54" t="n"/>
+      <c r="AE3" s="54" t="n"/>
+      <c r="AF3" s="54" t="n"/>
+      <c r="AG3" s="54" t="n"/>
+      <c r="AH3" s="54" t="n"/>
+      <c r="AI3" s="54" t="n"/>
+      <c r="AJ3" s="54" t="n"/>
+      <c r="AK3" s="54" t="n"/>
+      <c r="AL3" s="54" t="n"/>
+      <c r="AM3" s="54" t="n"/>
+      <c r="AN3" s="54" t="n"/>
+      <c r="AO3" s="54" t="n"/>
+      <c r="AP3" s="400" t="n"/>
+      <c r="AQ3" s="401" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="326" t="n"/>
-      <c r="AS3" s="326" t="n"/>
-      <c r="AT3" s="326" t="n"/>
-      <c r="AU3" s="326" t="n"/>
-      <c r="AV3" s="327" t="n"/>
-      <c r="AW3" s="381" t="inlineStr">
+      <c r="AR3" s="402" t="n"/>
+      <c r="AS3" s="402" t="n"/>
+      <c r="AT3" s="402" t="n"/>
+      <c r="AU3" s="402" t="n"/>
+      <c r="AV3" s="403" t="n"/>
+      <c r="AW3" s="297" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="326" t="n"/>
-      <c r="AY3" s="326" t="n"/>
-      <c r="AZ3" s="326" t="n"/>
-      <c r="BA3" s="326" t="n"/>
-      <c r="BB3" s="326" t="n"/>
-      <c r="BC3" s="326" t="n"/>
-      <c r="BD3" s="329" t="n"/>
+      <c r="AX3" s="404" t="n"/>
+      <c r="AY3" s="404" t="n"/>
+      <c r="AZ3" s="404" t="n"/>
+      <c r="BA3" s="404" t="n"/>
+      <c r="BB3" s="404" t="n"/>
+      <c r="BC3" s="404" t="n"/>
+      <c r="BD3" s="405" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="10" t="n"/>
-      <c r="K4" s="11" t="n"/>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="A4" s="399" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="400" t="n"/>
+      <c r="L4" s="406" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="380" t="inlineStr">
+      <c r="M4" s="54" t="n"/>
+      <c r="N4" s="54" t="n"/>
+      <c r="O4" s="54" t="n"/>
+      <c r="P4" s="54" t="n"/>
+      <c r="Q4" s="54" t="n"/>
+      <c r="R4" s="54" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
+      <c r="X4" s="54" t="n"/>
+      <c r="Y4" s="54" t="n"/>
+      <c r="Z4" s="54" t="n"/>
+      <c r="AA4" s="54" t="n"/>
+      <c r="AB4" s="54" t="n"/>
+      <c r="AC4" s="54" t="n"/>
+      <c r="AD4" s="54" t="n"/>
+      <c r="AE4" s="54" t="n"/>
+      <c r="AF4" s="54" t="n"/>
+      <c r="AG4" s="54" t="n"/>
+      <c r="AH4" s="54" t="n"/>
+      <c r="AI4" s="54" t="n"/>
+      <c r="AJ4" s="54" t="n"/>
+      <c r="AK4" s="54" t="n"/>
+      <c r="AL4" s="54" t="n"/>
+      <c r="AM4" s="54" t="n"/>
+      <c r="AN4" s="54" t="n"/>
+      <c r="AO4" s="54" t="n"/>
+      <c r="AP4" s="400" t="n"/>
+      <c r="AQ4" s="401" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="326" t="n"/>
-      <c r="AS4" s="326" t="n"/>
-      <c r="AT4" s="326" t="n"/>
-      <c r="AU4" s="326" t="n"/>
-      <c r="AV4" s="327" t="n"/>
-      <c r="AW4" s="381" t="inlineStr">
+      <c r="AR4" s="402" t="n"/>
+      <c r="AS4" s="402" t="n"/>
+      <c r="AT4" s="402" t="n"/>
+      <c r="AU4" s="402" t="n"/>
+      <c r="AV4" s="403" t="n"/>
+      <c r="AW4" s="297" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="326" t="n"/>
-      <c r="AY4" s="326" t="n"/>
-      <c r="AZ4" s="326" t="n"/>
-      <c r="BA4" s="326" t="n"/>
-      <c r="BB4" s="326" t="n"/>
-      <c r="BC4" s="326" t="n"/>
-      <c r="BD4" s="329" t="n"/>
+      <c r="AX4" s="404" t="n"/>
+      <c r="AY4" s="404" t="n"/>
+      <c r="AZ4" s="404" t="n"/>
+      <c r="BA4" s="404" t="n"/>
+      <c r="BB4" s="404" t="n"/>
+      <c r="BC4" s="404" t="n"/>
+      <c r="BD4" s="405" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="16" t="n"/>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
-      <c r="E5" s="17" t="n"/>
-      <c r="F5" s="17" t="n"/>
-      <c r="G5" s="17" t="n"/>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
-      <c r="J5" s="17" t="n"/>
-      <c r="K5" s="18" t="n"/>
-      <c r="L5" s="50" t="inlineStr">
+      <c r="A5" s="399" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="400" t="n"/>
+      <c r="L5" s="407" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="17" t="n"/>
-      <c r="N5" s="17" t="n"/>
-      <c r="O5" s="17" t="n"/>
-      <c r="P5" s="17" t="n"/>
-      <c r="Q5" s="17" t="n"/>
-      <c r="R5" s="17" t="n"/>
-      <c r="S5" s="17" t="n"/>
-      <c r="T5" s="17" t="n"/>
-      <c r="U5" s="17" t="n"/>
-      <c r="V5" s="17" t="n"/>
-      <c r="W5" s="17" t="n"/>
-      <c r="X5" s="17" t="n"/>
-      <c r="Y5" s="17" t="n"/>
-      <c r="Z5" s="17" t="n"/>
-      <c r="AA5" s="17" t="n"/>
-      <c r="AB5" s="17" t="n"/>
-      <c r="AC5" s="17" t="n"/>
-      <c r="AD5" s="17" t="n"/>
-      <c r="AE5" s="17" t="n"/>
-      <c r="AF5" s="17" t="n"/>
-      <c r="AG5" s="17" t="n"/>
-      <c r="AH5" s="17" t="n"/>
-      <c r="AI5" s="17" t="n"/>
-      <c r="AJ5" s="17" t="n"/>
-      <c r="AK5" s="17" t="n"/>
-      <c r="AL5" s="17" t="n"/>
-      <c r="AM5" s="17" t="n"/>
-      <c r="AN5" s="17" t="n"/>
-      <c r="AO5" s="17" t="n"/>
-      <c r="AP5" s="17" t="n"/>
-      <c r="AQ5" s="382" t="inlineStr">
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="54" t="n"/>
+      <c r="R5" s="54" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
+      <c r="X5" s="54" t="n"/>
+      <c r="Y5" s="54" t="n"/>
+      <c r="Z5" s="54" t="n"/>
+      <c r="AA5" s="54" t="n"/>
+      <c r="AB5" s="54" t="n"/>
+      <c r="AC5" s="54" t="n"/>
+      <c r="AD5" s="54" t="n"/>
+      <c r="AE5" s="54" t="n"/>
+      <c r="AF5" s="54" t="n"/>
+      <c r="AG5" s="54" t="n"/>
+      <c r="AH5" s="54" t="n"/>
+      <c r="AI5" s="54" t="n"/>
+      <c r="AJ5" s="54" t="n"/>
+      <c r="AK5" s="54" t="n"/>
+      <c r="AL5" s="54" t="n"/>
+      <c r="AM5" s="54" t="n"/>
+      <c r="AN5" s="54" t="n"/>
+      <c r="AO5" s="54" t="n"/>
+      <c r="AP5" s="400" t="n"/>
+      <c r="AQ5" s="401" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="331" t="n"/>
-      <c r="AS5" s="331" t="n"/>
-      <c r="AT5" s="331" t="n"/>
-      <c r="AU5" s="331" t="n"/>
-      <c r="AV5" s="332" t="n"/>
-      <c r="AW5" s="383" t="inlineStr">
+      <c r="AR5" s="402" t="n"/>
+      <c r="AS5" s="402" t="n"/>
+      <c r="AT5" s="402" t="n"/>
+      <c r="AU5" s="402" t="n"/>
+      <c r="AV5" s="403" t="n"/>
+      <c r="AW5" s="297" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="331" t="n"/>
-      <c r="AY5" s="331" t="n"/>
-      <c r="AZ5" s="331" t="n"/>
-      <c r="BA5" s="331" t="n"/>
-      <c r="BB5" s="331" t="n"/>
-      <c r="BC5" s="331" t="n"/>
-      <c r="BD5" s="334" t="n"/>
+      <c r="AX5" s="404" t="n"/>
+      <c r="AY5" s="404" t="n"/>
+      <c r="AZ5" s="404" t="n"/>
+      <c r="BA5" s="404" t="n"/>
+      <c r="BB5" s="404" t="n"/>
+      <c r="BC5" s="404" t="n"/>
+      <c r="BD5" s="405" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="309" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="408" t="n"/>
+      <c r="B6" s="419" t="n"/>
+      <c r="C6" s="419" t="n"/>
+      <c r="D6" s="419" t="n"/>
+      <c r="E6" s="419" t="n"/>
+      <c r="F6" s="419" t="n"/>
+      <c r="G6" s="419" t="n"/>
+      <c r="H6" s="419" t="n"/>
+      <c r="I6" s="419" t="n"/>
+      <c r="J6" s="419" t="n"/>
+      <c r="K6" s="420" t="n"/>
+      <c r="L6" s="419" t="n"/>
+      <c r="M6" s="419" t="n"/>
+      <c r="N6" s="419" t="n"/>
+      <c r="O6" s="419" t="n"/>
+      <c r="P6" s="419" t="n"/>
+      <c r="Q6" s="419" t="n"/>
+      <c r="R6" s="419" t="n"/>
+      <c r="S6" s="419" t="n"/>
+      <c r="T6" s="419" t="n"/>
+      <c r="U6" s="419" t="n"/>
+      <c r="V6" s="419" t="n"/>
+      <c r="W6" s="419" t="n"/>
+      <c r="X6" s="419" t="n"/>
+      <c r="Y6" s="419" t="n"/>
+      <c r="Z6" s="419" t="n"/>
+      <c r="AA6" s="419" t="n"/>
+      <c r="AB6" s="419" t="n"/>
+      <c r="AC6" s="419" t="n"/>
+      <c r="AD6" s="419" t="n"/>
+      <c r="AE6" s="419" t="n"/>
+      <c r="AF6" s="419" t="n"/>
+      <c r="AG6" s="419" t="n"/>
+      <c r="AH6" s="419" t="n"/>
+      <c r="AI6" s="419" t="n"/>
+      <c r="AJ6" s="419" t="n"/>
+      <c r="AK6" s="419" t="n"/>
+      <c r="AL6" s="419" t="n"/>
+      <c r="AM6" s="419" t="n"/>
+      <c r="AN6" s="419" t="n"/>
+      <c r="AO6" s="419" t="n"/>
+      <c r="AP6" s="420" t="n"/>
+      <c r="AQ6" s="421" t="n"/>
+      <c r="AR6" s="421" t="n"/>
+      <c r="AS6" s="421" t="n"/>
+      <c r="AT6" s="421" t="n"/>
+      <c r="AU6" s="421" t="n"/>
+      <c r="AV6" s="422" t="n"/>
+      <c r="AW6" s="423" t="n"/>
+      <c r="AX6" s="423" t="n"/>
+      <c r="AY6" s="423" t="n"/>
+      <c r="AZ6" s="423" t="n"/>
+      <c r="BA6" s="423" t="n"/>
+      <c r="BB6" s="423" t="n"/>
+      <c r="BC6" s="423" t="n"/>
+      <c r="BD6" s="424" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
-        </is>
-      </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="22" t="n"/>
-      <c r="G7" s="22" t="n"/>
-      <c r="H7" s="22" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="22" t="n"/>
-      <c r="K7" s="22" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="22" t="n"/>
-      <c r="N7" s="22" t="n"/>
-      <c r="O7" s="22" t="n"/>
-      <c r="P7" s="22" t="n"/>
-      <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="22" t="n"/>
-      <c r="S7" s="22" t="n"/>
-      <c r="T7" s="22" t="n"/>
-      <c r="U7" s="22" t="n"/>
-      <c r="V7" s="22" t="n"/>
-      <c r="W7" s="22" t="n"/>
-      <c r="X7" s="22" t="n"/>
-      <c r="Y7" s="22" t="n"/>
-      <c r="Z7" s="22" t="n"/>
-      <c r="AA7" s="22" t="n"/>
-      <c r="AB7" s="22" t="n"/>
-      <c r="AC7" s="22" t="n"/>
-      <c r="AD7" s="22" t="n"/>
-      <c r="AE7" s="22" t="n"/>
-      <c r="AF7" s="22" t="n"/>
-      <c r="AG7" s="22" t="n"/>
-      <c r="AH7" s="22" t="n"/>
-      <c r="AI7" s="22" t="n"/>
-      <c r="AJ7" s="22" t="n"/>
-      <c r="AK7" s="22" t="n"/>
-      <c r="AL7" s="22" t="n"/>
-      <c r="AM7" s="22" t="n"/>
-      <c r="AN7" s="22" t="n"/>
-      <c r="AO7" s="22" t="n"/>
-      <c r="AP7" s="22" t="n"/>
-      <c r="AQ7" s="22" t="n"/>
-      <c r="AR7" s="22" t="n"/>
-      <c r="AS7" s="22" t="n"/>
-      <c r="AT7" s="22" t="n"/>
-      <c r="AU7" s="22" t="n"/>
-      <c r="AV7" s="22" t="n"/>
-      <c r="AW7" s="22" t="n"/>
-      <c r="AX7" s="22" t="n"/>
-      <c r="AY7" s="22" t="n"/>
-      <c r="AZ7" s="22" t="n"/>
-      <c r="BA7" s="22" t="n"/>
-      <c r="BB7" s="22" t="n"/>
-      <c r="BC7" s="22" t="n"/>
-      <c r="BD7" s="23" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="425" t="n"/>
+      <c r="B7" s="416" t="n"/>
+      <c r="C7" s="416" t="n"/>
+      <c r="D7" s="416" t="n"/>
+      <c r="E7" s="416" t="n"/>
+      <c r="F7" s="416" t="n"/>
+      <c r="G7" s="416" t="n"/>
+      <c r="H7" s="416" t="n"/>
+      <c r="I7" s="416" t="n"/>
+      <c r="J7" s="416" t="n"/>
+      <c r="K7" s="416" t="n"/>
+      <c r="L7" s="416" t="n"/>
+      <c r="M7" s="416" t="n"/>
+      <c r="N7" s="416" t="n"/>
+      <c r="O7" s="416" t="n"/>
+      <c r="P7" s="416" t="n"/>
+      <c r="Q7" s="416" t="n"/>
+      <c r="R7" s="416" t="n"/>
+      <c r="S7" s="416" t="n"/>
+      <c r="T7" s="416" t="n"/>
+      <c r="U7" s="416" t="n"/>
+      <c r="V7" s="416" t="n"/>
+      <c r="W7" s="416" t="n"/>
+      <c r="X7" s="416" t="n"/>
+      <c r="Y7" s="416" t="n"/>
+      <c r="Z7" s="416" t="n"/>
+      <c r="AA7" s="416" t="n"/>
+      <c r="AB7" s="416" t="n"/>
+      <c r="AC7" s="416" t="n"/>
+      <c r="AD7" s="416" t="n"/>
+      <c r="AE7" s="416" t="n"/>
+      <c r="AF7" s="416" t="n"/>
+      <c r="AG7" s="416" t="n"/>
+      <c r="AH7" s="416" t="n"/>
+      <c r="AI7" s="416" t="n"/>
+      <c r="AJ7" s="416" t="n"/>
+      <c r="AK7" s="416" t="n"/>
+      <c r="AL7" s="416" t="n"/>
+      <c r="AM7" s="416" t="n"/>
+      <c r="AN7" s="416" t="n"/>
+      <c r="AO7" s="416" t="n"/>
+      <c r="AP7" s="416" t="n"/>
+      <c r="AQ7" s="416" t="n"/>
+      <c r="AR7" s="416" t="n"/>
+      <c r="AS7" s="416" t="n"/>
+      <c r="AT7" s="416" t="n"/>
+      <c r="AU7" s="416" t="n"/>
+      <c r="AV7" s="416" t="n"/>
+      <c r="AW7" s="416" t="n"/>
+      <c r="AX7" s="416" t="n"/>
+      <c r="AY7" s="416" t="n"/>
+      <c r="AZ7" s="416" t="n"/>
+      <c r="BA7" s="416" t="n"/>
+      <c r="BB7" s="416" t="n"/>
+      <c r="BC7" s="416" t="n"/>
+      <c r="BD7" s="416" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="384" t="inlineStr">
+      <c r="A8" s="311" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="385" t="n"/>
-      <c r="C8" s="385" t="n"/>
-      <c r="D8" s="385" t="n"/>
-      <c r="E8" s="385" t="n"/>
-      <c r="F8" s="385" t="n"/>
-      <c r="G8" s="385" t="n"/>
-      <c r="H8" s="385" t="n"/>
-      <c r="I8" s="385" t="n"/>
-      <c r="J8" s="385" t="n"/>
-      <c r="K8" s="385" t="n"/>
-      <c r="L8" s="385" t="n"/>
-      <c r="M8" s="385" t="n"/>
-      <c r="N8" s="385" t="n"/>
-      <c r="O8" s="385" t="n"/>
-      <c r="P8" s="385" t="n"/>
-      <c r="Q8" s="385" t="n"/>
-      <c r="R8" s="385" t="n"/>
-      <c r="S8" s="385" t="n"/>
-      <c r="T8" s="385" t="n"/>
-      <c r="U8" s="385" t="n"/>
-      <c r="V8" s="385" t="n"/>
-      <c r="W8" s="385" t="n"/>
-      <c r="X8" s="385" t="n"/>
-      <c r="Y8" s="385" t="n"/>
-      <c r="Z8" s="385" t="n"/>
-      <c r="AA8" s="385" t="n"/>
-      <c r="AB8" s="385" t="n"/>
-      <c r="AC8" s="385" t="n"/>
-      <c r="AD8" s="385" t="n"/>
-      <c r="AE8" s="385" t="n"/>
-      <c r="AF8" s="385" t="n"/>
-      <c r="AG8" s="385" t="n"/>
-      <c r="AH8" s="385" t="n"/>
-      <c r="AI8" s="385" t="n"/>
-      <c r="AJ8" s="385" t="n"/>
-      <c r="AK8" s="385" t="n"/>
-      <c r="AL8" s="385" t="n"/>
-      <c r="AM8" s="385" t="n"/>
-      <c r="AN8" s="385" t="n"/>
-      <c r="AO8" s="385" t="n"/>
-      <c r="AP8" s="385" t="n"/>
-      <c r="AQ8" s="385" t="n"/>
-      <c r="AR8" s="385" t="n"/>
-      <c r="AS8" s="385" t="n"/>
-      <c r="AT8" s="385" t="n"/>
-      <c r="AU8" s="385" t="n"/>
-      <c r="AV8" s="385" t="n"/>
-      <c r="AW8" s="385" t="n"/>
-      <c r="AX8" s="385" t="n"/>
-      <c r="AY8" s="385" t="n"/>
-      <c r="AZ8" s="385" t="n"/>
-      <c r="BA8" s="385" t="n"/>
-      <c r="BB8" s="385" t="n"/>
-      <c r="BC8" s="385" t="n"/>
-      <c r="BD8" s="386" t="n"/>
+      <c r="B8" s="417" t="n"/>
+      <c r="C8" s="417" t="n"/>
+      <c r="D8" s="417" t="n"/>
+      <c r="E8" s="417" t="n"/>
+      <c r="F8" s="417" t="n"/>
+      <c r="G8" s="417" t="n"/>
+      <c r="H8" s="417" t="n"/>
+      <c r="I8" s="417" t="n"/>
+      <c r="J8" s="417" t="n"/>
+      <c r="K8" s="417" t="n"/>
+      <c r="L8" s="417" t="n"/>
+      <c r="M8" s="417" t="n"/>
+      <c r="N8" s="417" t="n"/>
+      <c r="O8" s="417" t="n"/>
+      <c r="P8" s="417" t="n"/>
+      <c r="Q8" s="417" t="n"/>
+      <c r="R8" s="417" t="n"/>
+      <c r="S8" s="417" t="n"/>
+      <c r="T8" s="417" t="n"/>
+      <c r="U8" s="417" t="n"/>
+      <c r="V8" s="417" t="n"/>
+      <c r="W8" s="417" t="n"/>
+      <c r="X8" s="417" t="n"/>
+      <c r="Y8" s="417" t="n"/>
+      <c r="Z8" s="417" t="n"/>
+      <c r="AA8" s="417" t="n"/>
+      <c r="AB8" s="417" t="n"/>
+      <c r="AC8" s="417" t="n"/>
+      <c r="AD8" s="417" t="n"/>
+      <c r="AE8" s="417" t="n"/>
+      <c r="AF8" s="417" t="n"/>
+      <c r="AG8" s="417" t="n"/>
+      <c r="AH8" s="417" t="n"/>
+      <c r="AI8" s="417" t="n"/>
+      <c r="AJ8" s="417" t="n"/>
+      <c r="AK8" s="417" t="n"/>
+      <c r="AL8" s="417" t="n"/>
+      <c r="AM8" s="417" t="n"/>
+      <c r="AN8" s="417" t="n"/>
+      <c r="AO8" s="417" t="n"/>
+      <c r="AP8" s="417" t="n"/>
+      <c r="AQ8" s="417" t="n"/>
+      <c r="AR8" s="417" t="n"/>
+      <c r="AS8" s="417" t="n"/>
+      <c r="AT8" s="417" t="n"/>
+      <c r="AU8" s="417" t="n"/>
+      <c r="AV8" s="417" t="n"/>
+      <c r="AW8" s="417" t="n"/>
+      <c r="AX8" s="417" t="n"/>
+      <c r="AY8" s="417" t="n"/>
+      <c r="AZ8" s="417" t="n"/>
+      <c r="BA8" s="417" t="n"/>
+      <c r="BB8" s="417" t="n"/>
+      <c r="BC8" s="417" t="n"/>
+      <c r="BD8" s="418" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="275" t="inlineStr">
@@ -10288,66 +10909,66 @@
       <c r="BD19" s="320" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="384" t="inlineStr">
+      <c r="A20" s="311" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B20" s="385" t="n"/>
-      <c r="C20" s="385" t="n"/>
-      <c r="D20" s="385" t="n"/>
-      <c r="E20" s="385" t="n"/>
-      <c r="F20" s="385" t="n"/>
-      <c r="G20" s="385" t="n"/>
-      <c r="H20" s="385" t="n"/>
-      <c r="I20" s="385" t="n"/>
-      <c r="J20" s="385" t="n"/>
-      <c r="K20" s="385" t="n"/>
-      <c r="L20" s="385" t="n"/>
-      <c r="M20" s="385" t="n"/>
-      <c r="N20" s="385" t="n"/>
-      <c r="O20" s="385" t="n"/>
-      <c r="P20" s="385" t="n"/>
-      <c r="Q20" s="385" t="n"/>
-      <c r="R20" s="385" t="n"/>
-      <c r="S20" s="385" t="n"/>
-      <c r="T20" s="385" t="n"/>
-      <c r="U20" s="385" t="n"/>
-      <c r="V20" s="385" t="n"/>
-      <c r="W20" s="385" t="n"/>
-      <c r="X20" s="385" t="n"/>
-      <c r="Y20" s="385" t="n"/>
-      <c r="Z20" s="385" t="n"/>
-      <c r="AA20" s="385" t="n"/>
-      <c r="AB20" s="385" t="n"/>
-      <c r="AC20" s="385" t="n"/>
-      <c r="AD20" s="385" t="n"/>
-      <c r="AE20" s="385" t="n"/>
-      <c r="AF20" s="385" t="n"/>
-      <c r="AG20" s="385" t="n"/>
-      <c r="AH20" s="385" t="n"/>
-      <c r="AI20" s="385" t="n"/>
-      <c r="AJ20" s="385" t="n"/>
-      <c r="AK20" s="385" t="n"/>
-      <c r="AL20" s="385" t="n"/>
-      <c r="AM20" s="385" t="n"/>
-      <c r="AN20" s="385" t="n"/>
-      <c r="AO20" s="385" t="n"/>
-      <c r="AP20" s="385" t="n"/>
-      <c r="AQ20" s="385" t="n"/>
-      <c r="AR20" s="385" t="n"/>
-      <c r="AS20" s="385" t="n"/>
-      <c r="AT20" s="385" t="n"/>
-      <c r="AU20" s="385" t="n"/>
-      <c r="AV20" s="385" t="n"/>
-      <c r="AW20" s="385" t="n"/>
-      <c r="AX20" s="385" t="n"/>
-      <c r="AY20" s="385" t="n"/>
-      <c r="AZ20" s="385" t="n"/>
-      <c r="BA20" s="385" t="n"/>
-      <c r="BB20" s="385" t="n"/>
-      <c r="BC20" s="385" t="n"/>
-      <c r="BD20" s="386" t="n"/>
+      <c r="B20" s="417" t="n"/>
+      <c r="C20" s="417" t="n"/>
+      <c r="D20" s="417" t="n"/>
+      <c r="E20" s="417" t="n"/>
+      <c r="F20" s="417" t="n"/>
+      <c r="G20" s="417" t="n"/>
+      <c r="H20" s="417" t="n"/>
+      <c r="I20" s="417" t="n"/>
+      <c r="J20" s="417" t="n"/>
+      <c r="K20" s="417" t="n"/>
+      <c r="L20" s="417" t="n"/>
+      <c r="M20" s="417" t="n"/>
+      <c r="N20" s="417" t="n"/>
+      <c r="O20" s="417" t="n"/>
+      <c r="P20" s="417" t="n"/>
+      <c r="Q20" s="417" t="n"/>
+      <c r="R20" s="417" t="n"/>
+      <c r="S20" s="417" t="n"/>
+      <c r="T20" s="417" t="n"/>
+      <c r="U20" s="417" t="n"/>
+      <c r="V20" s="417" t="n"/>
+      <c r="W20" s="417" t="n"/>
+      <c r="X20" s="417" t="n"/>
+      <c r="Y20" s="417" t="n"/>
+      <c r="Z20" s="417" t="n"/>
+      <c r="AA20" s="417" t="n"/>
+      <c r="AB20" s="417" t="n"/>
+      <c r="AC20" s="417" t="n"/>
+      <c r="AD20" s="417" t="n"/>
+      <c r="AE20" s="417" t="n"/>
+      <c r="AF20" s="417" t="n"/>
+      <c r="AG20" s="417" t="n"/>
+      <c r="AH20" s="417" t="n"/>
+      <c r="AI20" s="417" t="n"/>
+      <c r="AJ20" s="417" t="n"/>
+      <c r="AK20" s="417" t="n"/>
+      <c r="AL20" s="417" t="n"/>
+      <c r="AM20" s="417" t="n"/>
+      <c r="AN20" s="417" t="n"/>
+      <c r="AO20" s="417" t="n"/>
+      <c r="AP20" s="417" t="n"/>
+      <c r="AQ20" s="417" t="n"/>
+      <c r="AR20" s="417" t="n"/>
+      <c r="AS20" s="417" t="n"/>
+      <c r="AT20" s="417" t="n"/>
+      <c r="AU20" s="417" t="n"/>
+      <c r="AV20" s="417" t="n"/>
+      <c r="AW20" s="417" t="n"/>
+      <c r="AX20" s="417" t="n"/>
+      <c r="AY20" s="417" t="n"/>
+      <c r="AZ20" s="417" t="n"/>
+      <c r="BA20" s="417" t="n"/>
+      <c r="BB20" s="417" t="n"/>
+      <c r="BC20" s="417" t="n"/>
+      <c r="BD20" s="418" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -840,6 +840,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4112,7 +4115,6 @@
       <c r="CD34" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="261">
     <mergeCell ref="AK16:AQ16"/>
     <mergeCell ref="A9:N9"/>
@@ -4171,8 +4173,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="A10:N10"/>
     <mergeCell ref="BV21:BY21"/>
-    <mergeCell ref="A10:N10"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>
@@ -5829,7 +5831,6 @@
       <c r="CD18" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="54">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="O9:AO9"/>
@@ -7373,7 +7374,6 @@
       <c r="CD19" s="23" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="79">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="Q1:BJ3"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -1452,7 +1452,7 @@
       <c r="BR4" s="30" t="n"/>
       <c r="BS4" s="47" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Engineering / QA</t>
         </is>
       </c>
       <c r="BT4" s="14" t="n"/>
@@ -1548,7 +1548,7 @@
       <c r="BR5" s="52" t="n"/>
       <c r="BS5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="BT5" s="17" t="n"/>
@@ -4173,8 +4173,8 @@
     <mergeCell ref="R20:X20"/>
     <mergeCell ref="Y16:AB16"/>
     <mergeCell ref="BO13:BU13"/>
+    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="A10:N10"/>
-    <mergeCell ref="BV21:BY21"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="BO21:BU21"/>
     <mergeCell ref="AR15:AU15"/>
@@ -4742,7 +4742,7 @@
       <c r="BR4" s="30" t="n"/>
       <c r="BS4" s="47" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Engineering / QA</t>
         </is>
       </c>
       <c r="BT4" s="14" t="n"/>
@@ -4838,7 +4838,7 @@
       <c r="BR5" s="52" t="n"/>
       <c r="BS5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="BT5" s="17" t="n"/>
@@ -6220,7 +6220,7 @@
       <c r="BR4" s="30" t="n"/>
       <c r="BS4" s="47" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Engineering / QA</t>
         </is>
       </c>
       <c r="BT4" s="14" t="n"/>
@@ -6316,7 +6316,7 @@
       <c r="BR5" s="52" t="n"/>
       <c r="BS5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="BT5" s="17" t="n"/>
@@ -7716,7 +7716,7 @@
       <c r="AV4" s="30" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>Engineering / QA</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -7786,7 +7786,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM132_RankRef" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM132_Actions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM132_PFMEA'!$1:$13</definedName>
@@ -826,7 +828,7 @@
       <row>0</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1552575" cy="438150"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1452,7 +1454,7 @@
       <c r="BR4" s="30" t="n"/>
       <c r="BS4" s="47" t="inlineStr">
         <is>
-          <t>Engineering / QA</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="BT4" s="14" t="n"/>
@@ -1548,7 +1550,7 @@
       <c r="BR5" s="52" t="n"/>
       <c r="BS5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="BT5" s="17" t="n"/>
@@ -1841,7 +1843,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>Prepared Date</t>
+          <t>Linked FRM-131 / FRM-133</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -1886,7 +1888,7 @@
       <c r="AO10" s="27" t="n"/>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Evidence Ref</t>
+          <t>Ref: SOP-101</t>
         </is>
       </c>
       <c r="AQ10" s="6" t="n"/>
@@ -1902,7 +1904,11 @@
       <c r="BA10" s="6" t="n"/>
       <c r="BB10" s="6" t="n"/>
       <c r="BC10" s="7" t="n"/>
-      <c r="BD10" s="25" t="n"/>
+      <c r="BD10" s="25" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="BE10" s="26" t="n"/>
       <c r="BF10" s="26" t="n"/>
       <c r="BG10" s="26" t="n"/>
@@ -4115,6 +4121,7 @@
       <c r="CD34" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="261">
     <mergeCell ref="AK16:AQ16"/>
     <mergeCell ref="A9:N9"/>
@@ -4742,7 +4749,7 @@
       <c r="BR4" s="30" t="n"/>
       <c r="BS4" s="47" t="inlineStr">
         <is>
-          <t>Engineering / QA</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="BT4" s="14" t="n"/>
@@ -4838,7 +4845,7 @@
       <c r="BR5" s="52" t="n"/>
       <c r="BS5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="BT5" s="17" t="n"/>
@@ -5831,6 +5838,7 @@
       <c r="CD18" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="54">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="O9:AO9"/>
@@ -6220,7 +6228,7 @@
       <c r="BR4" s="30" t="n"/>
       <c r="BS4" s="47" t="inlineStr">
         <is>
-          <t>Engineering / QA</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="BT4" s="14" t="n"/>
@@ -6316,7 +6324,7 @@
       <c r="BR5" s="52" t="n"/>
       <c r="BS5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="BT5" s="17" t="n"/>
@@ -7374,6 +7382,7 @@
       <c r="CD19" s="23" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="79">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="Q1:BJ3"/>
@@ -7716,7 +7725,7 @@
       <c r="AV4" s="30" t="n"/>
       <c r="AW4" s="47" t="inlineStr">
         <is>
-          <t>Engineering / QA</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="AX4" s="14" t="n"/>
@@ -7786,7 +7795,7 @@
       <c r="AV5" s="52" t="n"/>
       <c r="AW5" s="53" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="17" t="n"/>
@@ -9212,4 +9221,97 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-131, FRM-133; Parent ref: SOP-101</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-132_PFMEA_Lite.xlsx
@@ -3608,7 +3608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="516">
+  <cellXfs count="518">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4810,9 +4810,8 @@
     <xf numFmtId="0" fontId="80" fillId="47" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="240" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="239" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="240" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="244" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="80" fillId="52" borderId="239" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4828,9 +4827,8 @@
     <xf numFmtId="0" fontId="80" fillId="47" borderId="247" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="80" fillId="47" borderId="248" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="247" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="248" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="79" fillId="49" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4919,6 +4917,99 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã chi tiết / Phiên bản
+Part đang phân tích rủi ro process.</t>
+      </text>
+    </comment>
+    <comment ref="AP9" authorId="0" shapeId="0">
+      <text>
+        <t>Tên quy trình
+Tên tổng thể quy trình.
+Ví dụ: CNC Machining Process for HES-1234.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày PFMEA
+Ngày thực hiện hoặc cập nhật PFMEA.</t>
+      </text>
+    </comment>
+    <comment ref="AP10" authorId="0" shapeId="0">
+      <text>
+        <t>Trưởng nhóm
+Người chủ trì phân tích PFMEA.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Phân tích phương thức và ảnh hưởng lỗi
+PFMEA theo AIAG-VDA FMEA Handbook.
+Mỗi dòng = 1 failure mode cho 1 process step.
+S=Severity O=Occurrence D=Detection AP=Action Priority.
+AP: H=High(action required) M=Medium(should act) L=Low(monitor).</t>
+      </text>
+    </comment>
+    <comment ref="S13" authorId="0" shapeId="0">
+      <text>
+        <t>Bước / Lỗi / Ảnh hưởng
+Ghi: Bước quy trình → Lỗi có thể xảy ra → Ảnh hưởng lên sản phẩm/khách hàng.
+Ví dụ: CNC Milling OP10 → OD out of tolerance → Part rejected, delay delivery.</t>
+      </text>
+    </comment>
+    <comment ref="AB13" authorId="0" shapeId="0">
+      <text>
+        <t>Nguyên nhân / Kiểm soát
+Ghi: Nguyên nhân gốc → Biện pháp phòng ngừa → Biện pháp phát hiện.
+Ví dụ: Tool wear → Scheduled tool change → First piece + SPC.</t>
+      </text>
+    </comment>
+    <comment ref="AK13" authorId="0" shapeId="0">
+      <text>
+        <t>S = Severity (1-10)
+Mức nghiêm trọng của ảnh hưởng.
+1=Không đáng kể, 5=Trung bình, 8=Nghiêm trọng, 10=An toàn.</t>
+      </text>
+    </comment>
+    <comment ref="AT13" authorId="0" shapeId="0">
+      <text>
+        <t>O = Occurrence (1-10)
+Tần suất xảy ra nguyên nhân.
+1=Hiếm, 3=Thấp, 5=Trung bình, 8=Cao, 10=Rất cao.</t>
+      </text>
+    </comment>
+    <comment ref="BC13" authorId="0" shapeId="0">
+      <text>
+        <t>D = Detection (1-10)
+Khả năng phát hiện trước khi đến khách hàng.
+1=Chắc chắn phát hiện, 5=Trung bình, 10=Không phát hiện được.</t>
+      </text>
+    </comment>
+    <comment ref="BL13" authorId="0" shapeId="0">
+      <text>
+        <t>AP = Action Priority
+H = S≥8 hoặc S×O×D≥200 → hành động bắt buộc.
+M = 100≤RPN&lt;200 → nên hành động.
+L = RPN&lt;100 → theo dõi.</t>
+      </text>
+    </comment>
+    <comment ref="BU13" authorId="0" shapeId="0">
+      <text>
+        <t>Hành động
+Hành động cải thiện, người phụ trách, hạn hoàn thành.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6201,30 +6292,30 @@
       </c>
       <c r="B13" s="474" t="n"/>
       <c r="C13" s="474" t="n"/>
-      <c r="D13" s="475" t="n"/>
-      <c r="E13" s="488" t="inlineStr">
+      <c r="D13" s="474" t="n"/>
+      <c r="E13" s="474" t="n"/>
+      <c r="F13" s="474" t="n"/>
+      <c r="G13" s="474" t="n"/>
+      <c r="H13" s="474" t="n"/>
+      <c r="I13" s="475" t="n"/>
+      <c r="J13" s="488" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="F13" s="474" t="n"/>
-      <c r="G13" s="474" t="n"/>
-      <c r="H13" s="474" t="n"/>
-      <c r="I13" s="474" t="n"/>
-      <c r="J13" s="475" t="n"/>
-      <c r="K13" s="488" t="inlineStr">
-        <is>
-          <t>Process Step / Failure Mode / Effect</t>
-        </is>
-      </c>
+      <c r="K13" s="474" t="n"/>
       <c r="L13" s="474" t="n"/>
       <c r="M13" s="474" t="n"/>
       <c r="N13" s="474" t="n"/>
       <c r="O13" s="474" t="n"/>
       <c r="P13" s="474" t="n"/>
       <c r="Q13" s="474" t="n"/>
-      <c r="R13" s="474" t="n"/>
-      <c r="S13" s="474" t="n"/>
+      <c r="R13" s="475" t="n"/>
+      <c r="S13" s="488" t="inlineStr">
+        <is>
+          <t>Process Step / Failure Mode / Effect</t>
+        </is>
+      </c>
       <c r="T13" s="474" t="n"/>
       <c r="U13" s="474" t="n"/>
       <c r="V13" s="474" t="n"/>
@@ -6232,8 +6323,12 @@
       <c r="X13" s="474" t="n"/>
       <c r="Y13" s="474" t="n"/>
       <c r="Z13" s="474" t="n"/>
-      <c r="AA13" s="474" t="n"/>
-      <c r="AB13" s="474" t="n"/>
+      <c r="AA13" s="475" t="n"/>
+      <c r="AB13" s="488" t="inlineStr">
+        <is>
+          <t>Cause / Controls</t>
+        </is>
+      </c>
       <c r="AC13" s="474" t="n"/>
       <c r="AD13" s="474" t="n"/>
       <c r="AE13" s="474" t="n"/>
@@ -6241,21 +6336,25 @@
       <c r="AG13" s="474" t="n"/>
       <c r="AH13" s="474" t="n"/>
       <c r="AI13" s="474" t="n"/>
-      <c r="AJ13" s="474" t="n"/>
-      <c r="AK13" s="474" t="n"/>
+      <c r="AJ13" s="475" t="n"/>
+      <c r="AK13" s="488" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="AL13" s="474" t="n"/>
       <c r="AM13" s="474" t="n"/>
       <c r="AN13" s="474" t="n"/>
       <c r="AO13" s="474" t="n"/>
-      <c r="AP13" s="475" t="n"/>
-      <c r="AQ13" s="488" t="inlineStr">
+      <c r="AP13" s="474" t="n"/>
+      <c r="AQ13" s="474" t="n"/>
+      <c r="AR13" s="474" t="n"/>
+      <c r="AS13" s="475" t="n"/>
+      <c r="AT13" s="488" t="inlineStr">
         <is>
-          <t>Cause / Current Controls</t>
+          <t>O</t>
         </is>
       </c>
-      <c r="AR13" s="474" t="n"/>
-      <c r="AS13" s="474" t="n"/>
-      <c r="AT13" s="474" t="n"/>
       <c r="AU13" s="474" t="n"/>
       <c r="AV13" s="474" t="n"/>
       <c r="AW13" s="474" t="n"/>
@@ -6263,34 +6362,38 @@
       <c r="AY13" s="474" t="n"/>
       <c r="AZ13" s="474" t="n"/>
       <c r="BA13" s="474" t="n"/>
-      <c r="BB13" s="474" t="n"/>
-      <c r="BC13" s="474" t="n"/>
+      <c r="BB13" s="475" t="n"/>
+      <c r="BC13" s="488" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="BD13" s="474" t="n"/>
       <c r="BE13" s="474" t="n"/>
       <c r="BF13" s="474" t="n"/>
       <c r="BG13" s="474" t="n"/>
       <c r="BH13" s="474" t="n"/>
       <c r="BI13" s="474" t="n"/>
-      <c r="BJ13" s="475" t="n"/>
-      <c r="BK13" s="488" t="inlineStr">
+      <c r="BJ13" s="474" t="n"/>
+      <c r="BK13" s="475" t="n"/>
+      <c r="BL13" s="488" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>AP</t>
         </is>
       </c>
-      <c r="BL13" s="474" t="n"/>
       <c r="BM13" s="474" t="n"/>
       <c r="BN13" s="474" t="n"/>
       <c r="BO13" s="474" t="n"/>
       <c r="BP13" s="474" t="n"/>
       <c r="BQ13" s="474" t="n"/>
-      <c r="BR13" s="475" t="n"/>
-      <c r="BS13" s="489" t="inlineStr">
+      <c r="BR13" s="474" t="n"/>
+      <c r="BS13" s="474" t="n"/>
+      <c r="BT13" s="475" t="n"/>
+      <c r="BU13" s="489" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Action</t>
         </is>
       </c>
-      <c r="BT13" s="474" t="n"/>
-      <c r="BU13" s="474" t="n"/>
       <c r="BV13" s="474" t="n"/>
       <c r="BW13" s="474" t="n"/>
       <c r="BX13" s="474" t="n"/>
@@ -6302,35 +6405,36 @@
       <c r="CD13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="491" t="n"/>
-      <c r="D14" s="492" t="n"/>
-      <c r="E14" s="493" t="inlineStr">
+      <c r="D14" s="491" t="n"/>
+      <c r="E14" s="491" t="n"/>
+      <c r="F14" s="491" t="n"/>
+      <c r="G14" s="491" t="n"/>
+      <c r="H14" s="491" t="n"/>
+      <c r="I14" s="492" t="n"/>
+      <c r="J14" s="493" t="inlineStr">
         <is>
           <t>TEC</t>
         </is>
       </c>
-      <c r="F14" s="491" t="n"/>
-      <c r="G14" s="491" t="n"/>
-      <c r="H14" s="491" t="n"/>
-      <c r="I14" s="491" t="n"/>
-      <c r="J14" s="492" t="n"/>
-      <c r="K14" s="494" t="inlineStr">
-        <is>
-          <t>(Enter process step, potential failure mode, and effect).</t>
-        </is>
-      </c>
+      <c r="K14" s="491" t="n"/>
       <c r="L14" s="491" t="n"/>
       <c r="M14" s="491" t="n"/>
       <c r="N14" s="491" t="n"/>
       <c r="O14" s="491" t="n"/>
       <c r="P14" s="491" t="n"/>
       <c r="Q14" s="491" t="n"/>
-      <c r="R14" s="491" t="n"/>
-      <c r="S14" s="491" t="n"/>
+      <c r="R14" s="492" t="n"/>
+      <c r="S14" s="494" t="inlineStr">
+        <is>
+          <t>(Process step → Failure mode → Effect).</t>
+        </is>
+      </c>
       <c r="T14" s="491" t="n"/>
       <c r="U14" s="491" t="n"/>
       <c r="V14" s="491" t="n"/>
@@ -6338,8 +6442,12 @@
       <c r="X14" s="491" t="n"/>
       <c r="Y14" s="491" t="n"/>
       <c r="Z14" s="491" t="n"/>
-      <c r="AA14" s="491" t="n"/>
-      <c r="AB14" s="491" t="n"/>
+      <c r="AA14" s="492" t="n"/>
+      <c r="AB14" s="495" t="inlineStr">
+        <is>
+          <t>(Root cause → Prevention → Detection).</t>
+        </is>
+      </c>
       <c r="AC14" s="491" t="n"/>
       <c r="AD14" s="491" t="n"/>
       <c r="AE14" s="491" t="n"/>
@@ -6347,21 +6455,17 @@
       <c r="AG14" s="491" t="n"/>
       <c r="AH14" s="491" t="n"/>
       <c r="AI14" s="491" t="n"/>
-      <c r="AJ14" s="491" t="n"/>
-      <c r="AK14" s="491" t="n"/>
+      <c r="AJ14" s="492" t="n"/>
+      <c r="AK14" s="496" t="n"/>
       <c r="AL14" s="491" t="n"/>
       <c r="AM14" s="491" t="n"/>
       <c r="AN14" s="491" t="n"/>
       <c r="AO14" s="491" t="n"/>
-      <c r="AP14" s="492" t="n"/>
-      <c r="AQ14" s="495" t="inlineStr">
-        <is>
-          <t>(Enter cause, prevention control, detection control).</t>
-        </is>
-      </c>
+      <c r="AP14" s="491" t="n"/>
+      <c r="AQ14" s="491" t="n"/>
       <c r="AR14" s="491" t="n"/>
-      <c r="AS14" s="491" t="n"/>
-      <c r="AT14" s="491" t="n"/>
+      <c r="AS14" s="492" t="n"/>
+      <c r="AT14" s="496" t="n"/>
       <c r="AU14" s="491" t="n"/>
       <c r="AV14" s="491" t="n"/>
       <c r="AW14" s="491" t="n"/>
@@ -6369,26 +6473,26 @@
       <c r="AY14" s="491" t="n"/>
       <c r="AZ14" s="491" t="n"/>
       <c r="BA14" s="491" t="n"/>
-      <c r="BB14" s="491" t="n"/>
-      <c r="BC14" s="491" t="n"/>
+      <c r="BB14" s="492" t="n"/>
+      <c r="BC14" s="497" t="n"/>
       <c r="BD14" s="491" t="n"/>
       <c r="BE14" s="491" t="n"/>
       <c r="BF14" s="491" t="n"/>
       <c r="BG14" s="491" t="n"/>
       <c r="BH14" s="491" t="n"/>
       <c r="BI14" s="491" t="n"/>
-      <c r="BJ14" s="492" t="n"/>
-      <c r="BK14" s="496" t="n"/>
-      <c r="BL14" s="491" t="n"/>
+      <c r="BJ14" s="491" t="n"/>
+      <c r="BK14" s="492" t="n"/>
+      <c r="BL14" s="497" t="n"/>
       <c r="BM14" s="491" t="n"/>
       <c r="BN14" s="491" t="n"/>
       <c r="BO14" s="491" t="n"/>
       <c r="BP14" s="491" t="n"/>
       <c r="BQ14" s="491" t="n"/>
-      <c r="BR14" s="492" t="n"/>
-      <c r="BS14" s="497" t="n"/>
-      <c r="BT14" s="491" t="n"/>
-      <c r="BU14" s="491" t="n"/>
+      <c r="BR14" s="491" t="n"/>
+      <c r="BS14" s="491" t="n"/>
+      <c r="BT14" s="492" t="n"/>
+      <c r="BU14" s="498" t="n"/>
       <c r="BV14" s="491" t="n"/>
       <c r="BW14" s="491" t="n"/>
       <c r="BX14" s="491" t="n"/>
@@ -6397,34 +6501,35 @@
       <c r="CA14" s="491" t="n"/>
       <c r="CB14" s="491" t="n"/>
       <c r="CC14" s="491" t="n"/>
-      <c r="CD14" s="498" t="n"/>
+      <c r="CD14" s="499" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="491" t="n"/>
-      <c r="D15" s="492" t="n"/>
-      <c r="E15" s="493" t="inlineStr">
+      <c r="D15" s="491" t="n"/>
+      <c r="E15" s="491" t="n"/>
+      <c r="F15" s="491" t="n"/>
+      <c r="G15" s="491" t="n"/>
+      <c r="H15" s="491" t="n"/>
+      <c r="I15" s="492" t="n"/>
+      <c r="J15" s="493" t="inlineStr">
         <is>
           <t>TEC</t>
         </is>
       </c>
-      <c r="F15" s="491" t="n"/>
-      <c r="G15" s="491" t="n"/>
-      <c r="H15" s="491" t="n"/>
-      <c r="I15" s="491" t="n"/>
-      <c r="J15" s="492" t="n"/>
-      <c r="K15" s="499" t="inlineStr"/>
+      <c r="K15" s="491" t="n"/>
       <c r="L15" s="491" t="n"/>
       <c r="M15" s="491" t="n"/>
       <c r="N15" s="491" t="n"/>
       <c r="O15" s="491" t="n"/>
       <c r="P15" s="491" t="n"/>
       <c r="Q15" s="491" t="n"/>
-      <c r="R15" s="491" t="n"/>
-      <c r="S15" s="491" t="n"/>
+      <c r="R15" s="492" t="n"/>
+      <c r="S15" s="500" t="inlineStr"/>
       <c r="T15" s="491" t="n"/>
       <c r="U15" s="491" t="n"/>
       <c r="V15" s="491" t="n"/>
@@ -6432,8 +6537,8 @@
       <c r="X15" s="491" t="n"/>
       <c r="Y15" s="491" t="n"/>
       <c r="Z15" s="491" t="n"/>
-      <c r="AA15" s="491" t="n"/>
-      <c r="AB15" s="491" t="n"/>
+      <c r="AA15" s="492" t="n"/>
+      <c r="AB15" s="495" t="inlineStr"/>
       <c r="AC15" s="491" t="n"/>
       <c r="AD15" s="491" t="n"/>
       <c r="AE15" s="491" t="n"/>
@@ -6441,17 +6546,17 @@
       <c r="AG15" s="491" t="n"/>
       <c r="AH15" s="491" t="n"/>
       <c r="AI15" s="491" t="n"/>
-      <c r="AJ15" s="491" t="n"/>
-      <c r="AK15" s="491" t="n"/>
+      <c r="AJ15" s="492" t="n"/>
+      <c r="AK15" s="496" t="n"/>
       <c r="AL15" s="491" t="n"/>
       <c r="AM15" s="491" t="n"/>
       <c r="AN15" s="491" t="n"/>
       <c r="AO15" s="491" t="n"/>
-      <c r="AP15" s="492" t="n"/>
-      <c r="AQ15" s="495" t="inlineStr"/>
+      <c r="AP15" s="491" t="n"/>
+      <c r="AQ15" s="491" t="n"/>
       <c r="AR15" s="491" t="n"/>
-      <c r="AS15" s="491" t="n"/>
-      <c r="AT15" s="491" t="n"/>
+      <c r="AS15" s="492" t="n"/>
+      <c r="AT15" s="496" t="n"/>
       <c r="AU15" s="491" t="n"/>
       <c r="AV15" s="491" t="n"/>
       <c r="AW15" s="491" t="n"/>
@@ -6459,26 +6564,26 @@
       <c r="AY15" s="491" t="n"/>
       <c r="AZ15" s="491" t="n"/>
       <c r="BA15" s="491" t="n"/>
-      <c r="BB15" s="491" t="n"/>
-      <c r="BC15" s="491" t="n"/>
+      <c r="BB15" s="492" t="n"/>
+      <c r="BC15" s="497" t="n"/>
       <c r="BD15" s="491" t="n"/>
       <c r="BE15" s="491" t="n"/>
       <c r="BF15" s="491" t="n"/>
       <c r="BG15" s="491" t="n"/>
       <c r="BH15" s="491" t="n"/>
       <c r="BI15" s="491" t="n"/>
-      <c r="BJ15" s="492" t="n"/>
-      <c r="BK15" s="496" t="n"/>
-      <c r="BL15" s="491" t="n"/>
+      <c r="BJ15" s="491" t="n"/>
+      <c r="BK15" s="492" t="n"/>
+      <c r="BL15" s="497" t="n"/>
       <c r="BM15" s="491" t="n"/>
       <c r="BN15" s="491" t="n"/>
       <c r="BO15" s="491" t="n"/>
       <c r="BP15" s="491" t="n"/>
       <c r="BQ15" s="491" t="n"/>
-      <c r="BR15" s="492" t="n"/>
-      <c r="BS15" s="497" t="n"/>
-      <c r="BT15" s="491" t="n"/>
-      <c r="BU15" s="491" t="n"/>
+      <c r="BR15" s="491" t="n"/>
+      <c r="BS15" s="491" t="n"/>
+      <c r="BT15" s="492" t="n"/>
+      <c r="BU15" s="498" t="n"/>
       <c r="BV15" s="491" t="n"/>
       <c r="BW15" s="491" t="n"/>
       <c r="BX15" s="491" t="n"/>
@@ -6487,34 +6592,35 @@
       <c r="CA15" s="491" t="n"/>
       <c r="CB15" s="491" t="n"/>
       <c r="CC15" s="491" t="n"/>
-      <c r="CD15" s="498" t="n"/>
+      <c r="CD15" s="499" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="491" t="n"/>
-      <c r="D16" s="492" t="n"/>
-      <c r="E16" s="493" t="inlineStr">
+      <c r="D16" s="491" t="n"/>
+      <c r="E16" s="491" t="n"/>
+      <c r="F16" s="491" t="n"/>
+      <c r="G16" s="491" t="n"/>
+      <c r="H16" s="491" t="n"/>
+      <c r="I16" s="492" t="n"/>
+      <c r="J16" s="493" t="inlineStr">
         <is>
           <t>TEC</t>
         </is>
       </c>
-      <c r="F16" s="491" t="n"/>
-      <c r="G16" s="491" t="n"/>
-      <c r="H16" s="491" t="n"/>
-      <c r="I16" s="491" t="n"/>
-      <c r="J16" s="492" t="n"/>
-      <c r="K16" s="494" t="inlineStr"/>
+      <c r="K16" s="491" t="n"/>
       <c r="L16" s="491" t="n"/>
       <c r="M16" s="491" t="n"/>
       <c r="N16" s="491" t="n"/>
       <c r="O16" s="491" t="n"/>
       <c r="P16" s="491" t="n"/>
       <c r="Q16" s="491" t="n"/>
-      <c r="R16" s="491" t="n"/>
-      <c r="S16" s="491" t="n"/>
+      <c r="R16" s="492" t="n"/>
+      <c r="S16" s="494" t="inlineStr"/>
       <c r="T16" s="491" t="n"/>
       <c r="U16" s="491" t="n"/>
       <c r="V16" s="491" t="n"/>
@@ -6522,8 +6628,8 @@
       <c r="X16" s="491" t="n"/>
       <c r="Y16" s="491" t="n"/>
       <c r="Z16" s="491" t="n"/>
-      <c r="AA16" s="491" t="n"/>
-      <c r="AB16" s="491" t="n"/>
+      <c r="AA16" s="492" t="n"/>
+      <c r="AB16" s="495" t="inlineStr"/>
       <c r="AC16" s="491" t="n"/>
       <c r="AD16" s="491" t="n"/>
       <c r="AE16" s="491" t="n"/>
@@ -6531,17 +6637,17 @@
       <c r="AG16" s="491" t="n"/>
       <c r="AH16" s="491" t="n"/>
       <c r="AI16" s="491" t="n"/>
-      <c r="AJ16" s="491" t="n"/>
-      <c r="AK16" s="491" t="n"/>
+      <c r="AJ16" s="492" t="n"/>
+      <c r="AK16" s="496" t="n"/>
       <c r="AL16" s="491" t="n"/>
       <c r="AM16" s="491" t="n"/>
       <c r="AN16" s="491" t="n"/>
       <c r="AO16" s="491" t="n"/>
-      <c r="AP16" s="492" t="n"/>
-      <c r="AQ16" s="495" t="inlineStr"/>
+      <c r="AP16" s="491" t="n"/>
+      <c r="AQ16" s="491" t="n"/>
       <c r="AR16" s="491" t="n"/>
-      <c r="AS16" s="491" t="n"/>
-      <c r="AT16" s="491" t="n"/>
+      <c r="AS16" s="492" t="n"/>
+      <c r="AT16" s="496" t="n"/>
       <c r="AU16" s="491" t="n"/>
       <c r="AV16" s="491" t="n"/>
       <c r="AW16" s="491" t="n"/>
@@ -6549,26 +6655,26 @@
       <c r="AY16" s="491" t="n"/>
       <c r="AZ16" s="491" t="n"/>
       <c r="BA16" s="491" t="n"/>
-      <c r="BB16" s="491" t="n"/>
-      <c r="BC16" s="491" t="n"/>
+      <c r="BB16" s="492" t="n"/>
+      <c r="BC16" s="497" t="n"/>
       <c r="BD16" s="491" t="n"/>
       <c r="BE16" s="491" t="n"/>
       <c r="BF16" s="491" t="n"/>
       <c r="BG16" s="491" t="n"/>
       <c r="BH16" s="491" t="n"/>
       <c r="BI16" s="491" t="n"/>
-      <c r="BJ16" s="492" t="n"/>
-      <c r="BK16" s="496" t="n"/>
-      <c r="BL16" s="491" t="n"/>
+      <c r="BJ16" s="491" t="n"/>
+      <c r="BK16" s="492" t="n"/>
+      <c r="BL16" s="497" t="n"/>
       <c r="BM16" s="491" t="n"/>
       <c r="BN16" s="491" t="n"/>
       <c r="BO16" s="491" t="n"/>
       <c r="BP16" s="491" t="n"/>
       <c r="BQ16" s="491" t="n"/>
-      <c r="BR16" s="492" t="n"/>
-      <c r="BS16" s="497" t="n"/>
-      <c r="BT16" s="491" t="n"/>
-      <c r="BU16" s="491" t="n"/>
+      <c r="BR16" s="491" t="n"/>
+      <c r="BS16" s="491" t="n"/>
+      <c r="BT16" s="492" t="n"/>
+      <c r="BU16" s="498" t="n"/>
       <c r="BV16" s="491" t="n"/>
       <c r="BW16" s="491" t="n"/>
       <c r="BX16" s="491" t="n"/>
@@ -6577,30 +6683,31 @@
       <c r="CA16" s="491" t="n"/>
       <c r="CB16" s="491" t="n"/>
       <c r="CC16" s="491" t="n"/>
-      <c r="CD16" s="498" t="n"/>
+      <c r="CD16" s="499" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="491" t="n"/>
-      <c r="D17" s="492" t="n"/>
-      <c r="E17" s="500" t="n"/>
+      <c r="D17" s="491" t="n"/>
+      <c r="E17" s="491" t="n"/>
       <c r="F17" s="491" t="n"/>
       <c r="G17" s="491" t="n"/>
       <c r="H17" s="491" t="n"/>
-      <c r="I17" s="491" t="n"/>
-      <c r="J17" s="492" t="n"/>
-      <c r="K17" s="501" t="n"/>
+      <c r="I17" s="492" t="n"/>
+      <c r="J17" s="501" t="n"/>
+      <c r="K17" s="491" t="n"/>
       <c r="L17" s="491" t="n"/>
       <c r="M17" s="491" t="n"/>
       <c r="N17" s="491" t="n"/>
       <c r="O17" s="491" t="n"/>
       <c r="P17" s="491" t="n"/>
       <c r="Q17" s="491" t="n"/>
-      <c r="R17" s="491" t="n"/>
-      <c r="S17" s="491" t="n"/>
+      <c r="R17" s="492" t="n"/>
+      <c r="S17" s="502" t="n"/>
       <c r="T17" s="491" t="n"/>
       <c r="U17" s="491" t="n"/>
       <c r="V17" s="491" t="n"/>
@@ -6608,8 +6715,8 @@
       <c r="X17" s="491" t="n"/>
       <c r="Y17" s="491" t="n"/>
       <c r="Z17" s="491" t="n"/>
-      <c r="AA17" s="491" t="n"/>
-      <c r="AB17" s="491" t="n"/>
+      <c r="AA17" s="492" t="n"/>
+      <c r="AB17" s="501" t="n"/>
       <c r="AC17" s="491" t="n"/>
       <c r="AD17" s="491" t="n"/>
       <c r="AE17" s="491" t="n"/>
@@ -6617,17 +6724,17 @@
       <c r="AG17" s="491" t="n"/>
       <c r="AH17" s="491" t="n"/>
       <c r="AI17" s="491" t="n"/>
-      <c r="AJ17" s="491" t="n"/>
-      <c r="AK17" s="491" t="n"/>
+      <c r="AJ17" s="492" t="n"/>
+      <c r="AK17" s="496" t="n"/>
       <c r="AL17" s="491" t="n"/>
       <c r="AM17" s="491" t="n"/>
       <c r="AN17" s="491" t="n"/>
       <c r="AO17" s="491" t="n"/>
-      <c r="AP17" s="492" t="n"/>
-      <c r="AQ17" s="500" t="n"/>
+      <c r="AP17" s="491" t="n"/>
+      <c r="AQ17" s="491" t="n"/>
       <c r="AR17" s="491" t="n"/>
-      <c r="AS17" s="491" t="n"/>
-      <c r="AT17" s="491" t="n"/>
+      <c r="AS17" s="492" t="n"/>
+      <c r="AT17" s="496" t="n"/>
       <c r="AU17" s="491" t="n"/>
       <c r="AV17" s="491" t="n"/>
       <c r="AW17" s="491" t="n"/>
@@ -6635,26 +6742,26 @@
       <c r="AY17" s="491" t="n"/>
       <c r="AZ17" s="491" t="n"/>
       <c r="BA17" s="491" t="n"/>
-      <c r="BB17" s="491" t="n"/>
-      <c r="BC17" s="491" t="n"/>
+      <c r="BB17" s="492" t="n"/>
+      <c r="BC17" s="497" t="n"/>
       <c r="BD17" s="491" t="n"/>
       <c r="BE17" s="491" t="n"/>
       <c r="BF17" s="491" t="n"/>
       <c r="BG17" s="491" t="n"/>
       <c r="BH17" s="491" t="n"/>
       <c r="BI17" s="491" t="n"/>
-      <c r="BJ17" s="492" t="n"/>
-      <c r="BK17" s="496" t="n"/>
-      <c r="BL17" s="491" t="n"/>
+      <c r="BJ17" s="491" t="n"/>
+      <c r="BK17" s="492" t="n"/>
+      <c r="BL17" s="497" t="n"/>
       <c r="BM17" s="491" t="n"/>
       <c r="BN17" s="491" t="n"/>
       <c r="BO17" s="491" t="n"/>
       <c r="BP17" s="491" t="n"/>
       <c r="BQ17" s="491" t="n"/>
-      <c r="BR17" s="492" t="n"/>
-      <c r="BS17" s="497" t="n"/>
-      <c r="BT17" s="491" t="n"/>
-      <c r="BU17" s="491" t="n"/>
+      <c r="BR17" s="491" t="n"/>
+      <c r="BS17" s="491" t="n"/>
+      <c r="BT17" s="492" t="n"/>
+      <c r="BU17" s="498" t="n"/>
       <c r="BV17" s="491" t="n"/>
       <c r="BW17" s="491" t="n"/>
       <c r="BX17" s="491" t="n"/>
@@ -6663,30 +6770,31 @@
       <c r="CA17" s="491" t="n"/>
       <c r="CB17" s="491" t="n"/>
       <c r="CC17" s="491" t="n"/>
-      <c r="CD17" s="498" t="n"/>
+      <c r="CD17" s="499" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="491" t="n"/>
-      <c r="D18" s="492" t="n"/>
-      <c r="E18" s="500" t="n"/>
+      <c r="D18" s="491" t="n"/>
+      <c r="E18" s="491" t="n"/>
       <c r="F18" s="491" t="n"/>
       <c r="G18" s="491" t="n"/>
       <c r="H18" s="491" t="n"/>
-      <c r="I18" s="491" t="n"/>
-      <c r="J18" s="492" t="n"/>
-      <c r="K18" s="502" t="n"/>
+      <c r="I18" s="492" t="n"/>
+      <c r="J18" s="501" t="n"/>
+      <c r="K18" s="491" t="n"/>
       <c r="L18" s="491" t="n"/>
       <c r="M18" s="491" t="n"/>
       <c r="N18" s="491" t="n"/>
       <c r="O18" s="491" t="n"/>
       <c r="P18" s="491" t="n"/>
       <c r="Q18" s="491" t="n"/>
-      <c r="R18" s="491" t="n"/>
-      <c r="S18" s="491" t="n"/>
+      <c r="R18" s="492" t="n"/>
+      <c r="S18" s="503" t="n"/>
       <c r="T18" s="491" t="n"/>
       <c r="U18" s="491" t="n"/>
       <c r="V18" s="491" t="n"/>
@@ -6694,8 +6802,8 @@
       <c r="X18" s="491" t="n"/>
       <c r="Y18" s="491" t="n"/>
       <c r="Z18" s="491" t="n"/>
-      <c r="AA18" s="491" t="n"/>
-      <c r="AB18" s="491" t="n"/>
+      <c r="AA18" s="492" t="n"/>
+      <c r="AB18" s="501" t="n"/>
       <c r="AC18" s="491" t="n"/>
       <c r="AD18" s="491" t="n"/>
       <c r="AE18" s="491" t="n"/>
@@ -6703,17 +6811,17 @@
       <c r="AG18" s="491" t="n"/>
       <c r="AH18" s="491" t="n"/>
       <c r="AI18" s="491" t="n"/>
-      <c r="AJ18" s="491" t="n"/>
-      <c r="AK18" s="491" t="n"/>
+      <c r="AJ18" s="492" t="n"/>
+      <c r="AK18" s="496" t="n"/>
       <c r="AL18" s="491" t="n"/>
       <c r="AM18" s="491" t="n"/>
       <c r="AN18" s="491" t="n"/>
       <c r="AO18" s="491" t="n"/>
-      <c r="AP18" s="492" t="n"/>
-      <c r="AQ18" s="500" t="n"/>
+      <c r="AP18" s="491" t="n"/>
+      <c r="AQ18" s="491" t="n"/>
       <c r="AR18" s="491" t="n"/>
-      <c r="AS18" s="491" t="n"/>
-      <c r="AT18" s="491" t="n"/>
+      <c r="AS18" s="492" t="n"/>
+      <c r="AT18" s="496" t="n"/>
       <c r="AU18" s="491" t="n"/>
       <c r="AV18" s="491" t="n"/>
       <c r="AW18" s="491" t="n"/>
@@ -6721,26 +6829,26 @@
       <c r="AY18" s="491" t="n"/>
       <c r="AZ18" s="491" t="n"/>
       <c r="BA18" s="491" t="n"/>
-      <c r="BB18" s="491" t="n"/>
-      <c r="BC18" s="491" t="n"/>
+      <c r="BB18" s="492" t="n"/>
+      <c r="BC18" s="497" t="n"/>
       <c r="BD18" s="491" t="n"/>
       <c r="BE18" s="491" t="n"/>
       <c r="BF18" s="491" t="n"/>
       <c r="BG18" s="491" t="n"/>
       <c r="BH18" s="491" t="n"/>
       <c r="BI18" s="491" t="n"/>
-      <c r="BJ18" s="492" t="n"/>
-      <c r="BK18" s="496" t="n"/>
-      <c r="BL18" s="491" t="n"/>
+      <c r="BJ18" s="491" t="n"/>
+      <c r="BK18" s="492" t="n"/>
+      <c r="BL18" s="497" t="n"/>
       <c r="BM18" s="491" t="n"/>
       <c r="BN18" s="491" t="n"/>
       <c r="BO18" s="491" t="n"/>
       <c r="BP18" s="491" t="n"/>
       <c r="BQ18" s="491" t="n"/>
-      <c r="BR18" s="492" t="n"/>
-      <c r="BS18" s="497" t="n"/>
-      <c r="BT18" s="491" t="n"/>
-      <c r="BU18" s="491" t="n"/>
+      <c r="BR18" s="491" t="n"/>
+      <c r="BS18" s="491" t="n"/>
+      <c r="BT18" s="492" t="n"/>
+      <c r="BU18" s="498" t="n"/>
       <c r="BV18" s="491" t="n"/>
       <c r="BW18" s="491" t="n"/>
       <c r="BX18" s="491" t="n"/>
@@ -6749,30 +6857,31 @@
       <c r="CA18" s="491" t="n"/>
       <c r="CB18" s="491" t="n"/>
       <c r="CC18" s="491" t="n"/>
-      <c r="CD18" s="498" t="n"/>
+      <c r="CD18" s="499" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="491" t="n"/>
-      <c r="D19" s="492" t="n"/>
-      <c r="E19" s="500" t="n"/>
+      <c r="D19" s="491" t="n"/>
+      <c r="E19" s="491" t="n"/>
       <c r="F19" s="491" t="n"/>
       <c r="G19" s="491" t="n"/>
       <c r="H19" s="491" t="n"/>
-      <c r="I19" s="491" t="n"/>
-      <c r="J19" s="492" t="n"/>
-      <c r="K19" s="501" t="n"/>
+      <c r="I19" s="492" t="n"/>
+      <c r="J19" s="501" t="n"/>
+      <c r="K19" s="491" t="n"/>
       <c r="L19" s="491" t="n"/>
       <c r="M19" s="491" t="n"/>
       <c r="N19" s="491" t="n"/>
       <c r="O19" s="491" t="n"/>
       <c r="P19" s="491" t="n"/>
       <c r="Q19" s="491" t="n"/>
-      <c r="R19" s="491" t="n"/>
-      <c r="S19" s="491" t="n"/>
+      <c r="R19" s="492" t="n"/>
+      <c r="S19" s="502" t="n"/>
       <c r="T19" s="491" t="n"/>
       <c r="U19" s="491" t="n"/>
       <c r="V19" s="491" t="n"/>
@@ -6780,8 +6889,8 @@
       <c r="X19" s="491" t="n"/>
       <c r="Y19" s="491" t="n"/>
       <c r="Z19" s="491" t="n"/>
-      <c r="AA19" s="491" t="n"/>
-      <c r="AB19" s="491" t="n"/>
+      <c r="AA19" s="492" t="n"/>
+      <c r="AB19" s="501" t="n"/>
       <c r="AC19" s="491" t="n"/>
       <c r="AD19" s="491" t="n"/>
       <c r="AE19" s="491" t="n"/>
@@ -6789,17 +6898,17 @@
       <c r="AG19" s="491" t="n"/>
       <c r="AH19" s="491" t="n"/>
       <c r="AI19" s="491" t="n"/>
-      <c r="AJ19" s="491" t="n"/>
-      <c r="AK19" s="491" t="n"/>
+      <c r="AJ19" s="492" t="n"/>
+      <c r="AK19" s="496" t="n"/>
       <c r="AL19" s="491" t="n"/>
       <c r="AM19" s="491" t="n"/>
       <c r="AN19" s="491" t="n"/>
       <c r="AO19" s="491" t="n"/>
-      <c r="AP19" s="492" t="n"/>
-      <c r="AQ19" s="500" t="n"/>
+      <c r="AP19" s="491" t="n"/>
+      <c r="AQ19" s="491" t="n"/>
       <c r="AR19" s="491" t="n"/>
-      <c r="AS19" s="491" t="n"/>
-      <c r="AT19" s="491" t="n"/>
+      <c r="AS19" s="492" t="n"/>
+      <c r="AT19" s="496" t="n"/>
       <c r="AU19" s="491" t="n"/>
       <c r="AV19" s="491" t="n"/>
       <c r="AW19" s="491" t="n"/>
@@ -6807,26 +6916,26 @@
       <c r="AY19" s="491" t="n"/>
       <c r="AZ19" s="491" t="n"/>
       <c r="BA19" s="491" t="n"/>
-      <c r="BB19" s="491" t="n"/>
-      <c r="BC19" s="491" t="n"/>
+      <c r="BB19" s="492" t="n"/>
+      <c r="BC19" s="497" t="n"/>
       <c r="BD19" s="491" t="n"/>
       <c r="BE19" s="491" t="n"/>
       <c r="BF19" s="491" t="n"/>
       <c r="BG19" s="491" t="n"/>
       <c r="BH19" s="491" t="n"/>
       <c r="BI19" s="491" t="n"/>
-      <c r="BJ19" s="492" t="n"/>
-      <c r="BK19" s="496" t="n"/>
-      <c r="BL19" s="491" t="n"/>
+      <c r="BJ19" s="491" t="n"/>
+      <c r="BK19" s="492" t="n"/>
+      <c r="BL19" s="497" t="n"/>
       <c r="BM19" s="491" t="n"/>
       <c r="BN19" s="491" t="n"/>
       <c r="BO19" s="491" t="n"/>
       <c r="BP19" s="491" t="n"/>
       <c r="BQ19" s="491" t="n"/>
-      <c r="BR19" s="492" t="n"/>
-      <c r="BS19" s="497" t="n"/>
-      <c r="BT19" s="491" t="n"/>
-      <c r="BU19" s="491" t="n"/>
+      <c r="BR19" s="491" t="n"/>
+      <c r="BS19" s="491" t="n"/>
+      <c r="BT19" s="492" t="n"/>
+      <c r="BU19" s="498" t="n"/>
       <c r="BV19" s="491" t="n"/>
       <c r="BW19" s="491" t="n"/>
       <c r="BX19" s="491" t="n"/>
@@ -6835,30 +6944,31 @@
       <c r="CA19" s="491" t="n"/>
       <c r="CB19" s="491" t="n"/>
       <c r="CC19" s="491" t="n"/>
-      <c r="CD19" s="498" t="n"/>
+      <c r="CD19" s="499" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="491" t="n"/>
-      <c r="D20" s="492" t="n"/>
-      <c r="E20" s="500" t="n"/>
+      <c r="D20" s="491" t="n"/>
+      <c r="E20" s="491" t="n"/>
       <c r="F20" s="491" t="n"/>
       <c r="G20" s="491" t="n"/>
       <c r="H20" s="491" t="n"/>
-      <c r="I20" s="491" t="n"/>
-      <c r="J20" s="492" t="n"/>
-      <c r="K20" s="502" t="n"/>
+      <c r="I20" s="492" t="n"/>
+      <c r="J20" s="501" t="n"/>
+      <c r="K20" s="491" t="n"/>
       <c r="L20" s="491" t="n"/>
       <c r="M20" s="491" t="n"/>
       <c r="N20" s="491" t="n"/>
       <c r="O20" s="491" t="n"/>
       <c r="P20" s="491" t="n"/>
       <c r="Q20" s="491" t="n"/>
-      <c r="R20" s="491" t="n"/>
-      <c r="S20" s="491" t="n"/>
+      <c r="R20" s="492" t="n"/>
+      <c r="S20" s="503" t="n"/>
       <c r="T20" s="491" t="n"/>
       <c r="U20" s="491" t="n"/>
       <c r="V20" s="491" t="n"/>
@@ -6866,8 +6976,8 @@
       <c r="X20" s="491" t="n"/>
       <c r="Y20" s="491" t="n"/>
       <c r="Z20" s="491" t="n"/>
-      <c r="AA20" s="491" t="n"/>
-      <c r="AB20" s="491" t="n"/>
+      <c r="AA20" s="492" t="n"/>
+      <c r="AB20" s="501" t="n"/>
       <c r="AC20" s="491" t="n"/>
       <c r="AD20" s="491" t="n"/>
       <c r="AE20" s="491" t="n"/>
@@ -6875,17 +6985,17 @@
       <c r="AG20" s="491" t="n"/>
       <c r="AH20" s="491" t="n"/>
       <c r="AI20" s="491" t="n"/>
-      <c r="AJ20" s="491" t="n"/>
-      <c r="AK20" s="491" t="n"/>
+      <c r="AJ20" s="492" t="n"/>
+      <c r="AK20" s="496" t="n"/>
       <c r="AL20" s="491" t="n"/>
       <c r="AM20" s="491" t="n"/>
       <c r="AN20" s="491" t="n"/>
       <c r="AO20" s="491" t="n"/>
-      <c r="AP20" s="492" t="n"/>
-      <c r="AQ20" s="500" t="n"/>
+      <c r="AP20" s="491" t="n"/>
+      <c r="AQ20" s="491" t="n"/>
       <c r="AR20" s="491" t="n"/>
-      <c r="AS20" s="491" t="n"/>
-      <c r="AT20" s="491" t="n"/>
+      <c r="AS20" s="492" t="n"/>
+      <c r="AT20" s="496" t="n"/>
       <c r="AU20" s="491" t="n"/>
       <c r="AV20" s="491" t="n"/>
       <c r="AW20" s="491" t="n"/>
@@ -6893,26 +7003,26 @@
       <c r="AY20" s="491" t="n"/>
       <c r="AZ20" s="491" t="n"/>
       <c r="BA20" s="491" t="n"/>
-      <c r="BB20" s="491" t="n"/>
-      <c r="BC20" s="491" t="n"/>
+      <c r="BB20" s="492" t="n"/>
+      <c r="BC20" s="497" t="n"/>
       <c r="BD20" s="491" t="n"/>
       <c r="BE20" s="491" t="n"/>
       <c r="BF20" s="491" t="n"/>
       <c r="BG20" s="491" t="n"/>
       <c r="BH20" s="491" t="n"/>
       <c r="BI20" s="491" t="n"/>
-      <c r="BJ20" s="492" t="n"/>
-      <c r="BK20" s="496" t="n"/>
-      <c r="BL20" s="491" t="n"/>
+      <c r="BJ20" s="491" t="n"/>
+      <c r="BK20" s="492" t="n"/>
+      <c r="BL20" s="497" t="n"/>
       <c r="BM20" s="491" t="n"/>
       <c r="BN20" s="491" t="n"/>
       <c r="BO20" s="491" t="n"/>
       <c r="BP20" s="491" t="n"/>
       <c r="BQ20" s="491" t="n"/>
-      <c r="BR20" s="492" t="n"/>
-      <c r="BS20" s="497" t="n"/>
-      <c r="BT20" s="491" t="n"/>
-      <c r="BU20" s="491" t="n"/>
+      <c r="BR20" s="491" t="n"/>
+      <c r="BS20" s="491" t="n"/>
+      <c r="BT20" s="492" t="n"/>
+      <c r="BU20" s="498" t="n"/>
       <c r="BV20" s="491" t="n"/>
       <c r="BW20" s="491" t="n"/>
       <c r="BX20" s="491" t="n"/>
@@ -6921,30 +7031,31 @@
       <c r="CA20" s="491" t="n"/>
       <c r="CB20" s="491" t="n"/>
       <c r="CC20" s="491" t="n"/>
-      <c r="CD20" s="498" t="n"/>
+      <c r="CD20" s="499" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>8</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
       <c r="C21" s="491" t="n"/>
-      <c r="D21" s="492" t="n"/>
-      <c r="E21" s="500" t="n"/>
+      <c r="D21" s="491" t="n"/>
+      <c r="E21" s="491" t="n"/>
       <c r="F21" s="491" t="n"/>
       <c r="G21" s="491" t="n"/>
       <c r="H21" s="491" t="n"/>
-      <c r="I21" s="491" t="n"/>
-      <c r="J21" s="492" t="n"/>
-      <c r="K21" s="501" t="n"/>
+      <c r="I21" s="492" t="n"/>
+      <c r="J21" s="501" t="n"/>
+      <c r="K21" s="491" t="n"/>
       <c r="L21" s="491" t="n"/>
       <c r="M21" s="491" t="n"/>
       <c r="N21" s="491" t="n"/>
       <c r="O21" s="491" t="n"/>
       <c r="P21" s="491" t="n"/>
       <c r="Q21" s="491" t="n"/>
-      <c r="R21" s="491" t="n"/>
-      <c r="S21" s="491" t="n"/>
+      <c r="R21" s="492" t="n"/>
+      <c r="S21" s="502" t="n"/>
       <c r="T21" s="491" t="n"/>
       <c r="U21" s="491" t="n"/>
       <c r="V21" s="491" t="n"/>
@@ -6952,8 +7063,8 @@
       <c r="X21" s="491" t="n"/>
       <c r="Y21" s="491" t="n"/>
       <c r="Z21" s="491" t="n"/>
-      <c r="AA21" s="491" t="n"/>
-      <c r="AB21" s="491" t="n"/>
+      <c r="AA21" s="492" t="n"/>
+      <c r="AB21" s="501" t="n"/>
       <c r="AC21" s="491" t="n"/>
       <c r="AD21" s="491" t="n"/>
       <c r="AE21" s="491" t="n"/>
@@ -6961,17 +7072,17 @@
       <c r="AG21" s="491" t="n"/>
       <c r="AH21" s="491" t="n"/>
       <c r="AI21" s="491" t="n"/>
-      <c r="AJ21" s="491" t="n"/>
-      <c r="AK21" s="491" t="n"/>
+      <c r="AJ21" s="492" t="n"/>
+      <c r="AK21" s="496" t="n"/>
       <c r="AL21" s="491" t="n"/>
       <c r="AM21" s="491" t="n"/>
       <c r="AN21" s="491" t="n"/>
       <c r="AO21" s="491" t="n"/>
-      <c r="AP21" s="492" t="n"/>
-      <c r="AQ21" s="500" t="n"/>
+      <c r="AP21" s="491" t="n"/>
+      <c r="AQ21" s="491" t="n"/>
       <c r="AR21" s="491" t="n"/>
-      <c r="AS21" s="491" t="n"/>
-      <c r="AT21" s="491" t="n"/>
+      <c r="AS21" s="492" t="n"/>
+      <c r="AT21" s="496" t="n"/>
       <c r="AU21" s="491" t="n"/>
       <c r="AV21" s="491" t="n"/>
       <c r="AW21" s="491" t="n"/>
@@ -6979,26 +7090,26 @@
       <c r="AY21" s="491" t="n"/>
       <c r="AZ21" s="491" t="n"/>
       <c r="BA21" s="491" t="n"/>
-      <c r="BB21" s="491" t="n"/>
-      <c r="BC21" s="491" t="n"/>
+      <c r="BB21" s="492" t="n"/>
+      <c r="BC21" s="497" t="n"/>
       <c r="BD21" s="491" t="n"/>
       <c r="BE21" s="491" t="n"/>
       <c r="BF21" s="491" t="n"/>
       <c r="BG21" s="491" t="n"/>
       <c r="BH21" s="491" t="n"/>
       <c r="BI21" s="491" t="n"/>
-      <c r="BJ21" s="492" t="n"/>
-      <c r="BK21" s="496" t="n"/>
-      <c r="BL21" s="491" t="n"/>
+      <c r="BJ21" s="491" t="n"/>
+      <c r="BK21" s="492" t="n"/>
+      <c r="BL21" s="497" t="n"/>
       <c r="BM21" s="491" t="n"/>
       <c r="BN21" s="491" t="n"/>
       <c r="BO21" s="491" t="n"/>
       <c r="BP21" s="491" t="n"/>
       <c r="BQ21" s="491" t="n"/>
-      <c r="BR21" s="492" t="n"/>
-      <c r="BS21" s="497" t="n"/>
-      <c r="BT21" s="491" t="n"/>
-      <c r="BU21" s="491" t="n"/>
+      <c r="BR21" s="491" t="n"/>
+      <c r="BS21" s="491" t="n"/>
+      <c r="BT21" s="492" t="n"/>
+      <c r="BU21" s="498" t="n"/>
       <c r="BV21" s="491" t="n"/>
       <c r="BW21" s="491" t="n"/>
       <c r="BX21" s="491" t="n"/>
@@ -7007,30 +7118,31 @@
       <c r="CA21" s="491" t="n"/>
       <c r="CB21" s="491" t="n"/>
       <c r="CC21" s="491" t="n"/>
-      <c r="CD21" s="498" t="n"/>
+      <c r="CD21" s="499" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>9</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
       <c r="C22" s="491" t="n"/>
-      <c r="D22" s="492" t="n"/>
-      <c r="E22" s="500" t="n"/>
+      <c r="D22" s="491" t="n"/>
+      <c r="E22" s="491" t="n"/>
       <c r="F22" s="491" t="n"/>
       <c r="G22" s="491" t="n"/>
       <c r="H22" s="491" t="n"/>
-      <c r="I22" s="491" t="n"/>
-      <c r="J22" s="492" t="n"/>
-      <c r="K22" s="502" t="n"/>
+      <c r="I22" s="492" t="n"/>
+      <c r="J22" s="501" t="n"/>
+      <c r="K22" s="491" t="n"/>
       <c r="L22" s="491" t="n"/>
       <c r="M22" s="491" t="n"/>
       <c r="N22" s="491" t="n"/>
       <c r="O22" s="491" t="n"/>
       <c r="P22" s="491" t="n"/>
       <c r="Q22" s="491" t="n"/>
-      <c r="R22" s="491" t="n"/>
-      <c r="S22" s="491" t="n"/>
+      <c r="R22" s="492" t="n"/>
+      <c r="S22" s="503" t="n"/>
       <c r="T22" s="491" t="n"/>
       <c r="U22" s="491" t="n"/>
       <c r="V22" s="491" t="n"/>
@@ -7038,8 +7150,8 @@
       <c r="X22" s="491" t="n"/>
       <c r="Y22" s="491" t="n"/>
       <c r="Z22" s="491" t="n"/>
-      <c r="AA22" s="491" t="n"/>
-      <c r="AB22" s="491" t="n"/>
+      <c r="AA22" s="492" t="n"/>
+      <c r="AB22" s="501" t="n"/>
       <c r="AC22" s="491" t="n"/>
       <c r="AD22" s="491" t="n"/>
       <c r="AE22" s="491" t="n"/>
@@ -7047,17 +7159,17 @@
       <c r="AG22" s="491" t="n"/>
       <c r="AH22" s="491" t="n"/>
       <c r="AI22" s="491" t="n"/>
-      <c r="AJ22" s="491" t="n"/>
-      <c r="AK22" s="491" t="n"/>
+      <c r="AJ22" s="492" t="n"/>
+      <c r="AK22" s="496" t="n"/>
       <c r="AL22" s="491" t="n"/>
       <c r="AM22" s="491" t="n"/>
       <c r="AN22" s="491" t="n"/>
       <c r="AO22" s="491" t="n"/>
-      <c r="AP22" s="492" t="n"/>
-      <c r="AQ22" s="500" t="n"/>
+      <c r="AP22" s="491" t="n"/>
+      <c r="AQ22" s="491" t="n"/>
       <c r="AR22" s="491" t="n"/>
-      <c r="AS22" s="491" t="n"/>
-      <c r="AT22" s="491" t="n"/>
+      <c r="AS22" s="492" t="n"/>
+      <c r="AT22" s="496" t="n"/>
       <c r="AU22" s="491" t="n"/>
       <c r="AV22" s="491" t="n"/>
       <c r="AW22" s="491" t="n"/>
@@ -7065,26 +7177,26 @@
       <c r="AY22" s="491" t="n"/>
       <c r="AZ22" s="491" t="n"/>
       <c r="BA22" s="491" t="n"/>
-      <c r="BB22" s="491" t="n"/>
-      <c r="BC22" s="491" t="n"/>
+      <c r="BB22" s="492" t="n"/>
+      <c r="BC22" s="497" t="n"/>
       <c r="BD22" s="491" t="n"/>
       <c r="BE22" s="491" t="n"/>
       <c r="BF22" s="491" t="n"/>
       <c r="BG22" s="491" t="n"/>
       <c r="BH22" s="491" t="n"/>
       <c r="BI22" s="491" t="n"/>
-      <c r="BJ22" s="492" t="n"/>
-      <c r="BK22" s="496" t="n"/>
-      <c r="BL22" s="491" t="n"/>
+      <c r="BJ22" s="491" t="n"/>
+      <c r="BK22" s="492" t="n"/>
+      <c r="BL22" s="497" t="n"/>
       <c r="BM22" s="491" t="n"/>
       <c r="BN22" s="491" t="n"/>
       <c r="BO22" s="491" t="n"/>
       <c r="BP22" s="491" t="n"/>
       <c r="BQ22" s="491" t="n"/>
-      <c r="BR22" s="492" t="n"/>
-      <c r="BS22" s="497" t="n"/>
-      <c r="BT22" s="491" t="n"/>
-      <c r="BU22" s="491" t="n"/>
+      <c r="BR22" s="491" t="n"/>
+      <c r="BS22" s="491" t="n"/>
+      <c r="BT22" s="492" t="n"/>
+      <c r="BU22" s="498" t="n"/>
       <c r="BV22" s="491" t="n"/>
       <c r="BW22" s="491" t="n"/>
       <c r="BX22" s="491" t="n"/>
@@ -7093,30 +7205,31 @@
       <c r="CA22" s="491" t="n"/>
       <c r="CB22" s="491" t="n"/>
       <c r="CC22" s="491" t="n"/>
-      <c r="CD22" s="498" t="n"/>
+      <c r="CD22" s="499" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="490" t="n">
-        <v>10</v>
+      <c r="A23" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B23" s="491" t="n"/>
       <c r="C23" s="491" t="n"/>
-      <c r="D23" s="492" t="n"/>
-      <c r="E23" s="500" t="n"/>
+      <c r="D23" s="491" t="n"/>
+      <c r="E23" s="491" t="n"/>
       <c r="F23" s="491" t="n"/>
       <c r="G23" s="491" t="n"/>
       <c r="H23" s="491" t="n"/>
-      <c r="I23" s="491" t="n"/>
-      <c r="J23" s="492" t="n"/>
-      <c r="K23" s="501" t="n"/>
+      <c r="I23" s="492" t="n"/>
+      <c r="J23" s="501" t="n"/>
+      <c r="K23" s="491" t="n"/>
       <c r="L23" s="491" t="n"/>
       <c r="M23" s="491" t="n"/>
       <c r="N23" s="491" t="n"/>
       <c r="O23" s="491" t="n"/>
       <c r="P23" s="491" t="n"/>
       <c r="Q23" s="491" t="n"/>
-      <c r="R23" s="491" t="n"/>
-      <c r="S23" s="491" t="n"/>
+      <c r="R23" s="492" t="n"/>
+      <c r="S23" s="502" t="n"/>
       <c r="T23" s="491" t="n"/>
       <c r="U23" s="491" t="n"/>
       <c r="V23" s="491" t="n"/>
@@ -7124,8 +7237,8 @@
       <c r="X23" s="491" t="n"/>
       <c r="Y23" s="491" t="n"/>
       <c r="Z23" s="491" t="n"/>
-      <c r="AA23" s="491" t="n"/>
-      <c r="AB23" s="491" t="n"/>
+      <c r="AA23" s="492" t="n"/>
+      <c r="AB23" s="501" t="n"/>
       <c r="AC23" s="491" t="n"/>
       <c r="AD23" s="491" t="n"/>
       <c r="AE23" s="491" t="n"/>
@@ -7133,17 +7246,17 @@
       <c r="AG23" s="491" t="n"/>
       <c r="AH23" s="491" t="n"/>
       <c r="AI23" s="491" t="n"/>
-      <c r="AJ23" s="491" t="n"/>
-      <c r="AK23" s="491" t="n"/>
+      <c r="AJ23" s="492" t="n"/>
+      <c r="AK23" s="496" t="n"/>
       <c r="AL23" s="491" t="n"/>
       <c r="AM23" s="491" t="n"/>
       <c r="AN23" s="491" t="n"/>
       <c r="AO23" s="491" t="n"/>
-      <c r="AP23" s="492" t="n"/>
-      <c r="AQ23" s="500" t="n"/>
+      <c r="AP23" s="491" t="n"/>
+      <c r="AQ23" s="491" t="n"/>
       <c r="AR23" s="491" t="n"/>
-      <c r="AS23" s="491" t="n"/>
-      <c r="AT23" s="491" t="n"/>
+      <c r="AS23" s="492" t="n"/>
+      <c r="AT23" s="496" t="n"/>
       <c r="AU23" s="491" t="n"/>
       <c r="AV23" s="491" t="n"/>
       <c r="AW23" s="491" t="n"/>
@@ -7151,26 +7264,26 @@
       <c r="AY23" s="491" t="n"/>
       <c r="AZ23" s="491" t="n"/>
       <c r="BA23" s="491" t="n"/>
-      <c r="BB23" s="491" t="n"/>
-      <c r="BC23" s="491" t="n"/>
+      <c r="BB23" s="492" t="n"/>
+      <c r="BC23" s="497" t="n"/>
       <c r="BD23" s="491" t="n"/>
       <c r="BE23" s="491" t="n"/>
       <c r="BF23" s="491" t="n"/>
       <c r="BG23" s="491" t="n"/>
       <c r="BH23" s="491" t="n"/>
       <c r="BI23" s="491" t="n"/>
-      <c r="BJ23" s="492" t="n"/>
-      <c r="BK23" s="496" t="n"/>
-      <c r="BL23" s="491" t="n"/>
+      <c r="BJ23" s="491" t="n"/>
+      <c r="BK23" s="492" t="n"/>
+      <c r="BL23" s="497" t="n"/>
       <c r="BM23" s="491" t="n"/>
       <c r="BN23" s="491" t="n"/>
       <c r="BO23" s="491" t="n"/>
       <c r="BP23" s="491" t="n"/>
       <c r="BQ23" s="491" t="n"/>
-      <c r="BR23" s="492" t="n"/>
-      <c r="BS23" s="497" t="n"/>
-      <c r="BT23" s="491" t="n"/>
-      <c r="BU23" s="491" t="n"/>
+      <c r="BR23" s="491" t="n"/>
+      <c r="BS23" s="491" t="n"/>
+      <c r="BT23" s="492" t="n"/>
+      <c r="BU23" s="498" t="n"/>
       <c r="BV23" s="491" t="n"/>
       <c r="BW23" s="491" t="n"/>
       <c r="BX23" s="491" t="n"/>
@@ -7179,30 +7292,31 @@
       <c r="CA23" s="491" t="n"/>
       <c r="CB23" s="491" t="n"/>
       <c r="CC23" s="491" t="n"/>
-      <c r="CD23" s="498" t="n"/>
+      <c r="CD23" s="499" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1" s="264">
-      <c r="A24" s="490" t="n">
-        <v>11</v>
+      <c r="A24" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B24" s="491" t="n"/>
       <c r="C24" s="491" t="n"/>
-      <c r="D24" s="492" t="n"/>
-      <c r="E24" s="500" t="n"/>
+      <c r="D24" s="491" t="n"/>
+      <c r="E24" s="491" t="n"/>
       <c r="F24" s="491" t="n"/>
       <c r="G24" s="491" t="n"/>
       <c r="H24" s="491" t="n"/>
-      <c r="I24" s="491" t="n"/>
-      <c r="J24" s="492" t="n"/>
-      <c r="K24" s="502" t="n"/>
+      <c r="I24" s="492" t="n"/>
+      <c r="J24" s="501" t="n"/>
+      <c r="K24" s="491" t="n"/>
       <c r="L24" s="491" t="n"/>
       <c r="M24" s="491" t="n"/>
       <c r="N24" s="491" t="n"/>
       <c r="O24" s="491" t="n"/>
       <c r="P24" s="491" t="n"/>
       <c r="Q24" s="491" t="n"/>
-      <c r="R24" s="491" t="n"/>
-      <c r="S24" s="491" t="n"/>
+      <c r="R24" s="492" t="n"/>
+      <c r="S24" s="503" t="n"/>
       <c r="T24" s="491" t="n"/>
       <c r="U24" s="491" t="n"/>
       <c r="V24" s="491" t="n"/>
@@ -7210,8 +7324,8 @@
       <c r="X24" s="491" t="n"/>
       <c r="Y24" s="491" t="n"/>
       <c r="Z24" s="491" t="n"/>
-      <c r="AA24" s="491" t="n"/>
-      <c r="AB24" s="491" t="n"/>
+      <c r="AA24" s="492" t="n"/>
+      <c r="AB24" s="501" t="n"/>
       <c r="AC24" s="491" t="n"/>
       <c r="AD24" s="491" t="n"/>
       <c r="AE24" s="491" t="n"/>
@@ -7219,17 +7333,17 @@
       <c r="AG24" s="491" t="n"/>
       <c r="AH24" s="491" t="n"/>
       <c r="AI24" s="491" t="n"/>
-      <c r="AJ24" s="491" t="n"/>
-      <c r="AK24" s="491" t="n"/>
+      <c r="AJ24" s="492" t="n"/>
+      <c r="AK24" s="496" t="n"/>
       <c r="AL24" s="491" t="n"/>
       <c r="AM24" s="491" t="n"/>
       <c r="AN24" s="491" t="n"/>
       <c r="AO24" s="491" t="n"/>
-      <c r="AP24" s="492" t="n"/>
-      <c r="AQ24" s="500" t="n"/>
+      <c r="AP24" s="491" t="n"/>
+      <c r="AQ24" s="491" t="n"/>
       <c r="AR24" s="491" t="n"/>
-      <c r="AS24" s="491" t="n"/>
-      <c r="AT24" s="491" t="n"/>
+      <c r="AS24" s="492" t="n"/>
+      <c r="AT24" s="496" t="n"/>
       <c r="AU24" s="491" t="n"/>
       <c r="AV24" s="491" t="n"/>
       <c r="AW24" s="491" t="n"/>
@@ -7237,26 +7351,26 @@
       <c r="AY24" s="491" t="n"/>
       <c r="AZ24" s="491" t="n"/>
       <c r="BA24" s="491" t="n"/>
-      <c r="BB24" s="491" t="n"/>
-      <c r="BC24" s="491" t="n"/>
+      <c r="BB24" s="492" t="n"/>
+      <c r="BC24" s="497" t="n"/>
       <c r="BD24" s="491" t="n"/>
       <c r="BE24" s="491" t="n"/>
       <c r="BF24" s="491" t="n"/>
       <c r="BG24" s="491" t="n"/>
       <c r="BH24" s="491" t="n"/>
       <c r="BI24" s="491" t="n"/>
-      <c r="BJ24" s="492" t="n"/>
-      <c r="BK24" s="496" t="n"/>
-      <c r="BL24" s="491" t="n"/>
+      <c r="BJ24" s="491" t="n"/>
+      <c r="BK24" s="492" t="n"/>
+      <c r="BL24" s="497" t="n"/>
       <c r="BM24" s="491" t="n"/>
       <c r="BN24" s="491" t="n"/>
       <c r="BO24" s="491" t="n"/>
       <c r="BP24" s="491" t="n"/>
       <c r="BQ24" s="491" t="n"/>
-      <c r="BR24" s="492" t="n"/>
-      <c r="BS24" s="497" t="n"/>
-      <c r="BT24" s="491" t="n"/>
-      <c r="BU24" s="491" t="n"/>
+      <c r="BR24" s="491" t="n"/>
+      <c r="BS24" s="491" t="n"/>
+      <c r="BT24" s="492" t="n"/>
+      <c r="BU24" s="498" t="n"/>
       <c r="BV24" s="491" t="n"/>
       <c r="BW24" s="491" t="n"/>
       <c r="BX24" s="491" t="n"/>
@@ -7265,30 +7379,31 @@
       <c r="CA24" s="491" t="n"/>
       <c r="CB24" s="491" t="n"/>
       <c r="CC24" s="491" t="n"/>
-      <c r="CD24" s="498" t="n"/>
+      <c r="CD24" s="499" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1" s="264">
-      <c r="A25" s="490" t="n">
-        <v>12</v>
+      <c r="A25" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B25" s="491" t="n"/>
       <c r="C25" s="491" t="n"/>
-      <c r="D25" s="492" t="n"/>
-      <c r="E25" s="500" t="n"/>
+      <c r="D25" s="491" t="n"/>
+      <c r="E25" s="491" t="n"/>
       <c r="F25" s="491" t="n"/>
       <c r="G25" s="491" t="n"/>
       <c r="H25" s="491" t="n"/>
-      <c r="I25" s="491" t="n"/>
-      <c r="J25" s="492" t="n"/>
-      <c r="K25" s="501" t="n"/>
+      <c r="I25" s="492" t="n"/>
+      <c r="J25" s="501" t="n"/>
+      <c r="K25" s="491" t="n"/>
       <c r="L25" s="491" t="n"/>
       <c r="M25" s="491" t="n"/>
       <c r="N25" s="491" t="n"/>
       <c r="O25" s="491" t="n"/>
       <c r="P25" s="491" t="n"/>
       <c r="Q25" s="491" t="n"/>
-      <c r="R25" s="491" t="n"/>
-      <c r="S25" s="491" t="n"/>
+      <c r="R25" s="492" t="n"/>
+      <c r="S25" s="502" t="n"/>
       <c r="T25" s="491" t="n"/>
       <c r="U25" s="491" t="n"/>
       <c r="V25" s="491" t="n"/>
@@ -7296,8 +7411,8 @@
       <c r="X25" s="491" t="n"/>
       <c r="Y25" s="491" t="n"/>
       <c r="Z25" s="491" t="n"/>
-      <c r="AA25" s="491" t="n"/>
-      <c r="AB25" s="491" t="n"/>
+      <c r="AA25" s="492" t="n"/>
+      <c r="AB25" s="501" t="n"/>
       <c r="AC25" s="491" t="n"/>
       <c r="AD25" s="491" t="n"/>
       <c r="AE25" s="491" t="n"/>
@@ -7305,17 +7420,17 @@
       <c r="AG25" s="491" t="n"/>
       <c r="AH25" s="491" t="n"/>
       <c r="AI25" s="491" t="n"/>
-      <c r="AJ25" s="491" t="n"/>
-      <c r="AK25" s="491" t="n"/>
+      <c r="AJ25" s="492" t="n"/>
+      <c r="AK25" s="496" t="n"/>
       <c r="AL25" s="491" t="n"/>
       <c r="AM25" s="491" t="n"/>
       <c r="AN25" s="491" t="n"/>
       <c r="AO25" s="491" t="n"/>
-      <c r="AP25" s="492" t="n"/>
-      <c r="AQ25" s="500" t="n"/>
+      <c r="AP25" s="491" t="n"/>
+      <c r="AQ25" s="491" t="n"/>
       <c r="AR25" s="491" t="n"/>
-      <c r="AS25" s="491" t="n"/>
-      <c r="AT25" s="491" t="n"/>
+      <c r="AS25" s="492" t="n"/>
+      <c r="AT25" s="496" t="n"/>
       <c r="AU25" s="491" t="n"/>
       <c r="AV25" s="491" t="n"/>
       <c r="AW25" s="491" t="n"/>
@@ -7323,26 +7438,26 @@
       <c r="AY25" s="491" t="n"/>
       <c r="AZ25" s="491" t="n"/>
       <c r="BA25" s="491" t="n"/>
-      <c r="BB25" s="491" t="n"/>
-      <c r="BC25" s="491" t="n"/>
+      <c r="BB25" s="492" t="n"/>
+      <c r="BC25" s="497" t="n"/>
       <c r="BD25" s="491" t="n"/>
       <c r="BE25" s="491" t="n"/>
       <c r="BF25" s="491" t="n"/>
       <c r="BG25" s="491" t="n"/>
       <c r="BH25" s="491" t="n"/>
       <c r="BI25" s="491" t="n"/>
-      <c r="BJ25" s="492" t="n"/>
-      <c r="BK25" s="496" t="n"/>
-      <c r="BL25" s="491" t="n"/>
+      <c r="BJ25" s="491" t="n"/>
+      <c r="BK25" s="492" t="n"/>
+      <c r="BL25" s="497" t="n"/>
       <c r="BM25" s="491" t="n"/>
       <c r="BN25" s="491" t="n"/>
       <c r="BO25" s="491" t="n"/>
       <c r="BP25" s="491" t="n"/>
       <c r="BQ25" s="491" t="n"/>
-      <c r="BR25" s="492" t="n"/>
-      <c r="BS25" s="497" t="n"/>
-      <c r="BT25" s="491" t="n"/>
-      <c r="BU25" s="491" t="n"/>
+      <c r="BR25" s="491" t="n"/>
+      <c r="BS25" s="491" t="n"/>
+      <c r="BT25" s="492" t="n"/>
+      <c r="BU25" s="498" t="n"/>
       <c r="BV25" s="491" t="n"/>
       <c r="BW25" s="491" t="n"/>
       <c r="BX25" s="491" t="n"/>
@@ -7351,30 +7466,31 @@
       <c r="CA25" s="491" t="n"/>
       <c r="CB25" s="491" t="n"/>
       <c r="CC25" s="491" t="n"/>
-      <c r="CD25" s="498" t="n"/>
+      <c r="CD25" s="499" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1" s="264">
-      <c r="A26" s="490" t="n">
-        <v>13</v>
+      <c r="A26" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B26" s="491" t="n"/>
       <c r="C26" s="491" t="n"/>
-      <c r="D26" s="492" t="n"/>
-      <c r="E26" s="500" t="n"/>
+      <c r="D26" s="491" t="n"/>
+      <c r="E26" s="491" t="n"/>
       <c r="F26" s="491" t="n"/>
       <c r="G26" s="491" t="n"/>
       <c r="H26" s="491" t="n"/>
-      <c r="I26" s="491" t="n"/>
-      <c r="J26" s="492" t="n"/>
-      <c r="K26" s="502" t="n"/>
+      <c r="I26" s="492" t="n"/>
+      <c r="J26" s="501" t="n"/>
+      <c r="K26" s="491" t="n"/>
       <c r="L26" s="491" t="n"/>
       <c r="M26" s="491" t="n"/>
       <c r="N26" s="491" t="n"/>
       <c r="O26" s="491" t="n"/>
       <c r="P26" s="491" t="n"/>
       <c r="Q26" s="491" t="n"/>
-      <c r="R26" s="491" t="n"/>
-      <c r="S26" s="491" t="n"/>
+      <c r="R26" s="492" t="n"/>
+      <c r="S26" s="503" t="n"/>
       <c r="T26" s="491" t="n"/>
       <c r="U26" s="491" t="n"/>
       <c r="V26" s="491" t="n"/>
@@ -7382,8 +7498,8 @@
       <c r="X26" s="491" t="n"/>
       <c r="Y26" s="491" t="n"/>
       <c r="Z26" s="491" t="n"/>
-      <c r="AA26" s="491" t="n"/>
-      <c r="AB26" s="491" t="n"/>
+      <c r="AA26" s="492" t="n"/>
+      <c r="AB26" s="501" t="n"/>
       <c r="AC26" s="491" t="n"/>
       <c r="AD26" s="491" t="n"/>
       <c r="AE26" s="491" t="n"/>
@@ -7391,17 +7507,17 @@
       <c r="AG26" s="491" t="n"/>
       <c r="AH26" s="491" t="n"/>
       <c r="AI26" s="491" t="n"/>
-      <c r="AJ26" s="491" t="n"/>
-      <c r="AK26" s="491" t="n"/>
+      <c r="AJ26" s="492" t="n"/>
+      <c r="AK26" s="496" t="n"/>
       <c r="AL26" s="491" t="n"/>
       <c r="AM26" s="491" t="n"/>
       <c r="AN26" s="491" t="n"/>
       <c r="AO26" s="491" t="n"/>
-      <c r="AP26" s="492" t="n"/>
-      <c r="AQ26" s="500" t="n"/>
+      <c r="AP26" s="491" t="n"/>
+      <c r="AQ26" s="491" t="n"/>
       <c r="AR26" s="491" t="n"/>
-      <c r="AS26" s="491" t="n"/>
-      <c r="AT26" s="491" t="n"/>
+      <c r="AS26" s="492" t="n"/>
+      <c r="AT26" s="496" t="n"/>
       <c r="AU26" s="491" t="n"/>
       <c r="AV26" s="491" t="n"/>
       <c r="AW26" s="491" t="n"/>
@@ -7409,26 +7525,26 @@
       <c r="AY26" s="491" t="n"/>
       <c r="AZ26" s="491" t="n"/>
       <c r="BA26" s="491" t="n"/>
-      <c r="BB26" s="491" t="n"/>
-      <c r="BC26" s="491" t="n"/>
+      <c r="BB26" s="492" t="n"/>
+      <c r="BC26" s="497" t="n"/>
       <c r="BD26" s="491" t="n"/>
       <c r="BE26" s="491" t="n"/>
       <c r="BF26" s="491" t="n"/>
       <c r="BG26" s="491" t="n"/>
       <c r="BH26" s="491" t="n"/>
       <c r="BI26" s="491" t="n"/>
-      <c r="BJ26" s="492" t="n"/>
-      <c r="BK26" s="496" t="n"/>
-      <c r="BL26" s="491" t="n"/>
+      <c r="BJ26" s="491" t="n"/>
+      <c r="BK26" s="492" t="n"/>
+      <c r="BL26" s="497" t="n"/>
       <c r="BM26" s="491" t="n"/>
       <c r="BN26" s="491" t="n"/>
       <c r="BO26" s="491" t="n"/>
       <c r="BP26" s="491" t="n"/>
       <c r="BQ26" s="491" t="n"/>
-      <c r="BR26" s="492" t="n"/>
-      <c r="BS26" s="497" t="n"/>
-      <c r="BT26" s="491" t="n"/>
-      <c r="BU26" s="491" t="n"/>
+      <c r="BR26" s="491" t="n"/>
+      <c r="BS26" s="491" t="n"/>
+      <c r="BT26" s="492" t="n"/>
+      <c r="BU26" s="498" t="n"/>
       <c r="BV26" s="491" t="n"/>
       <c r="BW26" s="491" t="n"/>
       <c r="BX26" s="491" t="n"/>
@@ -7437,30 +7553,31 @@
       <c r="CA26" s="491" t="n"/>
       <c r="CB26" s="491" t="n"/>
       <c r="CC26" s="491" t="n"/>
-      <c r="CD26" s="498" t="n"/>
+      <c r="CD26" s="499" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1" s="264">
-      <c r="A27" s="490" t="n">
-        <v>14</v>
+      <c r="A27" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B27" s="491" t="n"/>
       <c r="C27" s="491" t="n"/>
-      <c r="D27" s="492" t="n"/>
-      <c r="E27" s="500" t="n"/>
+      <c r="D27" s="491" t="n"/>
+      <c r="E27" s="491" t="n"/>
       <c r="F27" s="491" t="n"/>
       <c r="G27" s="491" t="n"/>
       <c r="H27" s="491" t="n"/>
-      <c r="I27" s="491" t="n"/>
-      <c r="J27" s="492" t="n"/>
-      <c r="K27" s="501" t="n"/>
+      <c r="I27" s="492" t="n"/>
+      <c r="J27" s="501" t="n"/>
+      <c r="K27" s="491" t="n"/>
       <c r="L27" s="491" t="n"/>
       <c r="M27" s="491" t="n"/>
       <c r="N27" s="491" t="n"/>
       <c r="O27" s="491" t="n"/>
       <c r="P27" s="491" t="n"/>
       <c r="Q27" s="491" t="n"/>
-      <c r="R27" s="491" t="n"/>
-      <c r="S27" s="491" t="n"/>
+      <c r="R27" s="492" t="n"/>
+      <c r="S27" s="502" t="n"/>
       <c r="T27" s="491" t="n"/>
       <c r="U27" s="491" t="n"/>
       <c r="V27" s="491" t="n"/>
@@ -7468,8 +7585,8 @@
       <c r="X27" s="491" t="n"/>
       <c r="Y27" s="491" t="n"/>
       <c r="Z27" s="491" t="n"/>
-      <c r="AA27" s="491" t="n"/>
-      <c r="AB27" s="491" t="n"/>
+      <c r="AA27" s="492" t="n"/>
+      <c r="AB27" s="501" t="n"/>
       <c r="AC27" s="491" t="n"/>
       <c r="AD27" s="491" t="n"/>
       <c r="AE27" s="491" t="n"/>
@@ -7477,17 +7594,17 @@
       <c r="AG27" s="491" t="n"/>
       <c r="AH27" s="491" t="n"/>
       <c r="AI27" s="491" t="n"/>
-      <c r="AJ27" s="491" t="n"/>
-      <c r="AK27" s="491" t="n"/>
+      <c r="AJ27" s="492" t="n"/>
+      <c r="AK27" s="496" t="n"/>
       <c r="AL27" s="491" t="n"/>
       <c r="AM27" s="491" t="n"/>
       <c r="AN27" s="491" t="n"/>
       <c r="AO27" s="491" t="n"/>
-      <c r="AP27" s="492" t="n"/>
-      <c r="AQ27" s="500" t="n"/>
+      <c r="AP27" s="491" t="n"/>
+      <c r="AQ27" s="491" t="n"/>
       <c r="AR27" s="491" t="n"/>
-      <c r="AS27" s="491" t="n"/>
-      <c r="AT27" s="491" t="n"/>
+      <c r="AS27" s="492" t="n"/>
+      <c r="AT27" s="496" t="n"/>
       <c r="AU27" s="491" t="n"/>
       <c r="AV27" s="491" t="n"/>
       <c r="AW27" s="491" t="n"/>
@@ -7495,26 +7612,26 @@
       <c r="AY27" s="491" t="n"/>
       <c r="AZ27" s="491" t="n"/>
       <c r="BA27" s="491" t="n"/>
-      <c r="BB27" s="491" t="n"/>
-      <c r="BC27" s="491" t="n"/>
+      <c r="BB27" s="492" t="n"/>
+      <c r="BC27" s="497" t="n"/>
       <c r="BD27" s="491" t="n"/>
       <c r="BE27" s="491" t="n"/>
       <c r="BF27" s="491" t="n"/>
       <c r="BG27" s="491" t="n"/>
       <c r="BH27" s="491" t="n"/>
       <c r="BI27" s="491" t="n"/>
-      <c r="BJ27" s="492" t="n"/>
-      <c r="BK27" s="496" t="n"/>
-      <c r="BL27" s="491" t="n"/>
+      <c r="BJ27" s="491" t="n"/>
+      <c r="BK27" s="492" t="n"/>
+      <c r="BL27" s="497" t="n"/>
       <c r="BM27" s="491" t="n"/>
       <c r="BN27" s="491" t="n"/>
       <c r="BO27" s="491" t="n"/>
       <c r="BP27" s="491" t="n"/>
       <c r="BQ27" s="491" t="n"/>
-      <c r="BR27" s="492" t="n"/>
-      <c r="BS27" s="497" t="n"/>
-      <c r="BT27" s="491" t="n"/>
-      <c r="BU27" s="491" t="n"/>
+      <c r="BR27" s="491" t="n"/>
+      <c r="BS27" s="491" t="n"/>
+      <c r="BT27" s="492" t="n"/>
+      <c r="BU27" s="498" t="n"/>
       <c r="BV27" s="491" t="n"/>
       <c r="BW27" s="491" t="n"/>
       <c r="BX27" s="491" t="n"/>
@@ -7523,30 +7640,31 @@
       <c r="CA27" s="491" t="n"/>
       <c r="CB27" s="491" t="n"/>
       <c r="CC27" s="491" t="n"/>
-      <c r="CD27" s="498" t="n"/>
+      <c r="CD27" s="499" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1" s="264">
-      <c r="A28" s="490" t="n">
-        <v>15</v>
+      <c r="A28" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B28" s="491" t="n"/>
       <c r="C28" s="491" t="n"/>
-      <c r="D28" s="492" t="n"/>
-      <c r="E28" s="500" t="n"/>
+      <c r="D28" s="491" t="n"/>
+      <c r="E28" s="491" t="n"/>
       <c r="F28" s="491" t="n"/>
       <c r="G28" s="491" t="n"/>
       <c r="H28" s="491" t="n"/>
-      <c r="I28" s="491" t="n"/>
-      <c r="J28" s="492" t="n"/>
-      <c r="K28" s="502" t="n"/>
+      <c r="I28" s="492" t="n"/>
+      <c r="J28" s="501" t="n"/>
+      <c r="K28" s="491" t="n"/>
       <c r="L28" s="491" t="n"/>
       <c r="M28" s="491" t="n"/>
       <c r="N28" s="491" t="n"/>
       <c r="O28" s="491" t="n"/>
       <c r="P28" s="491" t="n"/>
       <c r="Q28" s="491" t="n"/>
-      <c r="R28" s="491" t="n"/>
-      <c r="S28" s="491" t="n"/>
+      <c r="R28" s="492" t="n"/>
+      <c r="S28" s="503" t="n"/>
       <c r="T28" s="491" t="n"/>
       <c r="U28" s="491" t="n"/>
       <c r="V28" s="491" t="n"/>
@@ -7554,8 +7672,8 @@
       <c r="X28" s="491" t="n"/>
       <c r="Y28" s="491" t="n"/>
       <c r="Z28" s="491" t="n"/>
-      <c r="AA28" s="491" t="n"/>
-      <c r="AB28" s="491" t="n"/>
+      <c r="AA28" s="492" t="n"/>
+      <c r="AB28" s="501" t="n"/>
       <c r="AC28" s="491" t="n"/>
       <c r="AD28" s="491" t="n"/>
       <c r="AE28" s="491" t="n"/>
@@ -7563,17 +7681,17 @@
       <c r="AG28" s="491" t="n"/>
       <c r="AH28" s="491" t="n"/>
       <c r="AI28" s="491" t="n"/>
-      <c r="AJ28" s="491" t="n"/>
-      <c r="AK28" s="491" t="n"/>
+      <c r="AJ28" s="492" t="n"/>
+      <c r="AK28" s="496" t="n"/>
       <c r="AL28" s="491" t="n"/>
       <c r="AM28" s="491" t="n"/>
       <c r="AN28" s="491" t="n"/>
       <c r="AO28" s="491" t="n"/>
-      <c r="AP28" s="492" t="n"/>
-      <c r="AQ28" s="500" t="n"/>
+      <c r="AP28" s="491" t="n"/>
+      <c r="AQ28" s="491" t="n"/>
       <c r="AR28" s="491" t="n"/>
-      <c r="AS28" s="491" t="n"/>
-      <c r="AT28" s="491" t="n"/>
+      <c r="AS28" s="492" t="n"/>
+      <c r="AT28" s="496" t="n"/>
       <c r="AU28" s="491" t="n"/>
       <c r="AV28" s="491" t="n"/>
       <c r="AW28" s="491" t="n"/>
@@ -7581,26 +7699,26 @@
       <c r="AY28" s="491" t="n"/>
       <c r="AZ28" s="491" t="n"/>
       <c r="BA28" s="491" t="n"/>
-      <c r="BB28" s="491" t="n"/>
-      <c r="BC28" s="491" t="n"/>
+      <c r="BB28" s="492" t="n"/>
+      <c r="BC28" s="497" t="n"/>
       <c r="BD28" s="491" t="n"/>
       <c r="BE28" s="491" t="n"/>
       <c r="BF28" s="491" t="n"/>
       <c r="BG28" s="491" t="n"/>
       <c r="BH28" s="491" t="n"/>
       <c r="BI28" s="491" t="n"/>
-      <c r="BJ28" s="492" t="n"/>
-      <c r="BK28" s="496" t="n"/>
-      <c r="BL28" s="491" t="n"/>
+      <c r="BJ28" s="491" t="n"/>
+      <c r="BK28" s="492" t="n"/>
+      <c r="BL28" s="497" t="n"/>
       <c r="BM28" s="491" t="n"/>
       <c r="BN28" s="491" t="n"/>
       <c r="BO28" s="491" t="n"/>
       <c r="BP28" s="491" t="n"/>
       <c r="BQ28" s="491" t="n"/>
-      <c r="BR28" s="492" t="n"/>
-      <c r="BS28" s="497" t="n"/>
-      <c r="BT28" s="491" t="n"/>
-      <c r="BU28" s="491" t="n"/>
+      <c r="BR28" s="491" t="n"/>
+      <c r="BS28" s="491" t="n"/>
+      <c r="BT28" s="492" t="n"/>
+      <c r="BU28" s="498" t="n"/>
       <c r="BV28" s="491" t="n"/>
       <c r="BW28" s="491" t="n"/>
       <c r="BX28" s="491" t="n"/>
@@ -7609,30 +7727,31 @@
       <c r="CA28" s="491" t="n"/>
       <c r="CB28" s="491" t="n"/>
       <c r="CC28" s="491" t="n"/>
-      <c r="CD28" s="498" t="n"/>
+      <c r="CD28" s="499" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1" s="264">
-      <c r="A29" s="490" t="n">
-        <v>16</v>
+      <c r="A29" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B29" s="491" t="n"/>
       <c r="C29" s="491" t="n"/>
-      <c r="D29" s="492" t="n"/>
-      <c r="E29" s="500" t="n"/>
+      <c r="D29" s="491" t="n"/>
+      <c r="E29" s="491" t="n"/>
       <c r="F29" s="491" t="n"/>
       <c r="G29" s="491" t="n"/>
       <c r="H29" s="491" t="n"/>
-      <c r="I29" s="491" t="n"/>
-      <c r="J29" s="492" t="n"/>
-      <c r="K29" s="501" t="n"/>
+      <c r="I29" s="492" t="n"/>
+      <c r="J29" s="501" t="n"/>
+      <c r="K29" s="491" t="n"/>
       <c r="L29" s="491" t="n"/>
       <c r="M29" s="491" t="n"/>
       <c r="N29" s="491" t="n"/>
       <c r="O29" s="491" t="n"/>
       <c r="P29" s="491" t="n"/>
       <c r="Q29" s="491" t="n"/>
-      <c r="R29" s="491" t="n"/>
-      <c r="S29" s="491" t="n"/>
+      <c r="R29" s="492" t="n"/>
+      <c r="S29" s="502" t="n"/>
       <c r="T29" s="491" t="n"/>
       <c r="U29" s="491" t="n"/>
       <c r="V29" s="491" t="n"/>
@@ -7640,8 +7759,8 @@
       <c r="X29" s="491" t="n"/>
       <c r="Y29" s="491" t="n"/>
       <c r="Z29" s="491" t="n"/>
-      <c r="AA29" s="491" t="n"/>
-      <c r="AB29" s="491" t="n"/>
+      <c r="AA29" s="492" t="n"/>
+      <c r="AB29" s="501" t="n"/>
       <c r="AC29" s="491" t="n"/>
       <c r="AD29" s="491" t="n"/>
       <c r="AE29" s="491" t="n"/>
@@ -7649,17 +7768,17 @@
       <c r="AG29" s="491" t="n"/>
       <c r="AH29" s="491" t="n"/>
       <c r="AI29" s="491" t="n"/>
-      <c r="AJ29" s="491" t="n"/>
-      <c r="AK29" s="491" t="n"/>
+      <c r="AJ29" s="492" t="n"/>
+      <c r="AK29" s="496" t="n"/>
       <c r="AL29" s="491" t="n"/>
       <c r="AM29" s="491" t="n"/>
       <c r="AN29" s="491" t="n"/>
       <c r="AO29" s="491" t="n"/>
-      <c r="AP29" s="492" t="n"/>
-      <c r="AQ29" s="500" t="n"/>
+      <c r="AP29" s="491" t="n"/>
+      <c r="AQ29" s="491" t="n"/>
       <c r="AR29" s="491" t="n"/>
-      <c r="AS29" s="491" t="n"/>
-      <c r="AT29" s="491" t="n"/>
+      <c r="AS29" s="492" t="n"/>
+      <c r="AT29" s="496" t="n"/>
       <c r="AU29" s="491" t="n"/>
       <c r="AV29" s="491" t="n"/>
       <c r="AW29" s="491" t="n"/>
@@ -7667,26 +7786,26 @@
       <c r="AY29" s="491" t="n"/>
       <c r="AZ29" s="491" t="n"/>
       <c r="BA29" s="491" t="n"/>
-      <c r="BB29" s="491" t="n"/>
-      <c r="BC29" s="491" t="n"/>
+      <c r="BB29" s="492" t="n"/>
+      <c r="BC29" s="497" t="n"/>
       <c r="BD29" s="491" t="n"/>
       <c r="BE29" s="491" t="n"/>
       <c r="BF29" s="491" t="n"/>
       <c r="BG29" s="491" t="n"/>
       <c r="BH29" s="491" t="n"/>
       <c r="BI29" s="491" t="n"/>
-      <c r="BJ29" s="492" t="n"/>
-      <c r="BK29" s="496" t="n"/>
-      <c r="BL29" s="491" t="n"/>
+      <c r="BJ29" s="491" t="n"/>
+      <c r="BK29" s="492" t="n"/>
+      <c r="BL29" s="497" t="n"/>
       <c r="BM29" s="491" t="n"/>
       <c r="BN29" s="491" t="n"/>
       <c r="BO29" s="491" t="n"/>
       <c r="BP29" s="491" t="n"/>
       <c r="BQ29" s="491" t="n"/>
-      <c r="BR29" s="492" t="n"/>
-      <c r="BS29" s="497" t="n"/>
-      <c r="BT29" s="491" t="n"/>
-      <c r="BU29" s="491" t="n"/>
+      <c r="BR29" s="491" t="n"/>
+      <c r="BS29" s="491" t="n"/>
+      <c r="BT29" s="492" t="n"/>
+      <c r="BU29" s="498" t="n"/>
       <c r="BV29" s="491" t="n"/>
       <c r="BW29" s="491" t="n"/>
       <c r="BX29" s="491" t="n"/>
@@ -7695,30 +7814,31 @@
       <c r="CA29" s="491" t="n"/>
       <c r="CB29" s="491" t="n"/>
       <c r="CC29" s="491" t="n"/>
-      <c r="CD29" s="498" t="n"/>
+      <c r="CD29" s="499" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1" s="264">
-      <c r="A30" s="490" t="n">
-        <v>17</v>
+      <c r="A30" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B30" s="491" t="n"/>
       <c r="C30" s="491" t="n"/>
-      <c r="D30" s="492" t="n"/>
-      <c r="E30" s="500" t="n"/>
+      <c r="D30" s="491" t="n"/>
+      <c r="E30" s="491" t="n"/>
       <c r="F30" s="491" t="n"/>
       <c r="G30" s="491" t="n"/>
       <c r="H30" s="491" t="n"/>
-      <c r="I30" s="491" t="n"/>
-      <c r="J30" s="492" t="n"/>
-      <c r="K30" s="502" t="n"/>
+      <c r="I30" s="492" t="n"/>
+      <c r="J30" s="501" t="n"/>
+      <c r="K30" s="491" t="n"/>
       <c r="L30" s="491" t="n"/>
       <c r="M30" s="491" t="n"/>
       <c r="N30" s="491" t="n"/>
       <c r="O30" s="491" t="n"/>
       <c r="P30" s="491" t="n"/>
       <c r="Q30" s="491" t="n"/>
-      <c r="R30" s="491" t="n"/>
-      <c r="S30" s="491" t="n"/>
+      <c r="R30" s="492" t="n"/>
+      <c r="S30" s="503" t="n"/>
       <c r="T30" s="491" t="n"/>
       <c r="U30" s="491" t="n"/>
       <c r="V30" s="491" t="n"/>
@@ -7726,8 +7846,8 @@
       <c r="X30" s="491" t="n"/>
       <c r="Y30" s="491" t="n"/>
       <c r="Z30" s="491" t="n"/>
-      <c r="AA30" s="491" t="n"/>
-      <c r="AB30" s="491" t="n"/>
+      <c r="AA30" s="492" t="n"/>
+      <c r="AB30" s="501" t="n"/>
       <c r="AC30" s="491" t="n"/>
       <c r="AD30" s="491" t="n"/>
       <c r="AE30" s="491" t="n"/>
@@ -7735,17 +7855,17 @@
       <c r="AG30" s="491" t="n"/>
       <c r="AH30" s="491" t="n"/>
       <c r="AI30" s="491" t="n"/>
-      <c r="AJ30" s="491" t="n"/>
-      <c r="AK30" s="491" t="n"/>
+      <c r="AJ30" s="492" t="n"/>
+      <c r="AK30" s="496" t="n"/>
       <c r="AL30" s="491" t="n"/>
       <c r="AM30" s="491" t="n"/>
       <c r="AN30" s="491" t="n"/>
       <c r="AO30" s="491" t="n"/>
-      <c r="AP30" s="492" t="n"/>
-      <c r="AQ30" s="500" t="n"/>
+      <c r="AP30" s="491" t="n"/>
+      <c r="AQ30" s="491" t="n"/>
       <c r="AR30" s="491" t="n"/>
-      <c r="AS30" s="491" t="n"/>
-      <c r="AT30" s="491" t="n"/>
+      <c r="AS30" s="492" t="n"/>
+      <c r="AT30" s="496" t="n"/>
       <c r="AU30" s="491" t="n"/>
       <c r="AV30" s="491" t="n"/>
       <c r="AW30" s="491" t="n"/>
@@ -7753,26 +7873,26 @@
       <c r="AY30" s="491" t="n"/>
       <c r="AZ30" s="491" t="n"/>
       <c r="BA30" s="491" t="n"/>
-      <c r="BB30" s="491" t="n"/>
-      <c r="BC30" s="491" t="n"/>
+      <c r="BB30" s="492" t="n"/>
+      <c r="BC30" s="497" t="n"/>
       <c r="BD30" s="491" t="n"/>
       <c r="BE30" s="491" t="n"/>
       <c r="BF30" s="491" t="n"/>
       <c r="BG30" s="491" t="n"/>
       <c r="BH30" s="491" t="n"/>
       <c r="BI30" s="491" t="n"/>
-      <c r="BJ30" s="492" t="n"/>
-      <c r="BK30" s="496" t="n"/>
-      <c r="BL30" s="491" t="n"/>
+      <c r="BJ30" s="491" t="n"/>
+      <c r="BK30" s="492" t="n"/>
+      <c r="BL30" s="497" t="n"/>
       <c r="BM30" s="491" t="n"/>
       <c r="BN30" s="491" t="n"/>
       <c r="BO30" s="491" t="n"/>
       <c r="BP30" s="491" t="n"/>
       <c r="BQ30" s="491" t="n"/>
-      <c r="BR30" s="492" t="n"/>
-      <c r="BS30" s="497" t="n"/>
-      <c r="BT30" s="491" t="n"/>
-      <c r="BU30" s="491" t="n"/>
+      <c r="BR30" s="491" t="n"/>
+      <c r="BS30" s="491" t="n"/>
+      <c r="BT30" s="492" t="n"/>
+      <c r="BU30" s="498" t="n"/>
       <c r="BV30" s="491" t="n"/>
       <c r="BW30" s="491" t="n"/>
       <c r="BX30" s="491" t="n"/>
@@ -7781,30 +7901,31 @@
       <c r="CA30" s="491" t="n"/>
       <c r="CB30" s="491" t="n"/>
       <c r="CC30" s="491" t="n"/>
-      <c r="CD30" s="498" t="n"/>
+      <c r="CD30" s="499" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1" s="264">
-      <c r="A31" s="503" t="n">
-        <v>18</v>
+      <c r="A31" s="504">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B31" s="481" t="n"/>
       <c r="C31" s="481" t="n"/>
-      <c r="D31" s="482" t="n"/>
-      <c r="E31" s="504" t="n"/>
+      <c r="D31" s="481" t="n"/>
+      <c r="E31" s="481" t="n"/>
       <c r="F31" s="481" t="n"/>
       <c r="G31" s="481" t="n"/>
       <c r="H31" s="481" t="n"/>
-      <c r="I31" s="481" t="n"/>
-      <c r="J31" s="482" t="n"/>
-      <c r="K31" s="505" t="n"/>
+      <c r="I31" s="482" t="n"/>
+      <c r="J31" s="505" t="n"/>
+      <c r="K31" s="481" t="n"/>
       <c r="L31" s="481" t="n"/>
       <c r="M31" s="481" t="n"/>
       <c r="N31" s="481" t="n"/>
       <c r="O31" s="481" t="n"/>
       <c r="P31" s="481" t="n"/>
       <c r="Q31" s="481" t="n"/>
-      <c r="R31" s="481" t="n"/>
-      <c r="S31" s="481" t="n"/>
+      <c r="R31" s="482" t="n"/>
+      <c r="S31" s="506" t="n"/>
       <c r="T31" s="481" t="n"/>
       <c r="U31" s="481" t="n"/>
       <c r="V31" s="481" t="n"/>
@@ -7812,8 +7933,8 @@
       <c r="X31" s="481" t="n"/>
       <c r="Y31" s="481" t="n"/>
       <c r="Z31" s="481" t="n"/>
-      <c r="AA31" s="481" t="n"/>
-      <c r="AB31" s="481" t="n"/>
+      <c r="AA31" s="482" t="n"/>
+      <c r="AB31" s="505" t="n"/>
       <c r="AC31" s="481" t="n"/>
       <c r="AD31" s="481" t="n"/>
       <c r="AE31" s="481" t="n"/>
@@ -7821,17 +7942,17 @@
       <c r="AG31" s="481" t="n"/>
       <c r="AH31" s="481" t="n"/>
       <c r="AI31" s="481" t="n"/>
-      <c r="AJ31" s="481" t="n"/>
-      <c r="AK31" s="481" t="n"/>
+      <c r="AJ31" s="482" t="n"/>
+      <c r="AK31" s="507" t="n"/>
       <c r="AL31" s="481" t="n"/>
       <c r="AM31" s="481" t="n"/>
       <c r="AN31" s="481" t="n"/>
       <c r="AO31" s="481" t="n"/>
-      <c r="AP31" s="482" t="n"/>
-      <c r="AQ31" s="504" t="n"/>
+      <c r="AP31" s="481" t="n"/>
+      <c r="AQ31" s="481" t="n"/>
       <c r="AR31" s="481" t="n"/>
-      <c r="AS31" s="481" t="n"/>
-      <c r="AT31" s="481" t="n"/>
+      <c r="AS31" s="482" t="n"/>
+      <c r="AT31" s="507" t="n"/>
       <c r="AU31" s="481" t="n"/>
       <c r="AV31" s="481" t="n"/>
       <c r="AW31" s="481" t="n"/>
@@ -7839,26 +7960,26 @@
       <c r="AY31" s="481" t="n"/>
       <c r="AZ31" s="481" t="n"/>
       <c r="BA31" s="481" t="n"/>
-      <c r="BB31" s="481" t="n"/>
-      <c r="BC31" s="481" t="n"/>
+      <c r="BB31" s="482" t="n"/>
+      <c r="BC31" s="508" t="n"/>
       <c r="BD31" s="481" t="n"/>
       <c r="BE31" s="481" t="n"/>
       <c r="BF31" s="481" t="n"/>
       <c r="BG31" s="481" t="n"/>
       <c r="BH31" s="481" t="n"/>
       <c r="BI31" s="481" t="n"/>
-      <c r="BJ31" s="482" t="n"/>
-      <c r="BK31" s="506" t="n"/>
-      <c r="BL31" s="481" t="n"/>
+      <c r="BJ31" s="481" t="n"/>
+      <c r="BK31" s="482" t="n"/>
+      <c r="BL31" s="508" t="n"/>
       <c r="BM31" s="481" t="n"/>
       <c r="BN31" s="481" t="n"/>
       <c r="BO31" s="481" t="n"/>
       <c r="BP31" s="481" t="n"/>
       <c r="BQ31" s="481" t="n"/>
-      <c r="BR31" s="482" t="n"/>
-      <c r="BS31" s="507" t="n"/>
-      <c r="BT31" s="481" t="n"/>
-      <c r="BU31" s="481" t="n"/>
+      <c r="BR31" s="481" t="n"/>
+      <c r="BS31" s="481" t="n"/>
+      <c r="BT31" s="482" t="n"/>
+      <c r="BU31" s="509" t="n"/>
       <c r="BV31" s="481" t="n"/>
       <c r="BW31" s="481" t="n"/>
       <c r="BX31" s="481" t="n"/>
@@ -8042,7 +8163,7 @@
       <c r="CD33" s="472" t="n"/>
     </row>
     <row r="34" ht="17" customHeight="1" s="264">
-      <c r="A34" s="508" t="inlineStr">
+      <c r="A34" s="510" t="inlineStr">
         <is>
           <t>Team Lead</t>
         </is>
@@ -8073,7 +8194,7 @@
       <c r="Y34" s="471" t="n"/>
       <c r="Z34" s="471" t="n"/>
       <c r="AA34" s="472" t="n"/>
-      <c r="AB34" s="508" t="inlineStr">
+      <c r="AB34" s="510" t="inlineStr">
         <is>
           <t>Engineering Mgr</t>
         </is>
@@ -8104,7 +8225,7 @@
       <c r="AZ34" s="471" t="n"/>
       <c r="BA34" s="471" t="n"/>
       <c r="BB34" s="472" t="n"/>
-      <c r="BC34" s="508" t="inlineStr">
+      <c r="BC34" s="510" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
@@ -8138,111 +8259,111 @@
       <c r="CD34" s="472" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1" s="264">
-      <c r="A35" s="509" t="inlineStr">
+      <c r="A35" s="511" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="B35" s="510" t="n"/>
-      <c r="C35" s="510" t="n"/>
-      <c r="D35" s="510" t="n"/>
-      <c r="E35" s="510" t="n"/>
-      <c r="F35" s="510" t="n"/>
-      <c r="G35" s="510" t="n"/>
-      <c r="H35" s="510" t="n"/>
-      <c r="I35" s="510" t="n"/>
-      <c r="J35" s="510" t="n"/>
-      <c r="K35" s="510" t="n"/>
-      <c r="L35" s="510" t="n"/>
-      <c r="M35" s="510" t="n"/>
-      <c r="N35" s="510" t="n"/>
-      <c r="O35" s="510" t="n"/>
-      <c r="P35" s="510" t="n"/>
-      <c r="Q35" s="510" t="n"/>
-      <c r="R35" s="510" t="n"/>
-      <c r="S35" s="510" t="n"/>
-      <c r="T35" s="510" t="n"/>
-      <c r="U35" s="510" t="n"/>
-      <c r="V35" s="510" t="n"/>
-      <c r="W35" s="510" t="n"/>
-      <c r="X35" s="510" t="n"/>
-      <c r="Y35" s="510" t="n"/>
-      <c r="Z35" s="510" t="n"/>
-      <c r="AA35" s="511" t="n"/>
-      <c r="AB35" s="509" t="inlineStr">
+      <c r="B35" s="512" t="n"/>
+      <c r="C35" s="512" t="n"/>
+      <c r="D35" s="512" t="n"/>
+      <c r="E35" s="512" t="n"/>
+      <c r="F35" s="512" t="n"/>
+      <c r="G35" s="512" t="n"/>
+      <c r="H35" s="512" t="n"/>
+      <c r="I35" s="512" t="n"/>
+      <c r="J35" s="512" t="n"/>
+      <c r="K35" s="512" t="n"/>
+      <c r="L35" s="512" t="n"/>
+      <c r="M35" s="512" t="n"/>
+      <c r="N35" s="512" t="n"/>
+      <c r="O35" s="512" t="n"/>
+      <c r="P35" s="512" t="n"/>
+      <c r="Q35" s="512" t="n"/>
+      <c r="R35" s="512" t="n"/>
+      <c r="S35" s="512" t="n"/>
+      <c r="T35" s="512" t="n"/>
+      <c r="U35" s="512" t="n"/>
+      <c r="V35" s="512" t="n"/>
+      <c r="W35" s="512" t="n"/>
+      <c r="X35" s="512" t="n"/>
+      <c r="Y35" s="512" t="n"/>
+      <c r="Z35" s="512" t="n"/>
+      <c r="AA35" s="513" t="n"/>
+      <c r="AB35" s="511" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="AC35" s="510" t="n"/>
-      <c r="AD35" s="510" t="n"/>
-      <c r="AE35" s="510" t="n"/>
-      <c r="AF35" s="510" t="n"/>
-      <c r="AG35" s="510" t="n"/>
-      <c r="AH35" s="510" t="n"/>
-      <c r="AI35" s="510" t="n"/>
-      <c r="AJ35" s="510" t="n"/>
-      <c r="AK35" s="510" t="n"/>
-      <c r="AL35" s="510" t="n"/>
-      <c r="AM35" s="510" t="n"/>
-      <c r="AN35" s="510" t="n"/>
-      <c r="AO35" s="510" t="n"/>
-      <c r="AP35" s="510" t="n"/>
-      <c r="AQ35" s="510" t="n"/>
-      <c r="AR35" s="510" t="n"/>
-      <c r="AS35" s="510" t="n"/>
-      <c r="AT35" s="510" t="n"/>
-      <c r="AU35" s="510" t="n"/>
-      <c r="AV35" s="510" t="n"/>
-      <c r="AW35" s="510" t="n"/>
-      <c r="AX35" s="510" t="n"/>
-      <c r="AY35" s="510" t="n"/>
-      <c r="AZ35" s="510" t="n"/>
-      <c r="BA35" s="510" t="n"/>
-      <c r="BB35" s="511" t="n"/>
-      <c r="BC35" s="509" t="inlineStr">
+      <c r="AC35" s="512" t="n"/>
+      <c r="AD35" s="512" t="n"/>
+      <c r="AE35" s="512" t="n"/>
+      <c r="AF35" s="512" t="n"/>
+      <c r="AG35" s="512" t="n"/>
+      <c r="AH35" s="512" t="n"/>
+      <c r="AI35" s="512" t="n"/>
+      <c r="AJ35" s="512" t="n"/>
+      <c r="AK35" s="512" t="n"/>
+      <c r="AL35" s="512" t="n"/>
+      <c r="AM35" s="512" t="n"/>
+      <c r="AN35" s="512" t="n"/>
+      <c r="AO35" s="512" t="n"/>
+      <c r="AP35" s="512" t="n"/>
+      <c r="AQ35" s="512" t="n"/>
+      <c r="AR35" s="512" t="n"/>
+      <c r="AS35" s="512" t="n"/>
+      <c r="AT35" s="512" t="n"/>
+      <c r="AU35" s="512" t="n"/>
+      <c r="AV35" s="512" t="n"/>
+      <c r="AW35" s="512" t="n"/>
+      <c r="AX35" s="512" t="n"/>
+      <c r="AY35" s="512" t="n"/>
+      <c r="AZ35" s="512" t="n"/>
+      <c r="BA35" s="512" t="n"/>
+      <c r="BB35" s="513" t="n"/>
+      <c r="BC35" s="511" t="inlineStr">
         <is>
           <t>Name  /  Signature  /  Date</t>
         </is>
       </c>
-      <c r="BD35" s="510" t="n"/>
-      <c r="BE35" s="510" t="n"/>
-      <c r="BF35" s="510" t="n"/>
-      <c r="BG35" s="510" t="n"/>
-      <c r="BH35" s="510" t="n"/>
-      <c r="BI35" s="510" t="n"/>
-      <c r="BJ35" s="510" t="n"/>
-      <c r="BK35" s="510" t="n"/>
-      <c r="BL35" s="510" t="n"/>
-      <c r="BM35" s="510" t="n"/>
-      <c r="BN35" s="510" t="n"/>
-      <c r="BO35" s="510" t="n"/>
-      <c r="BP35" s="510" t="n"/>
-      <c r="BQ35" s="510" t="n"/>
-      <c r="BR35" s="510" t="n"/>
-      <c r="BS35" s="510" t="n"/>
-      <c r="BT35" s="510" t="n"/>
-      <c r="BU35" s="510" t="n"/>
-      <c r="BV35" s="510" t="n"/>
-      <c r="BW35" s="510" t="n"/>
-      <c r="BX35" s="510" t="n"/>
-      <c r="BY35" s="510" t="n"/>
-      <c r="BZ35" s="510" t="n"/>
-      <c r="CA35" s="510" t="n"/>
-      <c r="CB35" s="510" t="n"/>
-      <c r="CC35" s="510" t="n"/>
-      <c r="CD35" s="511" t="n"/>
+      <c r="BD35" s="512" t="n"/>
+      <c r="BE35" s="512" t="n"/>
+      <c r="BF35" s="512" t="n"/>
+      <c r="BG35" s="512" t="n"/>
+      <c r="BH35" s="512" t="n"/>
+      <c r="BI35" s="512" t="n"/>
+      <c r="BJ35" s="512" t="n"/>
+      <c r="BK35" s="512" t="n"/>
+      <c r="BL35" s="512" t="n"/>
+      <c r="BM35" s="512" t="n"/>
+      <c r="BN35" s="512" t="n"/>
+      <c r="BO35" s="512" t="n"/>
+      <c r="BP35" s="512" t="n"/>
+      <c r="BQ35" s="512" t="n"/>
+      <c r="BR35" s="512" t="n"/>
+      <c r="BS35" s="512" t="n"/>
+      <c r="BT35" s="512" t="n"/>
+      <c r="BU35" s="512" t="n"/>
+      <c r="BV35" s="512" t="n"/>
+      <c r="BW35" s="512" t="n"/>
+      <c r="BX35" s="512" t="n"/>
+      <c r="BY35" s="512" t="n"/>
+      <c r="BZ35" s="512" t="n"/>
+      <c r="CA35" s="512" t="n"/>
+      <c r="CB35" s="512" t="n"/>
+      <c r="CC35" s="512" t="n"/>
+      <c r="CD35" s="513" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1" s="264">
-      <c r="A36" s="512" t="n"/>
-      <c r="AA36" s="513" t="n"/>
-      <c r="AB36" s="512" t="n"/>
-      <c r="BB36" s="513" t="n"/>
-      <c r="BC36" s="512" t="n"/>
-      <c r="CD36" s="513" t="n"/>
+      <c r="A36" s="514" t="n"/>
+      <c r="AA36" s="515" t="n"/>
+      <c r="AB36" s="514" t="n"/>
+      <c r="BB36" s="515" t="n"/>
+      <c r="BC36" s="514" t="n"/>
+      <c r="CD36" s="515" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1" s="264">
-      <c r="A37" s="514" t="n"/>
+      <c r="A37" s="516" t="n"/>
       <c r="B37" s="481" t="n"/>
       <c r="C37" s="481" t="n"/>
       <c r="D37" s="481" t="n"/>
@@ -8269,7 +8390,7 @@
       <c r="Y37" s="481" t="n"/>
       <c r="Z37" s="481" t="n"/>
       <c r="AA37" s="486" t="n"/>
-      <c r="AB37" s="514" t="n"/>
+      <c r="AB37" s="516" t="n"/>
       <c r="AC37" s="481" t="n"/>
       <c r="AD37" s="481" t="n"/>
       <c r="AE37" s="481" t="n"/>
@@ -8296,7 +8417,7 @@
       <c r="AZ37" s="481" t="n"/>
       <c r="BA37" s="481" t="n"/>
       <c r="BB37" s="486" t="n"/>
-      <c r="BC37" s="514" t="n"/>
+      <c r="BC37" s="516" t="n"/>
       <c r="BD37" s="481" t="n"/>
       <c r="BE37" s="481" t="n"/>
       <c r="BF37" s="481" t="n"/>
@@ -8410,9 +8531,9 @@
       <c r="CD38" s="26" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1" s="264">
-      <c r="A39" s="515" t="inlineStr">
+      <c r="A39" s="517" t="inlineStr">
         <is>
-          <t>NOTICE — S=Severity O=Occurrence D=Detection AP=Action Priority (H/M/L). Ref: SOP-301. Retain: 10 years.</t>
+          <t>NOTICE — Living document. Update when process changes or new failure modes identified. S=Severity O=Occurrence D=Detection. Ref: SOP-301. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B39" s="471" t="n"/>
@@ -8498,161 +8619,219 @@
       <c r="CD39" s="472" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="150">
+  <mergeCells count="207">
     <mergeCell ref="A9:N9"/>
-    <mergeCell ref="BS30:CD30"/>
-    <mergeCell ref="E19:J19"/>
-    <mergeCell ref="E28:J28"/>
+    <mergeCell ref="J30:R30"/>
+    <mergeCell ref="BU15:CD15"/>
     <mergeCell ref="A7:CD7"/>
+    <mergeCell ref="BU24:CD24"/>
     <mergeCell ref="BD9:CD9"/>
-    <mergeCell ref="K13:AP13"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="BS29:CD29"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="E30:J30"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="K15:AP15"/>
-    <mergeCell ref="BS31:CD31"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="AB31:AJ31"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="AB21:AJ21"/>
+    <mergeCell ref="BU26:CD26"/>
+    <mergeCell ref="S19:AA19"/>
+    <mergeCell ref="AK16:AS16"/>
+    <mergeCell ref="BU16:CD16"/>
     <mergeCell ref="A33:CD33"/>
-    <mergeCell ref="BS15:CD15"/>
-    <mergeCell ref="BS21:CD21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="AQ16:BJ16"/>
-    <mergeCell ref="K21:AP21"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="BK28:BR28"/>
-    <mergeCell ref="AQ18:BJ18"/>
-    <mergeCell ref="BS16:CD16"/>
-    <mergeCell ref="AQ17:BJ17"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="BK14:BR14"/>
-    <mergeCell ref="BK29:BR29"/>
-    <mergeCell ref="BK23:BR23"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="K27:AP27"/>
-    <mergeCell ref="E24:J24"/>
-    <mergeCell ref="AQ19:BJ19"/>
+    <mergeCell ref="J31:R31"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="AB23:AJ23"/>
+    <mergeCell ref="AT31:BB31"/>
+    <mergeCell ref="BC17:BK17"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="AB13:AJ13"/>
+    <mergeCell ref="J21:R21"/>
+    <mergeCell ref="S30:AA30"/>
+    <mergeCell ref="AT21:BB21"/>
+    <mergeCell ref="BL21:BT21"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="S20:AA20"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="BU27:CD27"/>
+    <mergeCell ref="BC19:BK19"/>
+    <mergeCell ref="AT30:BB30"/>
+    <mergeCell ref="BC28:BK28"/>
+    <mergeCell ref="J23:R23"/>
+    <mergeCell ref="AB18:AJ18"/>
+    <mergeCell ref="BU17:CD17"/>
+    <mergeCell ref="BL23:BT23"/>
+    <mergeCell ref="S22:AA22"/>
+    <mergeCell ref="AT13:BB13"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="AT16:BB16"/>
+    <mergeCell ref="BU19:CD19"/>
     <mergeCell ref="A11:CD11"/>
-    <mergeCell ref="K17:AP17"/>
+    <mergeCell ref="BU28:CD28"/>
+    <mergeCell ref="AT27:BB27"/>
+    <mergeCell ref="AK13:AS13"/>
     <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="K19:AP19"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="K28:AP28"/>
+    <mergeCell ref="AT18:BB18"/>
+    <mergeCell ref="BU30:CD30"/>
+    <mergeCell ref="AK15:AS15"/>
+    <mergeCell ref="S23:AA23"/>
+    <mergeCell ref="AK24:AS24"/>
     <mergeCell ref="AB35:BB37"/>
-    <mergeCell ref="BS20:CD20"/>
-    <mergeCell ref="BK21:BR21"/>
+    <mergeCell ref="J27:R27"/>
+    <mergeCell ref="S13:AA13"/>
     <mergeCell ref="Q6:BJ6"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="K25:AP25"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="K30:AP30"/>
-    <mergeCell ref="BK27:BR27"/>
-    <mergeCell ref="BS22:CD22"/>
-    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="AB22:AJ22"/>
+    <mergeCell ref="BL27:BT27"/>
+    <mergeCell ref="AK21:AS21"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="J20:R20"/>
+    <mergeCell ref="AK26:AS26"/>
+    <mergeCell ref="BL20:BT20"/>
+    <mergeCell ref="S15:AA15"/>
+    <mergeCell ref="S24:AA24"/>
+    <mergeCell ref="BC24:BK24"/>
     <mergeCell ref="BS6:CD6"/>
-    <mergeCell ref="AQ21:BJ21"/>
+    <mergeCell ref="J22:R22"/>
+    <mergeCell ref="BL22:BT22"/>
     <mergeCell ref="A8:CD8"/>
     <mergeCell ref="AP10:BC10"/>
-    <mergeCell ref="E22:J22"/>
     <mergeCell ref="BK3:BR3"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="BS13:CD13"/>
+    <mergeCell ref="BU18:CD18"/>
+    <mergeCell ref="BC26:BK26"/>
+    <mergeCell ref="BL14:BT14"/>
+    <mergeCell ref="AB15:AJ15"/>
     <mergeCell ref="BK5:BR5"/>
     <mergeCell ref="A34:AA34"/>
     <mergeCell ref="A35:AA37"/>
+    <mergeCell ref="AB24:AJ24"/>
     <mergeCell ref="A39:CD39"/>
-    <mergeCell ref="E14:J14"/>
-    <mergeCell ref="BK20:BR20"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="BC27:BK27"/>
     <mergeCell ref="BK2:BR2"/>
-    <mergeCell ref="BK17:BR17"/>
-    <mergeCell ref="E23:J23"/>
-    <mergeCell ref="BS24:CD24"/>
-    <mergeCell ref="BS18:CD18"/>
+    <mergeCell ref="AK28:AS28"/>
+    <mergeCell ref="AB26:AJ26"/>
     <mergeCell ref="Q5:BJ5"/>
-    <mergeCell ref="BK22:BR22"/>
-    <mergeCell ref="BK31:BR31"/>
-    <mergeCell ref="BS26:CD26"/>
-    <mergeCell ref="AQ27:BJ27"/>
-    <mergeCell ref="K18:AP18"/>
-    <mergeCell ref="BK25:BR25"/>
-    <mergeCell ref="BK15:BR15"/>
-    <mergeCell ref="AQ30:BJ30"/>
-    <mergeCell ref="K16:AP16"/>
-    <mergeCell ref="BS19:CD19"/>
-    <mergeCell ref="AQ20:BJ20"/>
-    <mergeCell ref="AQ25:BJ25"/>
+    <mergeCell ref="J24:R24"/>
+    <mergeCell ref="AB16:AJ16"/>
+    <mergeCell ref="AK30:AS30"/>
+    <mergeCell ref="AT24:BB24"/>
+    <mergeCell ref="AB25:AJ25"/>
+    <mergeCell ref="BL24:BT24"/>
+    <mergeCell ref="S14:AA14"/>
+    <mergeCell ref="AK14:AS14"/>
+    <mergeCell ref="S28:AA28"/>
+    <mergeCell ref="BC22:BK22"/>
+    <mergeCell ref="J26:R26"/>
+    <mergeCell ref="AB27:AJ27"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="BU20:CD20"/>
+    <mergeCell ref="BL26:BT26"/>
     <mergeCell ref="A12:CD12"/>
-    <mergeCell ref="BK26:BR26"/>
-    <mergeCell ref="E27:J27"/>
-    <mergeCell ref="AQ22:BJ22"/>
+    <mergeCell ref="BC21:BK21"/>
+    <mergeCell ref="J16:R16"/>
+    <mergeCell ref="J25:R25"/>
+    <mergeCell ref="BL16:BT16"/>
+    <mergeCell ref="AT19:BB19"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="BL25:BT25"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="BU22:CD22"/>
+    <mergeCell ref="BC14:BK14"/>
     <mergeCell ref="A32:CD32"/>
-    <mergeCell ref="K20:AP20"/>
-    <mergeCell ref="K29:AP29"/>
-    <mergeCell ref="E25:J25"/>
-    <mergeCell ref="BK18:BR18"/>
-    <mergeCell ref="K22:AP22"/>
-    <mergeCell ref="E18:J18"/>
-    <mergeCell ref="K31:AP31"/>
-    <mergeCell ref="BS28:CD28"/>
-    <mergeCell ref="AQ29:BJ29"/>
-    <mergeCell ref="AQ23:BJ23"/>
-    <mergeCell ref="AQ13:BJ13"/>
-    <mergeCell ref="K14:AP14"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="AQ31:BJ31"/>
+    <mergeCell ref="BU31:CD31"/>
+    <mergeCell ref="BC23:BK23"/>
+    <mergeCell ref="BL18:BT18"/>
+    <mergeCell ref="BC13:BK13"/>
+    <mergeCell ref="BU21:CD21"/>
+    <mergeCell ref="AB28:AJ28"/>
+    <mergeCell ref="S26:AA26"/>
+    <mergeCell ref="AK27:AS27"/>
+    <mergeCell ref="BU14:CD14"/>
+    <mergeCell ref="BU23:CD23"/>
+    <mergeCell ref="AT22:BB22"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="S16:AA16"/>
+    <mergeCell ref="AK17:AS17"/>
+    <mergeCell ref="AB30:AJ30"/>
+    <mergeCell ref="S25:AA25"/>
+    <mergeCell ref="J14:R14"/>
+    <mergeCell ref="AB20:AJ20"/>
+    <mergeCell ref="J29:R29"/>
+    <mergeCell ref="AB14:AJ14"/>
+    <mergeCell ref="AB29:AJ29"/>
+    <mergeCell ref="AT28:BB28"/>
+    <mergeCell ref="BL29:BT29"/>
     <mergeCell ref="O10:AO10"/>
-    <mergeCell ref="K23:AP23"/>
-    <mergeCell ref="BK19:BR19"/>
-    <mergeCell ref="BK16:BR16"/>
-    <mergeCell ref="E20:J20"/>
-    <mergeCell ref="AQ15:BJ15"/>
-    <mergeCell ref="BS14:CD14"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="BS23:CD23"/>
-    <mergeCell ref="AQ24:BJ24"/>
+    <mergeCell ref="S18:AA18"/>
+    <mergeCell ref="J13:R13"/>
+    <mergeCell ref="AK19:AS19"/>
+    <mergeCell ref="S27:AA27"/>
+    <mergeCell ref="BL13:BT13"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="S17:AA17"/>
     <mergeCell ref="O9:AO9"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E29:J29"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="BL31:BT31"/>
+    <mergeCell ref="BC16:BK16"/>
+    <mergeCell ref="AK25:AS25"/>
+    <mergeCell ref="J15:R15"/>
     <mergeCell ref="BS4:CD4"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="BK30:BR30"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="AQ26:BJ26"/>
+    <mergeCell ref="AT20:BB20"/>
+    <mergeCell ref="BC25:BK25"/>
+    <mergeCell ref="AT14:BB14"/>
+    <mergeCell ref="BL15:BT15"/>
+    <mergeCell ref="AT29:BB29"/>
+    <mergeCell ref="AT23:BB23"/>
+    <mergeCell ref="A18:I18"/>
     <mergeCell ref="BK6:BR6"/>
+    <mergeCell ref="BC18:BK18"/>
     <mergeCell ref="A2:P6"/>
-    <mergeCell ref="K24:AP24"/>
-    <mergeCell ref="E15:J15"/>
+    <mergeCell ref="BL30:BT30"/>
+    <mergeCell ref="AK20:AS20"/>
+    <mergeCell ref="AK29:AS29"/>
     <mergeCell ref="AP9:BC9"/>
+    <mergeCell ref="BU25:CD25"/>
+    <mergeCell ref="AT15:BB15"/>
     <mergeCell ref="BC34:CD34"/>
-    <mergeCell ref="K26:AP26"/>
-    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="AK22:AS22"/>
+    <mergeCell ref="AK31:AS31"/>
     <mergeCell ref="Q2:BJ4"/>
     <mergeCell ref="BD10:CD10"/>
+    <mergeCell ref="AB17:AJ17"/>
     <mergeCell ref="BC35:CD37"/>
-    <mergeCell ref="BS27:CD27"/>
-    <mergeCell ref="BK13:BR13"/>
-    <mergeCell ref="E16:J16"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="AT26:BB26"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="BC20:BK20"/>
+    <mergeCell ref="S29:AA29"/>
+    <mergeCell ref="BC29:BK29"/>
     <mergeCell ref="BK4:BR4"/>
     <mergeCell ref="BS2:CD2"/>
-    <mergeCell ref="BS17:CD17"/>
+    <mergeCell ref="J18:R18"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="AB19:AJ19"/>
     <mergeCell ref="A38:CD38"/>
-    <mergeCell ref="BS25:CD25"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="S31:AA31"/>
+    <mergeCell ref="J17:R17"/>
+    <mergeCell ref="AK23:AS23"/>
+    <mergeCell ref="BC31:BK31"/>
+    <mergeCell ref="AT17:BB17"/>
     <mergeCell ref="AB34:BB34"/>
-    <mergeCell ref="BK24:BR24"/>
-    <mergeCell ref="AQ14:BJ14"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="AQ28:BJ28"/>
+    <mergeCell ref="BL17:BT17"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="AT25:BB25"/>
+    <mergeCell ref="S21:AA21"/>
+    <mergeCell ref="BC15:BK15"/>
+    <mergeCell ref="BU29:CD29"/>
     <mergeCell ref="BS3:CD3"/>
-    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="J19:R19"/>
+    <mergeCell ref="J28:R28"/>
+    <mergeCell ref="BU13:CD13"/>
+    <mergeCell ref="BL19:BT19"/>
+    <mergeCell ref="BC30:BK30"/>
+    <mergeCell ref="BL28:BT28"/>
+    <mergeCell ref="AK18:AS18"/>
     <mergeCell ref="BS5:CD5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
